--- a/New Files/Problem Repository.xlsx
+++ b/New Files/Problem Repository.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pomfegranate\Documents\GitHub\calculus-worksheets\New Files\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pomf\Documents\GitHub\calculus-worksheets\New Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CDC4DBB-250D-4CF1-9BC5-69FCC6F54238}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D56604-0520-4270-A0B9-026927E5B254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="49368" windowHeight="25668" xr2:uid="{D3F02B99-6D0D-4708-8A55-E87CA732C5E2}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="21285" xr2:uid="{D3F02B99-6D0D-4708-8A55-E87CA732C5E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/metadata.xml><?xml version="1.0" encoding="utf-8"?>
-<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
+<metadata xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:xlrd="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata" xmlns:xda="http://schemas.microsoft.com/office/spreadsheetml/2017/dynamicarray">
   <metadataTypes count="1">
     <metadataType name="XLDAPR" minSupportedVersion="120000" copy="1" pasteAll="1" pasteValues="1" merge="1" splitFirst="1" rowColShift="1" clearFormats="1" clearComments="1" assign="1" coerce="1" cellMeta="1"/>
   </metadataTypes>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="240" uniqueCount="174">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="229">
   <si>
     <t>Question</t>
   </si>
@@ -937,6 +937,277 @@
   </si>
   <si>
     <t>Problem Character Length (Use to Gauge Difficulty/Length)</t>
+  </si>
+  <si>
+    <t>Below is the graph of a function $f(x)$. Answer the following questions:
+\begin{center}
+\begin{tikzpicture}
+\begin{axis}[
+    width = 0.8\linewidth,
+    height = 0.8\linewidth,
+    grid = major,
+    axis lines = middle,
+    axis on top,
+    xlabel = \(x\),
+    ylabel = {\(f(x)\)},
+    xmin = -4,
+    xmax = 7,
+    ymin = -5,
+    ymax = 6,
+    minor tick num=1,
+    minor tick style={draw=none},
+]
+\addplot [
+    domain=-3:0, 
+    samples=100, 
+    color=red,
+    smooth
+]
+{-sqrt(9-x^2)+3};
+\addplot [
+    domain=3:6, 
+    samples=100, 
+    color=blue,
+    smooth
+]
+{-sqrt(9-(x-3)^2)};
+\addplot[mark=*, color=red] coordinates {(-3,3)};
+\addplot[mark=o, color=red] coordinates {(0,0)};
+\addplot[mark=o, color=blue] coordinates {(3,-3)};
+\addplot[mark=*, color=blue] coordinates {(6,0)};
+\end{axis}
+\end{tikzpicture}
+\end{center}
+\begin{enumerate}
+\item Is the function 1-to-1? How can you visually tell?
+\vfill
+\item Graph $f^{-1}(x)$ on the same $xy$-plane.
+\vfill
+\item  What is the domain of $f^{-1}$?
+\vfill
+\item What is the range or co-domain of $f^{-1}$?
+\vfill
+\item What is $f^{-1}(0)$?
+\vfill
+\end{enumerate}</t>
+  </si>
+  <si>
+    <t>Trey Carney</t>
+  </si>
+  <si>
+    <t>Let $f(x) = \dfrac{3}{1-x}$. Find $f^{-1}(x)$. Verify your answer by checking that $f^{-1}(f(x)) = x$.</t>
+  </si>
+  <si>
+    <t>Let $f(x) = \sqrt[3]{5-2x}$. Find $f^{-1}(x)$.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Find the domain and range of $f(x) = \dfrac{1-x}{x+2}$.  </t>
+  </si>
+  <si>
+    <t>Consider this graph of $y=f(x)$ and answer the questions below:
+\begin{center}
+\begin{tikzpicture}
+\begin{axis}[
+    width = 0.8\linewidth,
+    height = 0.8\linewidth,
+    grid = major,
+    axis lines = middle,
+    axis on top,
+    xlabel = \(x\),
+    ylabel = {\(f(x)\)},
+    xmin = -11,
+    xmax = 11,
+    ymin = -11,
+    ymax = 11,
+    minor tick num=1,
+    minor tick style={draw=none},
+]
+\addplot [
+    domain=-11:4, 
+    samples=100, 
+    color=red,
+    smooth
+]
+{-2*sqrt(-(x-4))};
+\addplot [
+    domain=4:11, 
+    samples=100, 
+    color=blue,
+    smooth
+]
+{x-4};
+\end{axis}
+\end{tikzpicture}
+\end{center}
+\begin{enumerate}
+\item What is $f^{-1}(-4)$?
+\item What is $f^{-1}(-2)$?
+\item What is $f^{-1}(5)$?
+\end{enumerate}</t>
+  </si>
+  <si>
+    <t>Solve for $x$: $\ln{(x+1)}-\ln{(x-1)}=1$</t>
+  </si>
+  <si>
+    <t>Solve for $x$: $e^{2x}-3e^x=-2$</t>
+  </si>
+  <si>
+    <t>Find the derivative $y'$: $y=x^3e^{-\frac{1}{x}}$</t>
+  </si>
+  <si>
+    <t>Find the derivative $y'$: $y=\frac{e^{\sin(2x)}}{1+\cos(x)}$</t>
+  </si>
+  <si>
+    <t>Evaluate the integral $$\int\frac{2x^3+x^2-3x}{3x^4+2x^3-9x^2+7}dx$$</t>
+  </si>
+  <si>
+    <t>Evaluate the definite integral $$\int_{\frac{\pi}{4}}^{\frac{\pi}{3}}\frac{8\sin(2x)}{5+6\sin^2(x)}dx$$</t>
+  </si>
+  <si>
+    <t>Find the derivative of: $f(x)=(\sin(2x))^{\sqrt{x}}$</t>
+  </si>
+  <si>
+    <t>Find the derivative of: $g(x)=(\sin^{-1}(x^3+2x-3))^2$</t>
+  </si>
+  <si>
+    <t>Find the derivative of:$h(x)=3x^3\sec^{-1}(\sqrt{x^2+1})$</t>
+  </si>
+  <si>
+    <t>Evaluate the integral using an appropriate substitution: $\int\frac{3x}{x^4+25}dx$</t>
+  </si>
+  <si>
+    <t>Evaluate the integral using an appropriate substitution: $\int\frac{4e^{3x}}{\sqrt{1-e^{6x}}}dx$</t>
+  </si>
+  <si>
+    <t>Evaluate the integral using integration by parts: $\int\ln(x^{x^2-3x})dx$</t>
+  </si>
+  <si>
+    <t>Evaluate the integral using integration by parts: $\int x^2\sin(3x)dx$</t>
+  </si>
+  <si>
+    <t>Evaluate the integral using integration by parts: $\int_0^1 e^{\sqrt{x}}dx$ (Hint: first take a u-substitution $t=\sqrt{x}$)</t>
+  </si>
+  <si>
+    <t>Evaluate the integral: $\int\frac{e^x}{1+16e^{2x}}dx$</t>
+  </si>
+  <si>
+    <t>Evaluate the integral: $\int\frac{1}{\sqrt{9-4x^2}}dx$</t>
+  </si>
+  <si>
+    <t>Evaluate the integral: $\int\frac{1}{x^2(x-1)}dx$</t>
+  </si>
+  <si>
+    <t>Evaluate the definite integral:
+$$\int_0^1(1+x^2)dx$$</t>
+  </si>
+  <si>
+    <t>\begin{enumerate}
+\item Evaluate the definite integral:
+$$\int_0^1(1+x^2)dx$$
+\vfill
+\item Find the Trapezoid rule approximation $T_5$ using $n=5$ rectangles.
+\vfill
+\newpage
+\item Using the last two problems, what is the magnitude of the absolute error $|E_{T_5}|=|\int_0^1(1+x^2)dx-T_5|$?
+\vfill
+\item What is the upper bound of of the error $|E_{T_5}|$ applied to this particular $n=5$, $a=0$, $b=1$, and $f(x)=1+x^2$? Comment on how this compares to what you found in the last question.</t>
+  </si>
+  <si>
+    <t>Suppose you wish to estimate $\int_0^15x^4dx$ to an accuracy having an Error  of $|E|&lt;10^{-3}$. How large would you need to choose $n$ for...
+\begin{enumerate}
+    \item Simpson's Rule?
+    \item the Trapezoid Rule?
+    \item Mid-point Rule?
+\end{enumerate}</t>
+  </si>
+  <si>
+    <t>Show the integral converges via Comparison Test
+$$\int_1^{\infty}\frac{x^2}{x^5+1}$$</t>
+  </si>
+  <si>
+    <t>Calculate the improper integral: $$\int_1^3\frac{1}{\sqrt{3-x}}dx$$</t>
+  </si>
+  <si>
+    <t>Calculate the improper integral: $$\int_{0}^{\infty}4x^2e^{-x^3}dx$$</t>
+  </si>
+  <si>
+    <t>Calculate the improper integral: $$\int_{-\infty}^{1}xe^{4x}dx$$</t>
+  </si>
+  <si>
+    <t>Calculate the improper integral: $$\int_0^9\frac{1}{\sqrt[3]{x-1}}dx$$</t>
+  </si>
+  <si>
+    <t>Show the integral diverges via Comparison Test
+$$\int_1^{\infty}\frac{7x^4}{x^5+2}$$</t>
+  </si>
+  <si>
+    <t>This series converges. Calculate its sum: $$\sum_{n=1}^{\infty}\left(\frac{1}{n}-\frac{1}{n+2}\right)$$</t>
+  </si>
+  <si>
+    <t>This series converges. Calculate its sum: $$\sum_{n=2}^{\infty}\frac{4}{n^2-1}$$</t>
+  </si>
+  <si>
+    <t>This series converges. Calculate its sum: $$\sum_{n=1}^{\infty}\left(\frac{2^n+3^n}{e^{2n}}\right)$$</t>
+  </si>
+  <si>
+    <t>This series converges. Calculate its sum: $$\sum_{n=0}^{\infty}\frac{-7}{4^{2n}}$$</t>
+  </si>
+  <si>
+    <t>Determine if the integral test for convergence applies (the comparable continuous function $f(x)$ must be continuous, positive, and decreasing for $x\in[1,\infty)$) and then if it does, show either convergence or divergence: $$\sum_{n=1}^{\infty}n^2e^{-n^3}$$</t>
+  </si>
+  <si>
+    <t>Determine if the integral test for convergence applies (the comparable continuous function $f(x)$ must be continuous, positive, and decreasing for $x\in[1,\infty)$) and then if it does, show either convergence or divergence: $$\sum_{n=1}^{\infty}\frac{\sqrt{n}}{1+\sqrt{n^3}}$$</t>
+  </si>
+  <si>
+    <t>Test the series for convergence/divergence: $$\sum_{n=0}^{\infty}\frac{(-1)^{n+1}}{\sqrt{n+1}}$$</t>
+  </si>
+  <si>
+    <t>Test the series for convergence/divergence: $$\sum_{n=1}^{\infty}\frac{(-1)^{n}\sqrt{n}}{2n}$$</t>
+  </si>
+  <si>
+    <t>Test the series for convergence/divergence: $$\sum_{n=1}^{\infty}(-1)^{n-1}\tan^{-1}(n)$$</t>
+  </si>
+  <si>
+    <t>Test the series for convergence/divergence: $$\sum_{n=1}^{\infty}(-1)^{n}\cos\left(\frac{\pi}{n}\right)$$</t>
+  </si>
+  <si>
+    <t>Test the series for convergence/divergence: $$\sum_{n=1}^{\infty}\frac{n\cos(n\pi)}{2^n}$$</t>
+  </si>
+  <si>
+    <t>Find the interval of convergence of the power series: $$\sum_{n=1}^{\infty}\frac{(-1)^{n+1}x^n}{\sqrt[3]{n}}$$</t>
+  </si>
+  <si>
+    <t>Find the interval of convergence of the power series: $$\sum_{n=1}^{\infty}\frac{(-1)^{n-1}x^n}{n5^n}$$</t>
+  </si>
+  <si>
+    <t>Find the interval of convergence of the power series: $$\sum_{n=0}^{\infty}\frac{x^{2n}}{n!}$$</t>
+  </si>
+  <si>
+    <t>Approximate the numerical value of $e^{\pi}$ using the $2$nd order Taylor polynomial $T_2(x)$ for the function $f(x)=e^x$ centered at $a=0$. How far off is the approximation? How far off does Taylor's Inequality allow (make sure you did better than this worst case guarantee)?</t>
+  </si>
+  <si>
+    <t>Approximate the numerical value of $\arctan(1.5)$ using the $2$nd order Taylor polynomial $T_2(x)$ for the function $f(x)=\arctan(x)$ centered at $a=1$. How far off is the approximation? How far off does Taylor's Inequality allow (make sure you did better than this worst case guarantee)?</t>
+  </si>
+  <si>
+    <t>Find the general or particular solution of the separable differential equation by using the method of separation of variables. \emph{Next, check that your answer is correct by differentiating!}: $\frac{dy}{dx}-e^{x+y}=0$</t>
+  </si>
+  <si>
+    <t>Find the general or particular solution of the separable differential equation by using the method of separation of variables. \emph{Next, check that your answer is correct by differentiating!}: $\frac{dy}{dx}=\frac{2x\sin(x^2)}{y};\quad y(0)=-1$</t>
+  </si>
+  <si>
+    <t>Find the particular solution of the first order linear differential equation by using an integrating factor. \emph{Next, check that your answer is correct by differentiating!}: $$x\frac{dy}{dx}+y=x\ln(x);\quad y(1)=0$$</t>
+  </si>
+  <si>
+    <t>Difficulty</t>
+  </si>
+  <si>
+    <t>Easy</t>
+  </si>
+  <si>
+    <t>Medium</t>
+  </si>
+  <si>
+    <t>Hard</t>
   </si>
 </sst>
 </file>
@@ -1086,7 +1357,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="10">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1"/>
@@ -1100,6 +1371,7 @@
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Explanatory Text" xfId="5" builtinId="53"/>
@@ -1439,19 +1711,19 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2206F7A8-9F15-490A-ABDA-74F02C917F9D}">
-  <dimension ref="A1:G300"/>
-  <sheetFormatPr defaultRowHeight="15" customHeight="1" thickTop="1" thickBottom="1" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:H300"/>
+  <sheetFormatPr defaultRowHeight="15" customHeight="1" thickTop="1" thickBottom="1" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="13.6640625" style="3" customWidth="1"/>
-    <col min="2" max="2" width="9.6640625" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="52.109375" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="10.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="13.44140625" style="6" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="16.6640625" style="8" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" style="8"/>
+    <col min="1" max="1" width="13.7109375" style="3" customWidth="1"/>
+    <col min="2" max="2" width="9.7109375" style="5" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="52.140625" style="5" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="10.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="13.42578125" style="6" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="16.7109375" style="8" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" style="8"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:8" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1473,8 +1745,11 @@
       <c r="G1" s="2" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H1" s="9" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A2" s="3" t="s">
         <v>88</v>
       </c>
@@ -1497,11 +1772,15 @@
         <v>168</v>
       </c>
       <c r="G2" s="8">
-        <f>IF(LEN(A2)=0,"",LEN(A2))</f>
+        <f t="shared" ref="G2:G65" si="0">IF(LEN(A2)=0,"",LEN(A2))</f>
         <v>115</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H2" t="str" cm="1">
+        <f t="array" ref="H2">_xlfn.IFS(G2="","",G2&gt;1000,"Hard",AND(G2&gt;150,G2&lt;=1000),"Medium",AND(G2&gt;0,G2&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A3" s="3" t="s">
         <v>89</v>
       </c>
@@ -1520,12 +1799,19 @@
         <f t="array" aca="1" ref="E3" ca="1">_xlfn.IFNA(_xlfn.IFS(D3&lt;6,1,D3&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F3" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G3" s="8">
-        <f t="shared" ref="G3:G66" si="0">IF(LEN(A3)=0,"",LEN(A3))</f>
+        <f t="shared" si="0"/>
         <v>37</v>
       </c>
-    </row>
-    <row r="4" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H3" t="str" cm="1">
+        <f t="array" ref="H3">_xlfn.IFS(G3="","",G3&gt;1000,"Hard",AND(G3&gt;150,G3&lt;=1000),"Medium",AND(G3&gt;0,G3&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A4" s="3" t="s">
         <v>90</v>
       </c>
@@ -1544,12 +1830,19 @@
         <f t="array" aca="1" ref="E4" ca="1">_xlfn.IFNA(_xlfn.IFS(D4&lt;6,1,D4&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F4" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G4" s="8">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="5" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H4" t="str" cm="1">
+        <f t="array" ref="H4">_xlfn.IFS(G4="","",G4&gt;1000,"Hard",AND(G4&gt;150,G4&lt;=1000),"Medium",AND(G4&gt;0,G4&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="5" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>91</v>
       </c>
@@ -1568,12 +1861,19 @@
         <f t="array" aca="1" ref="E5" ca="1">_xlfn.IFNA(_xlfn.IFS(D5&lt;6,1,D5&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F5" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G5" s="8">
         <f t="shared" si="0"/>
         <v>40</v>
       </c>
-    </row>
-    <row r="6" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H5" t="str" cm="1">
+        <f t="array" ref="H5">_xlfn.IFS(G5="","",G5&gt;1000,"Hard",AND(G5&gt;150,G5&lt;=1000),"Medium",AND(G5&gt;0,G5&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A6" s="3" t="s">
         <v>92</v>
       </c>
@@ -1592,12 +1892,19 @@
         <f t="array" aca="1" ref="E6" ca="1">_xlfn.IFNA(_xlfn.IFS(D6&lt;6,1,D6&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F6" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G6" s="8">
         <f t="shared" si="0"/>
         <v>45</v>
       </c>
-    </row>
-    <row r="7" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H6" t="str" cm="1">
+        <f t="array" ref="H6">_xlfn.IFS(G6="","",G6&gt;1000,"Hard",AND(G6&gt;150,G6&lt;=1000),"Medium",AND(G6&gt;0,G6&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>93</v>
       </c>
@@ -1616,12 +1923,19 @@
         <f t="array" aca="1" ref="E7" ca="1">_xlfn.IFNA(_xlfn.IFS(D7&lt;6,1,D7&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F7" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G7" s="8">
         <f t="shared" si="0"/>
         <v>52</v>
       </c>
-    </row>
-    <row r="8" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H7" t="str" cm="1">
+        <f t="array" ref="H7">_xlfn.IFS(G7="","",G7&gt;1000,"Hard",AND(G7&gt;150,G7&lt;=1000),"Medium",AND(G7&gt;0,G7&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="8" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="3" t="s">
         <v>94</v>
       </c>
@@ -1640,12 +1954,19 @@
         <f t="array" aca="1" ref="E8" ca="1">_xlfn.IFNA(_xlfn.IFS(D8&lt;6,1,D8&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F8" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G8" s="8">
         <f t="shared" si="0"/>
         <v>196</v>
       </c>
-    </row>
-    <row r="9" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H8" t="str" cm="1">
+        <f t="array" ref="H8">_xlfn.IFS(G8="","",G8&gt;1000,"Hard",AND(G8&gt;150,G8&lt;=1000),"Medium",AND(G8&gt;0,G8&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="9" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="3" t="s">
         <v>95</v>
       </c>
@@ -1664,12 +1985,19 @@
         <f t="array" aca="1" ref="E9" ca="1">_xlfn.IFNA(_xlfn.IFS(D9&lt;6,1,D9&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F9" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G9" s="8">
         <f t="shared" si="0"/>
         <v>196</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H9" t="str" cm="1">
+        <f t="array" ref="H9">_xlfn.IFS(G9="","",G9&gt;1000,"Hard",AND(G9&gt;150,G9&lt;=1000),"Medium",AND(G9&gt;0,G9&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="10" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A10" s="3" t="s">
         <v>96</v>
       </c>
@@ -1688,12 +2016,19 @@
         <f t="array" aca="1" ref="E10" ca="1">_xlfn.IFNA(_xlfn.IFS(D10&lt;6,1,D10&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F10" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G10" s="8">
         <f t="shared" si="0"/>
         <v>199</v>
       </c>
-    </row>
-    <row r="11" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H10" t="str" cm="1">
+        <f t="array" ref="H10">_xlfn.IFS(G10="","",G10&gt;1000,"Hard",AND(G10&gt;150,G10&lt;=1000),"Medium",AND(G10&gt;0,G10&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="11" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>97</v>
       </c>
@@ -1712,12 +2047,19 @@
         <f t="array" aca="1" ref="E11" ca="1">_xlfn.IFNA(_xlfn.IFS(D11&lt;6,1,D11&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F11" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G11" s="8">
         <f t="shared" si="0"/>
         <v>2529</v>
       </c>
-    </row>
-    <row r="12" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H11" t="str" cm="1">
+        <f t="array" ref="H11">_xlfn.IFS(G11="","",G11&gt;1000,"Hard",AND(G11&gt;150,G11&lt;=1000),"Medium",AND(G11&gt;0,G11&lt;=150),"Easy")</f>
+        <v>Hard</v>
+      </c>
+    </row>
+    <row r="12" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A12" s="3" t="s">
         <v>100</v>
       </c>
@@ -1736,12 +2078,19 @@
         <f t="array" aca="1" ref="E12" ca="1">_xlfn.IFNA(_xlfn.IFS(D12&lt;6,1,D12&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F12" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G12" s="8">
         <f t="shared" si="0"/>
         <v>266</v>
       </c>
-    </row>
-    <row r="13" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H12" t="str" cm="1">
+        <f t="array" ref="H12">_xlfn.IFS(G12="","",G12&gt;1000,"Hard",AND(G12&gt;150,G12&lt;=1000),"Medium",AND(G12&gt;0,G12&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="13" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A13" s="3" t="s">
         <v>101</v>
       </c>
@@ -1760,12 +2109,19 @@
         <f t="array" aca="1" ref="E13" ca="1">_xlfn.IFNA(_xlfn.IFS(D13&lt;6,1,D13&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F13" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G13" s="8">
         <f t="shared" si="0"/>
         <v>265</v>
       </c>
-    </row>
-    <row r="14" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H13" t="str" cm="1">
+        <f t="array" ref="H13">_xlfn.IFS(G13="","",G13&gt;1000,"Hard",AND(G13&gt;150,G13&lt;=1000),"Medium",AND(G13&gt;0,G13&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="14" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A14" s="3" t="s">
         <v>98</v>
       </c>
@@ -1784,12 +2140,19 @@
         <f t="array" aca="1" ref="E14" ca="1">_xlfn.IFNA(_xlfn.IFS(D14&lt;6,1,D14&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F14" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G14" s="8">
         <f t="shared" si="0"/>
         <v>271</v>
       </c>
-    </row>
-    <row r="15" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H14" t="str" cm="1">
+        <f t="array" ref="H14">_xlfn.IFS(G14="","",G14&gt;1000,"Hard",AND(G14&gt;150,G14&lt;=1000),"Medium",AND(G14&gt;0,G14&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="15" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
         <v>99</v>
       </c>
@@ -1808,12 +2171,19 @@
         <f t="array" aca="1" ref="E15" ca="1">_xlfn.IFNA(_xlfn.IFS(D15&lt;6,1,D15&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F15" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G15" s="8">
         <f t="shared" si="0"/>
         <v>264</v>
       </c>
-    </row>
-    <row r="16" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H15" t="str" cm="1">
+        <f t="array" ref="H15">_xlfn.IFS(G15="","",G15&gt;1000,"Hard",AND(G15&gt;150,G15&lt;=1000),"Medium",AND(G15&gt;0,G15&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A16" s="3" t="s">
         <v>102</v>
       </c>
@@ -1832,12 +2202,19 @@
         <f t="array" aca="1" ref="E16" ca="1">_xlfn.IFNA(_xlfn.IFS(D16&lt;6,1,D16&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F16" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G16" s="8">
         <f t="shared" si="0"/>
         <v>88</v>
       </c>
-    </row>
-    <row r="17" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H16" t="str" cm="1">
+        <f t="array" ref="H16">_xlfn.IFS(G16="","",G16&gt;1000,"Hard",AND(G16&gt;150,G16&lt;=1000),"Medium",AND(G16&gt;0,G16&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="17" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A17" s="3" t="s">
         <v>103</v>
       </c>
@@ -1856,12 +2233,19 @@
         <f t="array" aca="1" ref="E17" ca="1">_xlfn.IFNA(_xlfn.IFS(D17&lt;6,1,D17&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F17" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G17" s="8">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-    </row>
-    <row r="18" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H17" t="str" cm="1">
+        <f t="array" ref="H17">_xlfn.IFS(G17="","",G17&gt;1000,"Hard",AND(G17&gt;150,G17&lt;=1000),"Medium",AND(G17&gt;0,G17&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="18" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A18" s="3" t="s">
         <v>104</v>
       </c>
@@ -1880,12 +2264,19 @@
         <f t="array" aca="1" ref="E18" ca="1">_xlfn.IFNA(_xlfn.IFS(D18&lt;6,1,D18&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F18" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G18" s="8">
         <f t="shared" si="0"/>
         <v>148</v>
       </c>
-    </row>
-    <row r="19" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H18" t="str" cm="1">
+        <f t="array" ref="H18">_xlfn.IFS(G18="","",G18&gt;1000,"Hard",AND(G18&gt;150,G18&lt;=1000),"Medium",AND(G18&gt;0,G18&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="19" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>105</v>
       </c>
@@ -1904,12 +2295,19 @@
         <f t="array" aca="1" ref="E19" ca="1">_xlfn.IFNA(_xlfn.IFS(D19&lt;6,1,D19&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F19" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G19" s="8">
         <f t="shared" si="0"/>
         <v>1984</v>
       </c>
-    </row>
-    <row r="20" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H19" t="str" cm="1">
+        <f t="array" ref="H19">_xlfn.IFS(G19="","",G19&gt;1000,"Hard",AND(G19&gt;150,G19&lt;=1000),"Medium",AND(G19&gt;0,G19&lt;=150),"Easy")</f>
+        <v>Hard</v>
+      </c>
+    </row>
+    <row r="20" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>106</v>
       </c>
@@ -1928,12 +2326,19 @@
         <f t="array" aca="1" ref="E20" ca="1">_xlfn.IFNA(_xlfn.IFS(D20&lt;6,1,D20&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F20" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G20" s="8">
         <f t="shared" si="0"/>
         <v>367</v>
       </c>
-    </row>
-    <row r="21" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H20" t="str" cm="1">
+        <f t="array" ref="H20">_xlfn.IFS(G20="","",G20&gt;1000,"Hard",AND(G20&gt;150,G20&lt;=1000),"Medium",AND(G20&gt;0,G20&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="21" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>107</v>
       </c>
@@ -1952,12 +2357,19 @@
         <f t="array" aca="1" ref="E21" ca="1">_xlfn.IFNA(_xlfn.IFS(D21&lt;6,1,D21&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F21" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G21" s="8">
         <f t="shared" si="0"/>
         <v>328</v>
       </c>
-    </row>
-    <row r="22" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H21" t="str" cm="1">
+        <f t="array" ref="H21">_xlfn.IFS(G21="","",G21&gt;1000,"Hard",AND(G21&gt;150,G21&lt;=1000),"Medium",AND(G21&gt;0,G21&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="22" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A22" s="4" t="s">
         <v>108</v>
       </c>
@@ -1976,12 +2388,19 @@
         <f t="array" aca="1" ref="E22" ca="1">_xlfn.IFNA(_xlfn.IFS(D22&lt;6,1,D22&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F22" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G22" s="8">
         <f t="shared" si="0"/>
         <v>543</v>
       </c>
-    </row>
-    <row r="23" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H22" t="str" cm="1">
+        <f t="array" ref="H22">_xlfn.IFS(G22="","",G22&gt;1000,"Hard",AND(G22&gt;150,G22&lt;=1000),"Medium",AND(G22&gt;0,G22&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="23" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A23" s="3" t="s">
         <v>109</v>
       </c>
@@ -2000,12 +2419,19 @@
         <f t="array" aca="1" ref="E23" ca="1">_xlfn.IFNA(_xlfn.IFS(D23&lt;6,1,D23&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F23" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G23" s="8">
         <f t="shared" si="0"/>
         <v>112</v>
       </c>
-    </row>
-    <row r="24" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H23" t="str" cm="1">
+        <f t="array" ref="H23">_xlfn.IFS(G23="","",G23&gt;1000,"Hard",AND(G23&gt;150,G23&lt;=1000),"Medium",AND(G23&gt;0,G23&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="24" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
         <v>110</v>
       </c>
@@ -2024,12 +2450,19 @@
         <f t="array" aca="1" ref="E24" ca="1">_xlfn.IFNA(_xlfn.IFS(D24&lt;6,1,D24&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F24" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G24" s="8">
         <f t="shared" si="0"/>
         <v>109</v>
       </c>
-    </row>
-    <row r="25" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H24" t="str" cm="1">
+        <f t="array" ref="H24">_xlfn.IFS(G24="","",G24&gt;1000,"Hard",AND(G24&gt;150,G24&lt;=1000),"Medium",AND(G24&gt;0,G24&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="25" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
         <v>111</v>
       </c>
@@ -2048,12 +2481,19 @@
         <f t="array" aca="1" ref="E25" ca="1">_xlfn.IFNA(_xlfn.IFS(D25&lt;6,1,D25&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F25" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G25" s="8">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-    </row>
-    <row r="26" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H25" t="str" cm="1">
+        <f t="array" ref="H25">_xlfn.IFS(G25="","",G25&gt;1000,"Hard",AND(G25&gt;150,G25&lt;=1000),"Medium",AND(G25&gt;0,G25&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="26" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A26" s="3" t="s">
         <v>112</v>
       </c>
@@ -2072,12 +2512,19 @@
         <f t="array" aca="1" ref="E26" ca="1">_xlfn.IFNA(_xlfn.IFS(D26&lt;6,1,D26&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F26" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G26" s="8">
         <f t="shared" si="0"/>
         <v>145</v>
       </c>
-    </row>
-    <row r="27" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H26" t="str" cm="1">
+        <f t="array" ref="H26">_xlfn.IFS(G26="","",G26&gt;1000,"Hard",AND(G26&gt;150,G26&lt;=1000),"Medium",AND(G26&gt;0,G26&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="27" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A27" s="3" t="s">
         <v>113</v>
       </c>
@@ -2096,12 +2543,19 @@
         <f t="array" aca="1" ref="E27" ca="1">_xlfn.IFNA(_xlfn.IFS(D27&lt;6,1,D27&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F27" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G27" s="8">
         <f t="shared" si="0"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="28" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H27" t="str" cm="1">
+        <f t="array" ref="H27">_xlfn.IFS(G27="","",G27&gt;1000,"Hard",AND(G27&gt;150,G27&lt;=1000),"Medium",AND(G27&gt;0,G27&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="28" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A28" s="3" t="s">
         <v>114</v>
       </c>
@@ -2120,12 +2574,19 @@
         <f t="array" aca="1" ref="E28" ca="1">_xlfn.IFNA(_xlfn.IFS(D28&lt;6,1,D28&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F28" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G28" s="8">
         <f t="shared" si="0"/>
         <v>102</v>
       </c>
-    </row>
-    <row r="29" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H28" t="str" cm="1">
+        <f t="array" ref="H28">_xlfn.IFS(G28="","",G28&gt;1000,"Hard",AND(G28&gt;150,G28&lt;=1000),"Medium",AND(G28&gt;0,G28&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="29" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A29" s="3" t="s">
         <v>115</v>
       </c>
@@ -2144,12 +2605,19 @@
         <f t="array" aca="1" ref="E29" ca="1">_xlfn.IFNA(_xlfn.IFS(D29&lt;6,1,D29&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F29" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G29" s="8">
         <f t="shared" si="0"/>
         <v>110</v>
       </c>
-    </row>
-    <row r="30" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H29" t="str" cm="1">
+        <f t="array" ref="H29">_xlfn.IFS(G29="","",G29&gt;1000,"Hard",AND(G29&gt;150,G29&lt;=1000),"Medium",AND(G29&gt;0,G29&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="30" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A30" s="3" t="s">
         <v>116</v>
       </c>
@@ -2168,12 +2636,19 @@
         <f t="array" aca="1" ref="E30" ca="1">_xlfn.IFNA(_xlfn.IFS(D30&lt;6,1,D30&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F30" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G30" s="8">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-    </row>
-    <row r="31" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H30" t="str" cm="1">
+        <f t="array" ref="H30">_xlfn.IFS(G30="","",G30&gt;1000,"Hard",AND(G30&gt;150,G30&lt;=1000),"Medium",AND(G30&gt;0,G30&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="31" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A31" s="3" t="s">
         <v>117</v>
       </c>
@@ -2192,12 +2667,19 @@
         <f t="array" aca="1" ref="E31" ca="1">_xlfn.IFNA(_xlfn.IFS(D31&lt;6,1,D31&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F31" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G31" s="8">
         <f t="shared" si="0"/>
         <v>75</v>
       </c>
-    </row>
-    <row r="32" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H31" t="str" cm="1">
+        <f t="array" ref="H31">_xlfn.IFS(G31="","",G31&gt;1000,"Hard",AND(G31&gt;150,G31&lt;=1000),"Medium",AND(G31&gt;0,G31&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="32" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A32" s="3" t="s">
         <v>118</v>
       </c>
@@ -2216,12 +2698,19 @@
         <f t="array" aca="1" ref="E32" ca="1">_xlfn.IFNA(_xlfn.IFS(D32&lt;6,1,D32&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F32" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G32" s="8">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-    </row>
-    <row r="33" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H32" t="str" cm="1">
+        <f t="array" ref="H32">_xlfn.IFS(G32="","",G32&gt;1000,"Hard",AND(G32&gt;150,G32&lt;=1000),"Medium",AND(G32&gt;0,G32&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="33" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A33" s="3" t="s">
         <v>119</v>
       </c>
@@ -2240,12 +2729,19 @@
         <f t="array" aca="1" ref="E33" ca="1">_xlfn.IFNA(_xlfn.IFS(D33&lt;6,1,D33&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F33" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G33" s="8">
         <f t="shared" si="0"/>
         <v>36</v>
       </c>
-    </row>
-    <row r="34" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H33" t="str" cm="1">
+        <f t="array" ref="H33">_xlfn.IFS(G33="","",G33&gt;1000,"Hard",AND(G33&gt;150,G33&lt;=1000),"Medium",AND(G33&gt;0,G33&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="34" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A34" s="3" t="s">
         <v>120</v>
       </c>
@@ -2264,12 +2760,19 @@
         <f t="array" aca="1" ref="E34" ca="1">_xlfn.IFNA(_xlfn.IFS(D34&lt;6,1,D34&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F34" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G34" s="8">
         <f t="shared" si="0"/>
         <v>56</v>
       </c>
-    </row>
-    <row r="35" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H34" t="str" cm="1">
+        <f t="array" ref="H34">_xlfn.IFS(G34="","",G34&gt;1000,"Hard",AND(G34&gt;150,G34&lt;=1000),"Medium",AND(G34&gt;0,G34&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="35" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A35" s="3" t="s">
         <v>121</v>
       </c>
@@ -2288,12 +2791,19 @@
         <f t="array" aca="1" ref="E35" ca="1">_xlfn.IFNA(_xlfn.IFS(D35&lt;6,1,D35&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F35" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G35" s="8">
         <f t="shared" si="0"/>
         <v>61</v>
       </c>
-    </row>
-    <row r="36" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H35" t="str" cm="1">
+        <f t="array" ref="H35">_xlfn.IFS(G35="","",G35&gt;1000,"Hard",AND(G35&gt;150,G35&lt;=1000),"Medium",AND(G35&gt;0,G35&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="36" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A36" s="3" t="s">
         <v>122</v>
       </c>
@@ -2312,12 +2822,19 @@
         <f t="array" aca="1" ref="E36" ca="1">_xlfn.IFNA(_xlfn.IFS(D36&lt;6,1,D36&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F36" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G36" s="8">
         <f t="shared" si="0"/>
         <v>62</v>
       </c>
-    </row>
-    <row r="37" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H36" t="str" cm="1">
+        <f t="array" ref="H36">_xlfn.IFS(G36="","",G36&gt;1000,"Hard",AND(G36&gt;150,G36&lt;=1000),"Medium",AND(G36&gt;0,G36&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="37" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A37" s="4" t="s">
         <v>123</v>
       </c>
@@ -2336,12 +2853,19 @@
         <f t="array" aca="1" ref="E37" ca="1">_xlfn.IFNA(_xlfn.IFS(D37&lt;6,1,D37&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F37" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G37" s="8">
         <f t="shared" si="0"/>
         <v>463</v>
       </c>
-    </row>
-    <row r="38" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H37" t="str" cm="1">
+        <f t="array" ref="H37">_xlfn.IFS(G37="","",G37&gt;1000,"Hard",AND(G37&gt;150,G37&lt;=1000),"Medium",AND(G37&gt;0,G37&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="38" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A38" s="3" t="s">
         <v>124</v>
       </c>
@@ -2360,12 +2884,19 @@
         <f t="array" aca="1" ref="E38" ca="1">_xlfn.IFNA(_xlfn.IFS(D38&lt;6,1,D38&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F38" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G38" s="8">
         <f t="shared" si="0"/>
         <v>72</v>
       </c>
-    </row>
-    <row r="39" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H38" t="str" cm="1">
+        <f t="array" ref="H38">_xlfn.IFS(G38="","",G38&gt;1000,"Hard",AND(G38&gt;150,G38&lt;=1000),"Medium",AND(G38&gt;0,G38&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="39" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>125</v>
       </c>
@@ -2384,12 +2915,19 @@
         <f t="array" aca="1" ref="E39" ca="1">_xlfn.IFNA(_xlfn.IFS(D39&lt;6,1,D39&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F39" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G39" s="8">
         <f t="shared" si="0"/>
         <v>86</v>
       </c>
-    </row>
-    <row r="40" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H39" t="str" cm="1">
+        <f t="array" ref="H39">_xlfn.IFS(G39="","",G39&gt;1000,"Hard",AND(G39&gt;150,G39&lt;=1000),"Medium",AND(G39&gt;0,G39&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="40" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>126</v>
       </c>
@@ -2408,12 +2946,19 @@
         <f t="array" aca="1" ref="E40" ca="1">_xlfn.IFNA(_xlfn.IFS(D40&lt;6,1,D40&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F40" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G40" s="8">
         <f t="shared" si="0"/>
         <v>368</v>
       </c>
-    </row>
-    <row r="41" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H40" t="str" cm="1">
+        <f t="array" ref="H40">_xlfn.IFS(G40="","",G40&gt;1000,"Hard",AND(G40&gt;150,G40&lt;=1000),"Medium",AND(G40&gt;0,G40&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="41" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A41" s="3" t="s">
         <v>127</v>
       </c>
@@ -2432,12 +2977,19 @@
         <f t="array" aca="1" ref="E41" ca="1">_xlfn.IFNA(_xlfn.IFS(D41&lt;6,1,D41&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F41" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G41" s="8">
         <f t="shared" si="0"/>
         <v>79</v>
       </c>
-    </row>
-    <row r="42" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H41" t="str" cm="1">
+        <f t="array" ref="H41">_xlfn.IFS(G41="","",G41&gt;1000,"Hard",AND(G41&gt;150,G41&lt;=1000),"Medium",AND(G41&gt;0,G41&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="42" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A42" s="3" t="s">
         <v>128</v>
       </c>
@@ -2456,12 +3008,19 @@
         <f t="array" aca="1" ref="E42" ca="1">_xlfn.IFNA(_xlfn.IFS(D42&lt;6,1,D42&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F42" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G42" s="8">
         <f t="shared" si="0"/>
         <v>111</v>
       </c>
-    </row>
-    <row r="43" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H42" t="str" cm="1">
+        <f t="array" ref="H42">_xlfn.IFS(G42="","",G42&gt;1000,"Hard",AND(G42&gt;150,G42&lt;=1000),"Medium",AND(G42&gt;0,G42&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="43" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A43" s="4" t="s">
         <v>129</v>
       </c>
@@ -2480,12 +3039,19 @@
         <f t="array" aca="1" ref="E43" ca="1">_xlfn.IFNA(_xlfn.IFS(D43&lt;6,1,D43&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F43" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G43" s="8">
         <f t="shared" si="0"/>
         <v>116</v>
       </c>
-    </row>
-    <row r="44" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H43" t="str" cm="1">
+        <f t="array" ref="H43">_xlfn.IFS(G43="","",G43&gt;1000,"Hard",AND(G43&gt;150,G43&lt;=1000),"Medium",AND(G43&gt;0,G43&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A44" s="4" t="s">
         <v>130</v>
       </c>
@@ -2504,12 +3070,19 @@
         <f t="array" aca="1" ref="E44" ca="1">_xlfn.IFNA(_xlfn.IFS(D44&lt;6,1,D44&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F44" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G44" s="8">
         <f t="shared" si="0"/>
         <v>330</v>
       </c>
-    </row>
-    <row r="45" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H44" t="str" cm="1">
+        <f t="array" ref="H44">_xlfn.IFS(G44="","",G44&gt;1000,"Hard",AND(G44&gt;150,G44&lt;=1000),"Medium",AND(G44&gt;0,G44&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="45" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A45" s="4" t="s">
         <v>131</v>
       </c>
@@ -2528,12 +3101,19 @@
         <f t="array" aca="1" ref="E45" ca="1">_xlfn.IFNA(_xlfn.IFS(D45&lt;6,1,D45&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F45" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G45" s="8">
         <f t="shared" si="0"/>
         <v>248</v>
       </c>
-    </row>
-    <row r="46" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H45" t="str" cm="1">
+        <f t="array" ref="H45">_xlfn.IFS(G45="","",G45&gt;1000,"Hard",AND(G45&gt;150,G45&lt;=1000),"Medium",AND(G45&gt;0,G45&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="46" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A46" s="4" t="s">
         <v>132</v>
       </c>
@@ -2552,12 +3132,19 @@
         <f t="array" aca="1" ref="E46" ca="1">_xlfn.IFNA(_xlfn.IFS(D46&lt;6,1,D46&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F46" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G46" s="8">
         <f t="shared" si="0"/>
         <v>486</v>
       </c>
-    </row>
-    <row r="47" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H46" t="str" cm="1">
+        <f t="array" ref="H46">_xlfn.IFS(G46="","",G46&gt;1000,"Hard",AND(G46&gt;150,G46&lt;=1000),"Medium",AND(G46&gt;0,G46&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="47" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A47" s="3" t="s">
         <v>133</v>
       </c>
@@ -2576,12 +3163,19 @@
         <f t="array" aca="1" ref="E47" ca="1">_xlfn.IFNA(_xlfn.IFS(D47&lt;6,1,D47&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F47" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G47" s="8">
         <f t="shared" si="0"/>
         <v>171</v>
       </c>
-    </row>
-    <row r="48" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H47" t="str" cm="1">
+        <f t="array" ref="H47">_xlfn.IFS(G47="","",G47&gt;1000,"Hard",AND(G47&gt;150,G47&lt;=1000),"Medium",AND(G47&gt;0,G47&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="48" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A48" s="3" t="s">
         <v>134</v>
       </c>
@@ -2600,12 +3194,19 @@
         <f t="array" aca="1" ref="E48" ca="1">_xlfn.IFNA(_xlfn.IFS(D48&lt;6,1,D48&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F48" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G48" s="8">
         <f t="shared" si="0"/>
         <v>143</v>
       </c>
-    </row>
-    <row r="49" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H48" t="str" cm="1">
+        <f t="array" ref="H48">_xlfn.IFS(G48="","",G48&gt;1000,"Hard",AND(G48&gt;150,G48&lt;=1000),"Medium",AND(G48&gt;0,G48&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="49" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A49" s="4" t="s">
         <v>135</v>
       </c>
@@ -2624,12 +3225,19 @@
         <f t="array" aca="1" ref="E49" ca="1">_xlfn.IFNA(_xlfn.IFS(D49&lt;6,1,D49&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F49" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G49" s="8">
         <f t="shared" si="0"/>
         <v>2192</v>
       </c>
-    </row>
-    <row r="50" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H49" t="str" cm="1">
+        <f t="array" ref="H49">_xlfn.IFS(G49="","",G49&gt;1000,"Hard",AND(G49&gt;150,G49&lt;=1000),"Medium",AND(G49&gt;0,G49&lt;=150),"Easy")</f>
+        <v>Hard</v>
+      </c>
+    </row>
+    <row r="50" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A50" s="4" t="s">
         <v>152</v>
       </c>
@@ -2648,12 +3256,19 @@
         <f t="array" aca="1" ref="E50" ca="1">_xlfn.IFNA(_xlfn.IFS(D50&lt;6,1,D50&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F50" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G50" s="8">
         <f t="shared" si="0"/>
         <v>946</v>
       </c>
-    </row>
-    <row r="51" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H50" t="str" cm="1">
+        <f t="array" ref="H50">_xlfn.IFS(G50="","",G50&gt;1000,"Hard",AND(G50&gt;150,G50&lt;=1000),"Medium",AND(G50&gt;0,G50&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="51" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A51" s="3" t="s">
         <v>153</v>
       </c>
@@ -2672,12 +3287,19 @@
         <f t="array" aca="1" ref="E51" ca="1">_xlfn.IFNA(_xlfn.IFS(D51&lt;6,1,D51&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F51" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G51" s="8">
         <f t="shared" si="0"/>
         <v>78</v>
       </c>
-    </row>
-    <row r="52" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H51" t="str" cm="1">
+        <f t="array" ref="H51">_xlfn.IFS(G51="","",G51&gt;1000,"Hard",AND(G51&gt;150,G51&lt;=1000),"Medium",AND(G51&gt;0,G51&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="52" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A52" s="4" t="s">
         <v>154</v>
       </c>
@@ -2696,12 +3318,19 @@
         <f t="array" aca="1" ref="E52" ca="1">_xlfn.IFNA(_xlfn.IFS(D52&lt;6,1,D52&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F52" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G52" s="8">
         <f t="shared" si="0"/>
         <v>215</v>
       </c>
-    </row>
-    <row r="53" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H52" t="str" cm="1">
+        <f t="array" ref="H52">_xlfn.IFS(G52="","",G52&gt;1000,"Hard",AND(G52&gt;150,G52&lt;=1000),"Medium",AND(G52&gt;0,G52&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="53" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A53" s="4" t="s">
         <v>155</v>
       </c>
@@ -2720,12 +3349,19 @@
         <f t="array" aca="1" ref="E53" ca="1">_xlfn.IFNA(_xlfn.IFS(D53&lt;6,1,D53&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F53" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G53" s="8">
         <f t="shared" si="0"/>
         <v>210</v>
       </c>
-    </row>
-    <row r="54" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H53" t="str" cm="1">
+        <f t="array" ref="H53">_xlfn.IFS(G53="","",G53&gt;1000,"Hard",AND(G53&gt;150,G53&lt;=1000),"Medium",AND(G53&gt;0,G53&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="54" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A54" s="4" t="s">
         <v>156</v>
       </c>
@@ -2744,12 +3380,19 @@
         <f t="array" aca="1" ref="E54" ca="1">_xlfn.IFNA(_xlfn.IFS(D54&lt;6,1,D54&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F54" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G54" s="8">
         <f t="shared" si="0"/>
         <v>872</v>
       </c>
-    </row>
-    <row r="55" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H54" t="str" cm="1">
+        <f t="array" ref="H54">_xlfn.IFS(G54="","",G54&gt;1000,"Hard",AND(G54&gt;150,G54&lt;=1000),"Medium",AND(G54&gt;0,G54&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="55" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A55" s="3" t="s">
         <v>157</v>
       </c>
@@ -2768,12 +3411,19 @@
         <f t="array" aca="1" ref="E55" ca="1">_xlfn.IFNA(_xlfn.IFS(D55&lt;6,1,D55&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F55" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G55" s="8">
         <f t="shared" si="0"/>
         <v>91</v>
       </c>
-    </row>
-    <row r="56" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H55" t="str" cm="1">
+        <f t="array" ref="H55">_xlfn.IFS(G55="","",G55&gt;1000,"Hard",AND(G55&gt;150,G55&lt;=1000),"Medium",AND(G55&gt;0,G55&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="56" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>158</v>
       </c>
@@ -2792,12 +3442,19 @@
         <f t="array" aca="1" ref="E56" ca="1">_xlfn.IFNA(_xlfn.IFS(D56&lt;6,1,D56&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F56" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G56" s="8">
         <f t="shared" si="0"/>
         <v>113</v>
       </c>
-    </row>
-    <row r="57" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H56" t="str" cm="1">
+        <f t="array" ref="H56">_xlfn.IFS(G56="","",G56&gt;1000,"Hard",AND(G56&gt;150,G56&lt;=1000),"Medium",AND(G56&gt;0,G56&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="57" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A57" s="3" t="s">
         <v>159</v>
       </c>
@@ -2816,12 +3473,19 @@
         <f t="array" aca="1" ref="E57" ca="1">_xlfn.IFNA(_xlfn.IFS(D57&lt;6,1,D57&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F57" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G57" s="8">
         <f t="shared" si="0"/>
         <v>94</v>
       </c>
-    </row>
-    <row r="58" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H57" t="str" cm="1">
+        <f t="array" ref="H57">_xlfn.IFS(G57="","",G57&gt;1000,"Hard",AND(G57&gt;150,G57&lt;=1000),"Medium",AND(G57&gt;0,G57&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="58" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A58" s="3" t="s">
         <v>161</v>
       </c>
@@ -2840,12 +3504,19 @@
         <f t="array" aca="1" ref="E58" ca="1">_xlfn.IFNA(_xlfn.IFS(D58&lt;6,1,D58&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F58" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G58" s="8">
         <f t="shared" si="0"/>
         <v>66</v>
       </c>
-    </row>
-    <row r="59" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H58" t="str" cm="1">
+        <f t="array" ref="H58">_xlfn.IFS(G58="","",G58&gt;1000,"Hard",AND(G58&gt;150,G58&lt;=1000),"Medium",AND(G58&gt;0,G58&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="59" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A59" s="3" t="s">
         <v>162</v>
       </c>
@@ -2864,12 +3535,19 @@
         <f t="array" aca="1" ref="E59" ca="1">_xlfn.IFNA(_xlfn.IFS(D59&lt;6,1,D59&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F59" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G59" s="8">
         <f t="shared" si="0"/>
         <v>118</v>
       </c>
-    </row>
-    <row r="60" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H59" t="str" cm="1">
+        <f t="array" ref="H59">_xlfn.IFS(G59="","",G59&gt;1000,"Hard",AND(G59&gt;150,G59&lt;=1000),"Medium",AND(G59&gt;0,G59&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="60" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A60" s="3" t="s">
         <v>163</v>
       </c>
@@ -2888,12 +3566,19 @@
         <f t="array" aca="1" ref="E60" ca="1">_xlfn.IFNA(_xlfn.IFS(D60&lt;6,1,D60&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F60" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G60" s="8">
         <f t="shared" si="0"/>
         <v>59</v>
       </c>
-    </row>
-    <row r="61" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H60" t="str" cm="1">
+        <f t="array" ref="H60">_xlfn.IFS(G60="","",G60&gt;1000,"Hard",AND(G60&gt;150,G60&lt;=1000),"Medium",AND(G60&gt;0,G60&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="61" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A61" s="3" t="s">
         <v>164</v>
       </c>
@@ -2912,12 +3597,19 @@
         <f t="array" aca="1" ref="E61" ca="1">_xlfn.IFNA(_xlfn.IFS(D61&lt;6,1,D61&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F61" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G61" s="8">
         <f t="shared" si="0"/>
         <v>55</v>
       </c>
-    </row>
-    <row r="62" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H61" t="str" cm="1">
+        <f t="array" ref="H61">_xlfn.IFS(G61="","",G61&gt;1000,"Hard",AND(G61&gt;150,G61&lt;=1000),"Medium",AND(G61&gt;0,G61&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="62" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A62" s="3" t="s">
         <v>165</v>
       </c>
@@ -2936,12 +3628,19 @@
         <f t="array" aca="1" ref="E62" ca="1">_xlfn.IFNA(_xlfn.IFS(D62&lt;6,1,D62&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F62" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G62" s="8">
         <f t="shared" si="0"/>
         <v>48</v>
       </c>
-    </row>
-    <row r="63" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H62" t="str" cm="1">
+        <f t="array" ref="H62">_xlfn.IFS(G62="","",G62&gt;1000,"Hard",AND(G62&gt;150,G62&lt;=1000),"Medium",AND(G62&gt;0,G62&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="63" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A63" s="3" t="s">
         <v>166</v>
       </c>
@@ -2960,12 +3659,19 @@
         <f t="array" aca="1" ref="E63" ca="1">_xlfn.IFNA(_xlfn.IFS(D63&lt;6,1,D63&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F63" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G63" s="8">
         <f t="shared" si="0"/>
         <v>50</v>
       </c>
-    </row>
-    <row r="64" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H63" t="str" cm="1">
+        <f t="array" ref="H63">_xlfn.IFS(G63="","",G63&gt;1000,"Hard",AND(G63&gt;150,G63&lt;=1000),"Medium",AND(G63&gt;0,G63&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="64" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A64" s="3" t="s">
         <v>169</v>
       </c>
@@ -2984,12 +3690,19 @@
         <f t="array" aca="1" ref="E64" ca="1">_xlfn.IFNA(_xlfn.IFS(D64&lt;6,1,D64&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F64" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G64" s="8">
         <f t="shared" si="0"/>
         <v>68</v>
       </c>
-    </row>
-    <row r="65" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H64" t="str" cm="1">
+        <f t="array" ref="H64">_xlfn.IFS(G64="","",G64&gt;1000,"Hard",AND(G64&gt;150,G64&lt;=1000),"Medium",AND(G64&gt;0,G64&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="65" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A65" s="3" t="s">
         <v>170</v>
       </c>
@@ -3008,12 +3721,19 @@
         <f t="array" aca="1" ref="E65" ca="1">_xlfn.IFNA(_xlfn.IFS(D65&lt;6,1,D65&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F65" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G65" s="8">
         <f t="shared" si="0"/>
         <v>57</v>
       </c>
-    </row>
-    <row r="66" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H65" t="str" cm="1">
+        <f t="array" ref="H65">_xlfn.IFS(G65="","",G65&gt;1000,"Hard",AND(G65&gt;150,G65&lt;=1000),"Medium",AND(G65&gt;0,G65&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="66" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A66" s="3" t="s">
         <v>171</v>
       </c>
@@ -3032,12 +3752,19 @@
         <f t="array" aca="1" ref="E66" ca="1">_xlfn.IFNA(_xlfn.IFS(D66&lt;6,1,D66&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F66" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G66" s="8">
-        <f t="shared" si="0"/>
+        <f t="shared" ref="G66:G82" si="1">IF(LEN(A66)=0,"",LEN(A66))</f>
         <v>62</v>
       </c>
-    </row>
-    <row r="67" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H66" t="str" cm="1">
+        <f t="array" ref="H66">_xlfn.IFS(G66="","",G66&gt;1000,"Hard",AND(G66&gt;150,G66&lt;=1000),"Medium",AND(G66&gt;0,G66&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="67" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A67" s="3" t="s">
         <v>172</v>
       </c>
@@ -3056,912 +3783,1569 @@
         <f t="array" aca="1" ref="E67" ca="1">_xlfn.IFNA(_xlfn.IFS(D67&lt;6,1,D67&lt;12,2),"")</f>
         <v>1</v>
       </c>
+      <c r="F67" s="8" t="s">
+        <v>168</v>
+      </c>
       <c r="G67" s="8">
-        <f t="shared" ref="G67:G130" si="1">IF(LEN(A67)=0,"",LEN(A67))</f>
+        <f t="shared" si="1"/>
         <v>251</v>
       </c>
-    </row>
-    <row r="68" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="H67" t="str" cm="1">
+        <f t="array" ref="H67">_xlfn.IFS(G67="","",G67&gt;1000,"Hard",AND(G67&gt;150,G67&lt;=1000),"Medium",AND(G67&gt;0,G67&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="68" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A68" s="4" t="s">
+        <v>174</v>
+      </c>
       <c r="B68" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D68" s="6" t="str" cm="1">
+      <c r="C68" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D68" s="6" cm="1">
         <f t="array" aca="1" ref="D68" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C68, MATCH(FALSE, ISNUMBER(MID(C68, ROW(INDIRECT("1:"&amp;LEN(C68)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E68" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E68" s="7" cm="1">
         <f t="array" aca="1" ref="E68" ca="1">_xlfn.IFNA(_xlfn.IFS(D68&lt;6,1,D68&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G68" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F68" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G68" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="69" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1125</v>
+      </c>
+      <c r="H68" t="str" cm="1">
+        <f t="array" ref="H68">_xlfn.IFS(G68="","",G68&gt;1000,"Hard",AND(G68&gt;150,G68&lt;=1000),"Medium",AND(G68&gt;0,G68&lt;=150),"Easy")</f>
+        <v>Hard</v>
+      </c>
+    </row>
+    <row r="69" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A69" s="3" t="s">
+        <v>176</v>
+      </c>
       <c r="B69" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D69" s="6" t="str" cm="1">
+      <c r="C69" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D69" s="6" cm="1">
         <f t="array" aca="1" ref="D69" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C69, MATCH(FALSE, ISNUMBER(MID(C69, ROW(INDIRECT("1:"&amp;LEN(C69)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E69" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E69" s="7" cm="1">
         <f t="array" aca="1" ref="E69" ca="1">_xlfn.IFNA(_xlfn.IFS(D69&lt;6,1,D69&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G69" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F69" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G69" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="70" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>102</v>
+      </c>
+      <c r="H69" t="str" cm="1">
+        <f t="array" ref="H69">_xlfn.IFS(G69="","",G69&gt;1000,"Hard",AND(G69&gt;150,G69&lt;=1000),"Medium",AND(G69&gt;0,G69&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="70" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A70" s="3" t="s">
+        <v>177</v>
+      </c>
       <c r="B70" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D70" s="6" t="str" cm="1">
+      <c r="C70" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D70" s="6" cm="1">
         <f t="array" aca="1" ref="D70" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C70, MATCH(FALSE, ISNUMBER(MID(C70, ROW(INDIRECT("1:"&amp;LEN(C70)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E70" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E70" s="7" cm="1">
         <f t="array" aca="1" ref="E70" ca="1">_xlfn.IFNA(_xlfn.IFS(D70&lt;6,1,D70&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G70" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F70" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G70" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="71" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>46</v>
+      </c>
+      <c r="H70" t="str" cm="1">
+        <f t="array" ref="H70">_xlfn.IFS(G70="","",G70&gt;1000,"Hard",AND(G70&gt;150,G70&lt;=1000),"Medium",AND(G70&gt;0,G70&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="71" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A71" s="3" t="s">
+        <v>178</v>
+      </c>
       <c r="B71" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D71" s="6" t="str" cm="1">
+      <c r="C71" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D71" s="6" cm="1">
         <f t="array" aca="1" ref="D71" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C71, MATCH(FALSE, ISNUMBER(MID(C71, ROW(INDIRECT("1:"&amp;LEN(C71)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E71" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E71" s="7" cm="1">
         <f t="array" aca="1" ref="E71" ca="1">_xlfn.IFNA(_xlfn.IFS(D71&lt;6,1,D71&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G71" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F71" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G71" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="72" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="H71" t="str" cm="1">
+        <f t="array" ref="H71">_xlfn.IFS(G71="","",G71&gt;1000,"Hard",AND(G71&gt;150,G71&lt;=1000),"Medium",AND(G71&gt;0,G71&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="72" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A72" s="4" t="s">
+        <v>179</v>
+      </c>
       <c r="B72" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D72" s="6" t="str" cm="1">
+      <c r="C72" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="D72" s="6" cm="1">
         <f t="array" aca="1" ref="D72" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C72, MATCH(FALSE, ISNUMBER(MID(C72, ROW(INDIRECT("1:"&amp;LEN(C72)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E72" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E72" s="7" cm="1">
         <f t="array" aca="1" ref="E72" ca="1">_xlfn.IFNA(_xlfn.IFS(D72&lt;6,1,D72&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G72" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F72" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G72" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="73" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>736</v>
+      </c>
+      <c r="H72" t="str" cm="1">
+        <f t="array" ref="H72">_xlfn.IFS(G72="","",G72&gt;1000,"Hard",AND(G72&gt;150,G72&lt;=1000),"Medium",AND(G72&gt;0,G72&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="73" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A73" s="3" t="s">
+        <v>180</v>
+      </c>
       <c r="B73" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D73" s="6" t="str" cm="1">
+      <c r="C73" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="D73" s="6" cm="1">
         <f t="array" aca="1" ref="D73" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C73, MATCH(FALSE, ISNUMBER(MID(C73, ROW(INDIRECT("1:"&amp;LEN(C73)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E73" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E73" s="7" cm="1">
         <f t="array" aca="1" ref="E73" ca="1">_xlfn.IFNA(_xlfn.IFS(D73&lt;6,1,D73&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G73" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F73" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G73" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="74" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>40</v>
+      </c>
+      <c r="H73" t="str" cm="1">
+        <f t="array" ref="H73">_xlfn.IFS(G73="","",G73&gt;1000,"Hard",AND(G73&gt;150,G73&lt;=1000),"Medium",AND(G73&gt;0,G73&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="74" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A74" s="3" t="s">
+        <v>181</v>
+      </c>
       <c r="B74" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D74" s="6" t="str" cm="1">
+      <c r="C74" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D74" s="6" cm="1">
         <f t="array" aca="1" ref="D74" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C74, MATCH(FALSE, ISNUMBER(MID(C74, ROW(INDIRECT("1:"&amp;LEN(C74)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E74" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E74" s="7" cm="1">
         <f t="array" aca="1" ref="E74" ca="1">_xlfn.IFNA(_xlfn.IFS(D74&lt;6,1,D74&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G74" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F74" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G74" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="75" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>31</v>
+      </c>
+      <c r="H74" t="str" cm="1">
+        <f t="array" ref="H74">_xlfn.IFS(G74="","",G74&gt;1000,"Hard",AND(G74&gt;150,G74&lt;=1000),"Medium",AND(G74&gt;0,G74&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="75" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A75" s="3" t="s">
+        <v>182</v>
+      </c>
       <c r="B75" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D75" s="6" t="str" cm="1">
+      <c r="C75" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D75" s="6" cm="1">
         <f t="array" aca="1" ref="D75" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C75, MATCH(FALSE, ISNUMBER(MID(C75, ROW(INDIRECT("1:"&amp;LEN(C75)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E75" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E75" s="7" cm="1">
         <f t="array" aca="1" ref="E75" ca="1">_xlfn.IFNA(_xlfn.IFS(D75&lt;6,1,D75&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G75" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F75" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G75" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="76" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>49</v>
+      </c>
+      <c r="H75" t="str" cm="1">
+        <f t="array" ref="H75">_xlfn.IFS(G75="","",G75&gt;1000,"Hard",AND(G75&gt;150,G75&lt;=1000),"Medium",AND(G75&gt;0,G75&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="76" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A76" s="3" t="s">
+        <v>183</v>
+      </c>
       <c r="B76" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D76" s="6" t="str" cm="1">
+      <c r="C76" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D76" s="6" cm="1">
         <f t="array" aca="1" ref="D76" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C76, MATCH(FALSE, ISNUMBER(MID(C76, ROW(INDIRECT("1:"&amp;LEN(C76)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E76" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E76" s="7" cm="1">
         <f t="array" aca="1" ref="E76" ca="1">_xlfn.IFNA(_xlfn.IFS(D76&lt;6,1,D76&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G76" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F76" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G76" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="77" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>60</v>
+      </c>
+      <c r="H76" t="str" cm="1">
+        <f t="array" ref="H76">_xlfn.IFS(G76="","",G76&gt;1000,"Hard",AND(G76&gt;150,G76&lt;=1000),"Medium",AND(G76&gt;0,G76&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="77" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A77" s="3" t="s">
+        <v>184</v>
+      </c>
       <c r="B77" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D77" s="6" t="str" cm="1">
+      <c r="C77" s="5" t="s">
+        <v>33</v>
+      </c>
+      <c r="D77" s="6" cm="1">
         <f t="array" aca="1" ref="D77" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C77, MATCH(FALSE, ISNUMBER(MID(C77, ROW(INDIRECT("1:"&amp;LEN(C77)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E77" s="7" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="E77" s="7" cm="1">
         <f t="array" aca="1" ref="E77" ca="1">_xlfn.IFNA(_xlfn.IFS(D77&lt;6,1,D77&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G77" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F77" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G77" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="78" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>68</v>
+      </c>
+      <c r="H77" t="str" cm="1">
+        <f t="array" ref="H77">_xlfn.IFS(G77="","",G77&gt;1000,"Hard",AND(G77&gt;150,G77&lt;=1000),"Medium",AND(G77&gt;0,G77&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="78" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A78" s="3" t="s">
+        <v>185</v>
+      </c>
       <c r="B78" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D78" s="6" t="str" cm="1">
+      <c r="C78" s="5" t="s">
+        <v>51</v>
+      </c>
+      <c r="D78" s="6" cm="1">
         <f t="array" aca="1" ref="D78" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C78, MATCH(FALSE, ISNUMBER(MID(C78, ROW(INDIRECT("1:"&amp;LEN(C78)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E78" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E78" s="7" cm="1">
         <f t="array" aca="1" ref="E78" ca="1">_xlfn.IFNA(_xlfn.IFS(D78&lt;6,1,D78&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G78" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F78" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G78" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="79" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>103</v>
+      </c>
+      <c r="H78" t="str" cm="1">
+        <f t="array" ref="H78">_xlfn.IFS(G78="","",G78&gt;1000,"Hard",AND(G78&gt;150,G78&lt;=1000),"Medium",AND(G78&gt;0,G78&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="79" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A79" s="3" t="s">
+        <v>186</v>
+      </c>
       <c r="B79" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D79" s="6" t="str" cm="1">
+      <c r="C79" s="5" t="s">
+        <v>15</v>
+      </c>
+      <c r="D79" s="6" cm="1">
         <f t="array" aca="1" ref="D79" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C79, MATCH(FALSE, ISNUMBER(MID(C79, ROW(INDIRECT("1:"&amp;LEN(C79)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E79" s="7" t="str" cm="1">
+        <v>2</v>
+      </c>
+      <c r="E79" s="7" cm="1">
         <f t="array" aca="1" ref="E79" ca="1">_xlfn.IFNA(_xlfn.IFS(D79&lt;6,1,D79&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G79" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F79" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G79" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="80" spans="1:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>52</v>
+      </c>
+      <c r="H79" t="str" cm="1">
+        <f t="array" ref="H79">_xlfn.IFS(G79="","",G79&gt;1000,"Hard",AND(G79&gt;150,G79&lt;=1000),"Medium",AND(G79&gt;0,G79&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="80" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A80" s="3" t="s">
+        <v>187</v>
+      </c>
       <c r="B80" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D80" s="6" t="str" cm="1">
+      <c r="C80" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D80" s="6" cm="1">
         <f t="array" aca="1" ref="D80" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C80, MATCH(FALSE, ISNUMBER(MID(C80, ROW(INDIRECT("1:"&amp;LEN(C80)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E80" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E80" s="7" cm="1">
         <f t="array" aca="1" ref="E80" ca="1">_xlfn.IFNA(_xlfn.IFS(D80&lt;6,1,D80&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G80" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F80" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G80" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="81" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>54</v>
+      </c>
+      <c r="H80" t="str" cm="1">
+        <f t="array" ref="H80">_xlfn.IFS(G80="","",G80&gt;1000,"Hard",AND(G80&gt;150,G80&lt;=1000),"Medium",AND(G80&gt;0,G80&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="81" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A81" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="B81" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D81" s="6" t="str" cm="1">
+      <c r="C81" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="D81" s="6" cm="1">
         <f t="array" aca="1" ref="D81" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C81, MATCH(FALSE, ISNUMBER(MID(C81, ROW(INDIRECT("1:"&amp;LEN(C81)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E81" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E81" s="7" cm="1">
         <f t="array" aca="1" ref="E81" ca="1">_xlfn.IFNA(_xlfn.IFS(D81&lt;6,1,D81&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G81" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F81" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G81" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="82" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>57</v>
+      </c>
+      <c r="H81" t="str" cm="1">
+        <f t="array" ref="H81">_xlfn.IFS(G81="","",G81&gt;1000,"Hard",AND(G81&gt;150,G81&lt;=1000),"Medium",AND(G81&gt;0,G81&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="82" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A82" s="3" t="s">
+        <v>189</v>
+      </c>
       <c r="B82" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D82" s="6" t="str" cm="1">
+      <c r="C82" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D82" s="6" cm="1">
         <f t="array" aca="1" ref="D82" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C82, MATCH(FALSE, ISNUMBER(MID(C82, ROW(INDIRECT("1:"&amp;LEN(C82)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E82" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E82" s="7" cm="1">
         <f t="array" aca="1" ref="E82" ca="1">_xlfn.IFNA(_xlfn.IFS(D82&lt;6,1,D82&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G82" s="8" t="str">
+        <v>2</v>
+      </c>
+      <c r="F82" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G82" s="8">
         <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="83" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>82</v>
+      </c>
+      <c r="H82" t="str" cm="1">
+        <f t="array" ref="H82">_xlfn.IFS(G82="","",G82&gt;1000,"Hard",AND(G82&gt;150,G82&lt;=1000),"Medium",AND(G82&gt;0,G82&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="83" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A83" s="3" t="s">
+        <v>190</v>
+      </c>
       <c r="B83" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D83" s="6" t="str" cm="1">
+      <c r="C83" s="5" t="s">
+        <v>40</v>
+      </c>
+      <c r="D83" s="6" cm="1">
         <f t="array" aca="1" ref="D83" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C83, MATCH(FALSE, ISNUMBER(MID(C83, ROW(INDIRECT("1:"&amp;LEN(C83)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E83" s="7" t="str" cm="1">
+        <v>6</v>
+      </c>
+      <c r="E83" s="7" cm="1">
         <f t="array" aca="1" ref="E83" ca="1">_xlfn.IFNA(_xlfn.IFS(D83&lt;6,1,D83&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G83" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="84" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F83" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G83" s="8">
+        <f>IF(LEN(A83)=0,"",LEN(A83))</f>
+        <v>96</v>
+      </c>
+      <c r="H83" t="str" cm="1">
+        <f t="array" ref="H83">_xlfn.IFS(G83="","",G83&gt;1000,"Hard",AND(G83&gt;150,G83&lt;=1000),"Medium",AND(G83&gt;0,G83&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="84" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A84" s="3" t="s">
+        <v>191</v>
+      </c>
       <c r="B84" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D84" s="6" t="str" cm="1">
+      <c r="C84" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D84" s="6" cm="1">
         <f t="array" aca="1" ref="D84" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C84, MATCH(FALSE, ISNUMBER(MID(C84, ROW(INDIRECT("1:"&amp;LEN(C84)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E84" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E84" s="7" cm="1">
         <f t="array" aca="1" ref="E84" ca="1">_xlfn.IFNA(_xlfn.IFS(D84&lt;6,1,D84&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G84" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="85" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F84" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G84" s="8">
+        <f t="shared" ref="G84:G130" si="2">IF(LEN(A84)=0,"",LEN(A84))</f>
+        <v>73</v>
+      </c>
+      <c r="H84" t="str" cm="1">
+        <f t="array" ref="H84">_xlfn.IFS(G84="","",G84&gt;1000,"Hard",AND(G84&gt;150,G84&lt;=1000),"Medium",AND(G84&gt;0,G84&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="85" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A85" s="3" t="s">
+        <v>192</v>
+      </c>
       <c r="B85" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D85" s="6" t="str" cm="1">
+      <c r="C85" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D85" s="6" cm="1">
         <f t="array" aca="1" ref="D85" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C85, MATCH(FALSE, ISNUMBER(MID(C85, ROW(INDIRECT("1:"&amp;LEN(C85)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E85" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E85" s="7" cm="1">
         <f t="array" aca="1" ref="E85" ca="1">_xlfn.IFNA(_xlfn.IFS(D85&lt;6,1,D85&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G85" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="86" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F85" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G85" s="8">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="H85" t="str" cm="1">
+        <f t="array" ref="H85">_xlfn.IFS(G85="","",G85&gt;1000,"Hard",AND(G85&gt;150,G85&lt;=1000),"Medium",AND(G85&gt;0,G85&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="86" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A86" s="3" t="s">
+        <v>193</v>
+      </c>
       <c r="B86" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D86" s="6" t="str" cm="1">
+      <c r="C86" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="D86" s="6" cm="1">
         <f t="array" aca="1" ref="D86" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C86, MATCH(FALSE, ISNUMBER(MID(C86, ROW(INDIRECT("1:"&amp;LEN(C86)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E86" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E86" s="7" cm="1">
         <f t="array" aca="1" ref="E86" ca="1">_xlfn.IFNA(_xlfn.IFS(D86&lt;6,1,D86&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G86" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="87" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F86" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G86" s="8">
+        <f t="shared" si="2"/>
+        <v>124</v>
+      </c>
+      <c r="H86" t="str" cm="1">
+        <f t="array" ref="H86">_xlfn.IFS(G86="","",G86&gt;1000,"Hard",AND(G86&gt;150,G86&lt;=1000),"Medium",AND(G86&gt;0,G86&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="87" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A87" s="3" t="s">
+        <v>194</v>
+      </c>
       <c r="B87" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D87" s="6" t="str" cm="1">
+      <c r="C87" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D87" s="6" cm="1">
         <f t="array" aca="1" ref="D87" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C87, MATCH(FALSE, ISNUMBER(MID(C87, ROW(INDIRECT("1:"&amp;LEN(C87)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E87" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E87" s="7" cm="1">
         <f t="array" aca="1" ref="E87" ca="1">_xlfn.IFNA(_xlfn.IFS(D87&lt;6,1,D87&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G87" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="88" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F87" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G87" s="8">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="H87" t="str" cm="1">
+        <f t="array" ref="H87">_xlfn.IFS(G87="","",G87&gt;1000,"Hard",AND(G87&gt;150,G87&lt;=1000),"Medium",AND(G87&gt;0,G87&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="88" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A88" s="3" t="s">
+        <v>195</v>
+      </c>
       <c r="B88" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D88" s="6" t="str" cm="1">
+      <c r="C88" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="D88" s="6" cm="1">
         <f t="array" aca="1" ref="D88" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C88, MATCH(FALSE, ISNUMBER(MID(C88, ROW(INDIRECT("1:"&amp;LEN(C88)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E88" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E88" s="7" cm="1">
         <f t="array" aca="1" ref="E88" ca="1">_xlfn.IFNA(_xlfn.IFS(D88&lt;6,1,D88&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G88" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="89" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F88" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G88" s="8">
+        <f t="shared" si="2"/>
+        <v>54</v>
+      </c>
+      <c r="H88" t="str" cm="1">
+        <f t="array" ref="H88">_xlfn.IFS(G88="","",G88&gt;1000,"Hard",AND(G88&gt;150,G88&lt;=1000),"Medium",AND(G88&gt;0,G88&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="89" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A89" s="3" t="s">
+        <v>196</v>
+      </c>
       <c r="B89" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D89" s="6" t="str" cm="1">
+      <c r="C89" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="D89" s="6" cm="1">
         <f t="array" aca="1" ref="D89" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C89, MATCH(FALSE, ISNUMBER(MID(C89, ROW(INDIRECT("1:"&amp;LEN(C89)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E89" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E89" s="7" cm="1">
         <f t="array" aca="1" ref="E89" ca="1">_xlfn.IFNA(_xlfn.IFS(D89&lt;6,1,D89&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G89" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="90" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F89" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G89" s="8">
+        <f t="shared" si="2"/>
+        <v>49</v>
+      </c>
+      <c r="H89" t="str" cm="1">
+        <f t="array" ref="H89">_xlfn.IFS(G89="","",G89&gt;1000,"Hard",AND(G89&gt;150,G89&lt;=1000),"Medium",AND(G89&gt;0,G89&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="90" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A90" s="4" t="s">
+        <v>197</v>
+      </c>
       <c r="B90" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D90" s="6" t="str" cm="1">
+      <c r="C90" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="D90" s="6" cm="1">
         <f t="array" aca="1" ref="D90" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C90, MATCH(FALSE, ISNUMBER(MID(C90, ROW(INDIRECT("1:"&amp;LEN(C90)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E90" s="7" t="str" cm="1">
+        <v>4</v>
+      </c>
+      <c r="E90" s="7" cm="1">
         <f t="array" aca="1" ref="E90" ca="1">_xlfn.IFNA(_xlfn.IFS(D90&lt;6,1,D90&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G90" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="91" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>1</v>
+      </c>
+      <c r="F90" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G90" s="8">
+        <f t="shared" si="2"/>
+        <v>53</v>
+      </c>
+      <c r="H90" t="str" cm="1">
+        <f t="array" ref="H90">_xlfn.IFS(G90="","",G90&gt;1000,"Hard",AND(G90&gt;150,G90&lt;=1000),"Medium",AND(G90&gt;0,G90&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="91" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A91" s="4" t="s">
+        <v>198</v>
+      </c>
       <c r="B91" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D91" s="6" t="str" cm="1">
+      <c r="C91" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D91" s="6" cm="1">
         <f t="array" aca="1" ref="D91" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C91, MATCH(FALSE, ISNUMBER(MID(C91, ROW(INDIRECT("1:"&amp;LEN(C91)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E91" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E91" s="7" cm="1">
         <f t="array" aca="1" ref="E91" ca="1">_xlfn.IFNA(_xlfn.IFS(D91&lt;6,1,D91&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G91" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="92" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F91" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G91" s="8">
+        <f t="shared" si="2"/>
+        <v>491</v>
+      </c>
+      <c r="H91" t="str" cm="1">
+        <f t="array" ref="H91">_xlfn.IFS(G91="","",G91&gt;1000,"Hard",AND(G91&gt;150,G91&lt;=1000),"Medium",AND(G91&gt;0,G91&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="92" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A92" s="4" t="s">
+        <v>199</v>
+      </c>
       <c r="B92" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D92" s="6" t="str" cm="1">
+      <c r="C92" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="D92" s="6" cm="1">
         <f t="array" aca="1" ref="D92" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C92, MATCH(FALSE, ISNUMBER(MID(C92, ROW(INDIRECT("1:"&amp;LEN(C92)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E92" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E92" s="7" cm="1">
         <f t="array" aca="1" ref="E92" ca="1">_xlfn.IFNA(_xlfn.IFS(D92&lt;6,1,D92&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G92" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="93" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F92" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G92" s="8">
+        <f t="shared" si="2"/>
+        <v>257</v>
+      </c>
+      <c r="H92" t="str" cm="1">
+        <f t="array" ref="H92">_xlfn.IFS(G92="","",G92&gt;1000,"Hard",AND(G92&gt;150,G92&lt;=1000),"Medium",AND(G92&gt;0,G92&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="93" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A93" s="3" t="s">
+        <v>204</v>
+      </c>
       <c r="B93" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D93" s="6" t="str" cm="1">
+      <c r="C93" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D93" s="6" cm="1">
         <f t="array" aca="1" ref="D93" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C93, MATCH(FALSE, ISNUMBER(MID(C93, ROW(INDIRECT("1:"&amp;LEN(C93)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E93" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E93" s="7" cm="1">
         <f t="array" aca="1" ref="E93" ca="1">_xlfn.IFNA(_xlfn.IFS(D93&lt;6,1,D93&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G93" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="94" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F93" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G93" s="8">
+        <f t="shared" si="2"/>
+        <v>70</v>
+      </c>
+      <c r="H93" t="str" cm="1">
+        <f t="array" ref="H93">_xlfn.IFS(G93="","",G93&gt;1000,"Hard",AND(G93&gt;150,G93&lt;=1000),"Medium",AND(G93&gt;0,G93&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="94" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A94" s="3" t="s">
+        <v>201</v>
+      </c>
       <c r="B94" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D94" s="6" t="str" cm="1">
+      <c r="C94" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D94" s="6" cm="1">
         <f t="array" aca="1" ref="D94" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C94, MATCH(FALSE, ISNUMBER(MID(C94, ROW(INDIRECT("1:"&amp;LEN(C94)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E94" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E94" s="7" cm="1">
         <f t="array" aca="1" ref="E94" ca="1">_xlfn.IFNA(_xlfn.IFS(D94&lt;6,1,D94&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G94" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="95" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F94" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G94" s="8">
+        <f t="shared" si="2"/>
+        <v>67</v>
+      </c>
+      <c r="H94" t="str" cm="1">
+        <f t="array" ref="H94">_xlfn.IFS(G94="","",G94&gt;1000,"Hard",AND(G94&gt;150,G94&lt;=1000),"Medium",AND(G94&gt;0,G94&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="95" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A95" s="3" t="s">
+        <v>202</v>
+      </c>
       <c r="B95" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D95" s="6" t="str" cm="1">
+      <c r="C95" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D95" s="6" cm="1">
         <f t="array" aca="1" ref="D95" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C95, MATCH(FALSE, ISNUMBER(MID(C95, ROW(INDIRECT("1:"&amp;LEN(C95)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E95" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E95" s="7" cm="1">
         <f t="array" aca="1" ref="E95" ca="1">_xlfn.IFNA(_xlfn.IFS(D95&lt;6,1,D95&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G95" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="96" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F95" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G95" s="8">
+        <f t="shared" si="2"/>
+        <v>68</v>
+      </c>
+      <c r="H95" t="str" cm="1">
+        <f t="array" ref="H95">_xlfn.IFS(G95="","",G95&gt;1000,"Hard",AND(G95&gt;150,G95&lt;=1000),"Medium",AND(G95&gt;0,G95&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="96" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A96" s="3" t="s">
+        <v>203</v>
+      </c>
       <c r="B96" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D96" s="6" t="str" cm="1">
+      <c r="C96" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D96" s="6" cm="1">
         <f t="array" aca="1" ref="D96" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C96, MATCH(FALSE, ISNUMBER(MID(C96, ROW(INDIRECT("1:"&amp;LEN(C96)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E96" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E96" s="7" cm="1">
         <f t="array" aca="1" ref="E96" ca="1">_xlfn.IFNA(_xlfn.IFS(D96&lt;6,1,D96&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G96" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="97" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F96" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G96" s="8">
+        <f t="shared" si="2"/>
+        <v>64</v>
+      </c>
+      <c r="H96" t="str" cm="1">
+        <f t="array" ref="H96">_xlfn.IFS(G96="","",G96&gt;1000,"Hard",AND(G96&gt;150,G96&lt;=1000),"Medium",AND(G96&gt;0,G96&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="97" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A97" s="4" t="s">
+        <v>200</v>
+      </c>
       <c r="B97" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D97" s="6" t="str" cm="1">
+      <c r="C97" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D97" s="6" cm="1">
         <f t="array" aca="1" ref="D97" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C97, MATCH(FALSE, ISNUMBER(MID(C97, ROW(INDIRECT("1:"&amp;LEN(C97)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E97" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E97" s="7" cm="1">
         <f t="array" aca="1" ref="E97" ca="1">_xlfn.IFNA(_xlfn.IFS(D97&lt;6,1,D97&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G97" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="98" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F97" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G97" s="8">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="H97" t="str" cm="1">
+        <f t="array" ref="H97">_xlfn.IFS(G97="","",G97&gt;1000,"Hard",AND(G97&gt;150,G97&lt;=1000),"Medium",AND(G97&gt;0,G97&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="98" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A98" s="4" t="s">
+        <v>205</v>
+      </c>
       <c r="B98" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D98" s="6" t="str" cm="1">
+      <c r="C98" s="5" t="s">
+        <v>57</v>
+      </c>
+      <c r="D98" s="6" cm="1">
         <f t="array" aca="1" ref="D98" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C98, MATCH(FALSE, ISNUMBER(MID(C98, ROW(INDIRECT("1:"&amp;LEN(C98)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E98" s="7" t="str" cm="1">
+        <v>7</v>
+      </c>
+      <c r="E98" s="7" cm="1">
         <f t="array" aca="1" ref="E98" ca="1">_xlfn.IFNA(_xlfn.IFS(D98&lt;6,1,D98&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G98" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="99" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F98" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G98" s="8">
+        <f t="shared" si="2"/>
+        <v>84</v>
+      </c>
+      <c r="H98" t="str" cm="1">
+        <f t="array" ref="H98">_xlfn.IFS(G98="","",G98&gt;1000,"Hard",AND(G98&gt;150,G98&lt;=1000),"Medium",AND(G98&gt;0,G98&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="99" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A99" s="3" t="s">
+        <v>206</v>
+      </c>
       <c r="B99" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D99" s="6" t="str" cm="1">
+      <c r="C99" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D99" s="6" cm="1">
         <f t="array" aca="1" ref="D99" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C99, MATCH(FALSE, ISNUMBER(MID(C99, ROW(INDIRECT("1:"&amp;LEN(C99)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E99" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E99" s="7" cm="1">
         <f t="array" aca="1" ref="E99" ca="1">_xlfn.IFNA(_xlfn.IFS(D99&lt;6,1,D99&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G99" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="100" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F99" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G99" s="8">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+      <c r="H99" t="str" cm="1">
+        <f t="array" ref="H99">_xlfn.IFS(G99="","",G99&gt;1000,"Hard",AND(G99&gt;150,G99&lt;=1000),"Medium",AND(G99&gt;0,G99&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="100" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A100" s="3" t="s">
+        <v>207</v>
+      </c>
       <c r="B100" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D100" s="6" t="str" cm="1">
+      <c r="C100" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D100" s="6" cm="1">
         <f t="array" aca="1" ref="D100" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C100, MATCH(FALSE, ISNUMBER(MID(C100, ROW(INDIRECT("1:"&amp;LEN(C100)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E100" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E100" s="7" cm="1">
         <f t="array" aca="1" ref="E100" ca="1">_xlfn.IFNA(_xlfn.IFS(D100&lt;6,1,D100&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G100" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="101" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F100" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G100" s="8">
+        <f t="shared" si="2"/>
+        <v>80</v>
+      </c>
+      <c r="H100" t="str" cm="1">
+        <f t="array" ref="H100">_xlfn.IFS(G100="","",G100&gt;1000,"Hard",AND(G100&gt;150,G100&lt;=1000),"Medium",AND(G100&gt;0,G100&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="101" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A101" s="3" t="s">
+        <v>208</v>
+      </c>
       <c r="B101" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D101" s="6" t="str" cm="1">
+      <c r="C101" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D101" s="6" cm="1">
         <f t="array" aca="1" ref="D101" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C101, MATCH(FALSE, ISNUMBER(MID(C101, ROW(INDIRECT("1:"&amp;LEN(C101)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E101" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E101" s="7" cm="1">
         <f t="array" aca="1" ref="E101" ca="1">_xlfn.IFNA(_xlfn.IFS(D101&lt;6,1,D101&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G101" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="102" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F101" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G101" s="8">
+        <f t="shared" si="2"/>
+        <v>100</v>
+      </c>
+      <c r="H101" t="str" cm="1">
+        <f t="array" ref="H101">_xlfn.IFS(G101="","",G101&gt;1000,"Hard",AND(G101&gt;150,G101&lt;=1000),"Medium",AND(G101&gt;0,G101&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="102" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A102" s="3" t="s">
+        <v>209</v>
+      </c>
       <c r="B102" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D102" s="6" t="str" cm="1">
+      <c r="C102" s="5" t="s">
+        <v>76</v>
+      </c>
+      <c r="D102" s="6" cm="1">
         <f t="array" aca="1" ref="D102" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C102, MATCH(FALSE, ISNUMBER(MID(C102, ROW(INDIRECT("1:"&amp;LEN(C102)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E102" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E102" s="7" cm="1">
         <f t="array" aca="1" ref="E102" ca="1">_xlfn.IFNA(_xlfn.IFS(D102&lt;6,1,D102&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G102" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="103" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F102" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G102" s="8">
+        <f t="shared" si="2"/>
+        <v>82</v>
+      </c>
+      <c r="H102" t="str" cm="1">
+        <f t="array" ref="H102">_xlfn.IFS(G102="","",G102&gt;1000,"Hard",AND(G102&gt;150,G102&lt;=1000),"Medium",AND(G102&gt;0,G102&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="103" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A103" s="3" t="s">
+        <v>210</v>
+      </c>
       <c r="B103" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D103" s="6" t="str" cm="1">
+      <c r="C103" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D103" s="6" cm="1">
         <f t="array" aca="1" ref="D103" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C103, MATCH(FALSE, ISNUMBER(MID(C103, ROW(INDIRECT("1:"&amp;LEN(C103)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E103" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E103" s="7" cm="1">
         <f t="array" aca="1" ref="E103" ca="1">_xlfn.IFNA(_xlfn.IFS(D103&lt;6,1,D103&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G103" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="104" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F103" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G103" s="8">
+        <f t="shared" si="2"/>
+        <v>259</v>
+      </c>
+      <c r="H103" t="str" cm="1">
+        <f t="array" ref="H103">_xlfn.IFS(G103="","",G103&gt;1000,"Hard",AND(G103&gt;150,G103&lt;=1000),"Medium",AND(G103&gt;0,G103&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="104" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A104" s="3" t="s">
+        <v>211</v>
+      </c>
       <c r="B104" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D104" s="6" t="str" cm="1">
+      <c r="C104" s="5" t="s">
+        <v>77</v>
+      </c>
+      <c r="D104" s="6" cm="1">
         <f t="array" aca="1" ref="D104" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C104, MATCH(FALSE, ISNUMBER(MID(C104, ROW(INDIRECT("1:"&amp;LEN(C104)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E104" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E104" s="7" cm="1">
         <f t="array" aca="1" ref="E104" ca="1">_xlfn.IFNA(_xlfn.IFS(D104&lt;6,1,D104&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G104" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="105" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F104" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G104" s="8">
+        <f t="shared" si="2"/>
+        <v>277</v>
+      </c>
+      <c r="H104" t="str" cm="1">
+        <f t="array" ref="H104">_xlfn.IFS(G104="","",G104&gt;1000,"Hard",AND(G104&gt;150,G104&lt;=1000),"Medium",AND(G104&gt;0,G104&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="105" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A105" s="3" t="s">
+        <v>212</v>
+      </c>
       <c r="B105" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D105" s="6" t="str" cm="1">
+      <c r="C105" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D105" s="6" cm="1">
         <f t="array" aca="1" ref="D105" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C105, MATCH(FALSE, ISNUMBER(MID(C105, ROW(INDIRECT("1:"&amp;LEN(C105)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E105" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E105" s="7" cm="1">
         <f t="array" aca="1" ref="E105" ca="1">_xlfn.IFNA(_xlfn.IFS(D105&lt;6,1,D105&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G105" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="106" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F105" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G105" s="8">
+        <f t="shared" si="2"/>
+        <v>96</v>
+      </c>
+      <c r="H105" t="str" cm="1">
+        <f t="array" ref="H105">_xlfn.IFS(G105="","",G105&gt;1000,"Hard",AND(G105&gt;150,G105&lt;=1000),"Medium",AND(G105&gt;0,G105&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="106" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A106" s="3" t="s">
+        <v>213</v>
+      </c>
       <c r="B106" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D106" s="6" t="str" cm="1">
+      <c r="C106" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D106" s="6" cm="1">
         <f t="array" aca="1" ref="D106" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C106, MATCH(FALSE, ISNUMBER(MID(C106, ROW(INDIRECT("1:"&amp;LEN(C106)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E106" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E106" s="7" cm="1">
         <f t="array" aca="1" ref="E106" ca="1">_xlfn.IFNA(_xlfn.IFS(D106&lt;6,1,D106&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G106" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="107" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F106" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G106" s="8">
+        <f t="shared" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="H106" t="str" cm="1">
+        <f t="array" ref="H106">_xlfn.IFS(G106="","",G106&gt;1000,"Hard",AND(G106&gt;150,G106&lt;=1000),"Medium",AND(G106&gt;0,G106&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="107" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A107" s="3" t="s">
+        <v>214</v>
+      </c>
       <c r="B107" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D107" s="6" t="str" cm="1">
+      <c r="C107" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D107" s="6" cm="1">
         <f t="array" aca="1" ref="D107" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C107, MATCH(FALSE, ISNUMBER(MID(C107, ROW(INDIRECT("1:"&amp;LEN(C107)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E107" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E107" s="7" cm="1">
         <f t="array" aca="1" ref="E107" ca="1">_xlfn.IFNA(_xlfn.IFS(D107&lt;6,1,D107&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G107" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="108" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F107" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G107" s="8">
+        <f t="shared" si="2"/>
+        <v>89</v>
+      </c>
+      <c r="H107" t="str" cm="1">
+        <f t="array" ref="H107">_xlfn.IFS(G107="","",G107&gt;1000,"Hard",AND(G107&gt;150,G107&lt;=1000),"Medium",AND(G107&gt;0,G107&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="108" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A108" s="3" t="s">
+        <v>215</v>
+      </c>
       <c r="B108" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D108" s="6" t="str" cm="1">
+      <c r="C108" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D108" s="6" cm="1">
         <f t="array" aca="1" ref="D108" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C108, MATCH(FALSE, ISNUMBER(MID(C108, ROW(INDIRECT("1:"&amp;LEN(C108)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E108" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E108" s="7" cm="1">
         <f t="array" aca="1" ref="E108" ca="1">_xlfn.IFNA(_xlfn.IFS(D108&lt;6,1,D108&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G108" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="109" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F108" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G108" s="8">
+        <f t="shared" si="2"/>
+        <v>105</v>
+      </c>
+      <c r="H108" t="str" cm="1">
+        <f t="array" ref="H108">_xlfn.IFS(G108="","",G108&gt;1000,"Hard",AND(G108&gt;150,G108&lt;=1000),"Medium",AND(G108&gt;0,G108&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="109" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A109" s="3" t="s">
+        <v>216</v>
+      </c>
       <c r="B109" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D109" s="6" t="str" cm="1">
+      <c r="C109" s="5" t="s">
+        <v>79</v>
+      </c>
+      <c r="D109" s="6" cm="1">
         <f t="array" aca="1" ref="D109" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C109, MATCH(FALSE, ISNUMBER(MID(C109, ROW(INDIRECT("1:"&amp;LEN(C109)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E109" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E109" s="7" cm="1">
         <f t="array" aca="1" ref="E109" ca="1">_xlfn.IFNA(_xlfn.IFS(D109&lt;6,1,D109&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G109" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="110" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F109" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G109" s="8">
+        <f t="shared" si="2"/>
+        <v>90</v>
+      </c>
+      <c r="H109" t="str" cm="1">
+        <f t="array" ref="H109">_xlfn.IFS(G109="","",G109&gt;1000,"Hard",AND(G109&gt;150,G109&lt;=1000),"Medium",AND(G109&gt;0,G109&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="110" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A110" s="3" t="s">
+        <v>217</v>
+      </c>
       <c r="B110" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D110" s="6" t="str" cm="1">
+      <c r="C110" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D110" s="6" cm="1">
         <f t="array" aca="1" ref="D110" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C110, MATCH(FALSE, ISNUMBER(MID(C110, ROW(INDIRECT("1:"&amp;LEN(C110)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E110" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E110" s="7" cm="1">
         <f t="array" aca="1" ref="E110" ca="1">_xlfn.IFNA(_xlfn.IFS(D110&lt;6,1,D110&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G110" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="111" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F110" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G110" s="8">
+        <f t="shared" si="2"/>
+        <v>110</v>
+      </c>
+      <c r="H110" t="str" cm="1">
+        <f t="array" ref="H110">_xlfn.IFS(G110="","",G110&gt;1000,"Hard",AND(G110&gt;150,G110&lt;=1000),"Medium",AND(G110&gt;0,G110&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="111" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A111" s="3" t="s">
+        <v>218</v>
+      </c>
       <c r="B111" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D111" s="6" t="str" cm="1">
+      <c r="C111" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D111" s="6" cm="1">
         <f t="array" aca="1" ref="D111" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C111, MATCH(FALSE, ISNUMBER(MID(C111, ROW(INDIRECT("1:"&amp;LEN(C111)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E111" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E111" s="7" cm="1">
         <f t="array" aca="1" ref="E111" ca="1">_xlfn.IFNA(_xlfn.IFS(D111&lt;6,1,D111&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G111" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="112" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F111" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G111" s="8">
+        <f t="shared" si="2"/>
+        <v>103</v>
+      </c>
+      <c r="H111" t="str" cm="1">
+        <f t="array" ref="H111">_xlfn.IFS(G111="","",G111&gt;1000,"Hard",AND(G111&gt;150,G111&lt;=1000),"Medium",AND(G111&gt;0,G111&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="112" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A112" s="3" t="s">
+        <v>219</v>
+      </c>
       <c r="B112" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D112" s="6" t="str" cm="1">
+      <c r="C112" s="5" t="s">
+        <v>82</v>
+      </c>
+      <c r="D112" s="6" cm="1">
         <f t="array" aca="1" ref="D112" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C112, MATCH(FALSE, ISNUMBER(MID(C112, ROW(INDIRECT("1:"&amp;LEN(C112)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E112" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E112" s="7" cm="1">
         <f t="array" aca="1" ref="E112" ca="1">_xlfn.IFNA(_xlfn.IFS(D112&lt;6,1,D112&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G112" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="113" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F112" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G112" s="8">
+        <f t="shared" si="2"/>
+        <v>94</v>
+      </c>
+      <c r="H112" t="str" cm="1">
+        <f t="array" ref="H112">_xlfn.IFS(G112="","",G112&gt;1000,"Hard",AND(G112&gt;150,G112&lt;=1000),"Medium",AND(G112&gt;0,G112&lt;=150),"Easy")</f>
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="113" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A113" s="3" t="s">
+        <v>220</v>
+      </c>
       <c r="B113" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D113" s="6" t="str" cm="1">
+      <c r="C113" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D113" s="6" cm="1">
         <f t="array" aca="1" ref="D113" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C113, MATCH(FALSE, ISNUMBER(MID(C113, ROW(INDIRECT("1:"&amp;LEN(C113)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E113" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E113" s="7" cm="1">
         <f t="array" aca="1" ref="E113" ca="1">_xlfn.IFNA(_xlfn.IFS(D113&lt;6,1,D113&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G113" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="114" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F113" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G113" s="8">
+        <f t="shared" si="2"/>
+        <v>276</v>
+      </c>
+      <c r="H113" t="str" cm="1">
+        <f t="array" ref="H113">_xlfn.IFS(G113="","",G113&gt;1000,"Hard",AND(G113&gt;150,G113&lt;=1000),"Medium",AND(G113&gt;0,G113&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="114" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A114" s="3" t="s">
+        <v>221</v>
+      </c>
       <c r="B114" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D114" s="6" t="str" cm="1">
+      <c r="C114" s="5" t="s">
+        <v>84</v>
+      </c>
+      <c r="D114" s="6" cm="1">
         <f t="array" aca="1" ref="D114" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C114, MATCH(FALSE, ISNUMBER(MID(C114, ROW(INDIRECT("1:"&amp;LEN(C114)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E114" s="7" t="str" cm="1">
+        <v>11</v>
+      </c>
+      <c r="E114" s="7" cm="1">
         <f t="array" aca="1" ref="E114" ca="1">_xlfn.IFNA(_xlfn.IFS(D114&lt;6,1,D114&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G114" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="115" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F114" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G114" s="8">
+        <f t="shared" si="2"/>
+        <v>288</v>
+      </c>
+      <c r="H114" t="str" cm="1">
+        <f t="array" ref="H114">_xlfn.IFS(G114="","",G114&gt;1000,"Hard",AND(G114&gt;150,G114&lt;=1000),"Medium",AND(G114&gt;0,G114&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="115" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A115" s="3" t="s">
+        <v>222</v>
+      </c>
       <c r="B115" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D115" s="6" t="str" cm="1">
+      <c r="C115" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D115" s="6" cm="1">
         <f t="array" aca="1" ref="D115" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C115, MATCH(FALSE, ISNUMBER(MID(C115, ROW(INDIRECT("1:"&amp;LEN(C115)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E115" s="7" t="str" cm="1">
+        <v>9</v>
+      </c>
+      <c r="E115" s="7" cm="1">
         <f t="array" aca="1" ref="E115" ca="1">_xlfn.IFNA(_xlfn.IFS(D115&lt;6,1,D115&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G115" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="116" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F115" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G115" s="8">
+        <f t="shared" si="2"/>
+        <v>220</v>
+      </c>
+      <c r="H115" t="str" cm="1">
+        <f t="array" ref="H115">_xlfn.IFS(G115="","",G115&gt;1000,"Hard",AND(G115&gt;150,G115&lt;=1000),"Medium",AND(G115&gt;0,G115&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="116" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A116" s="3" t="s">
+        <v>223</v>
+      </c>
       <c r="B116" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D116" s="6" t="str" cm="1">
+      <c r="C116" s="5" t="s">
+        <v>65</v>
+      </c>
+      <c r="D116" s="6" cm="1">
         <f t="array" aca="1" ref="D116" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C116, MATCH(FALSE, ISNUMBER(MID(C116, ROW(INDIRECT("1:"&amp;LEN(C116)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E116" s="7" t="str" cm="1">
+        <v>9</v>
+      </c>
+      <c r="E116" s="7" cm="1">
         <f t="array" aca="1" ref="E116" ca="1">_xlfn.IFNA(_xlfn.IFS(D116&lt;6,1,D116&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G116" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="117" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F116" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G116" s="8">
+        <f t="shared" si="2"/>
+        <v>246</v>
+      </c>
+      <c r="H116" t="str" cm="1">
+        <f t="array" ref="H116">_xlfn.IFS(G116="","",G116&gt;1000,"Hard",AND(G116&gt;150,G116&lt;=1000),"Medium",AND(G116&gt;0,G116&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="117" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A117" s="3" t="s">
+        <v>224</v>
+      </c>
       <c r="B117" s="5" t="str">
         <f>""</f>
         <v/>
       </c>
-      <c r="D117" s="6" t="str" cm="1">
+      <c r="C117" s="5" t="s">
+        <v>67</v>
+      </c>
+      <c r="D117" s="6" cm="1">
         <f t="array" aca="1" ref="D117" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C117, MATCH(FALSE, ISNUMBER(MID(C117, ROW(INDIRECT("1:"&amp;LEN(C117)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E117" s="7" t="str" cm="1">
+        <v>9</v>
+      </c>
+      <c r="E117" s="7" cm="1">
         <f t="array" aca="1" ref="E117" ca="1">_xlfn.IFNA(_xlfn.IFS(D117&lt;6,1,D117&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G117" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="118" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <v>2</v>
+      </c>
+      <c r="F117" s="8" t="s">
+        <v>175</v>
+      </c>
+      <c r="G117" s="8">
+        <f t="shared" si="2"/>
+        <v>218</v>
+      </c>
+      <c r="H117" t="str" cm="1">
+        <f t="array" ref="H117">_xlfn.IFS(G117="","",G117&gt;1000,"Hard",AND(G117&gt;150,G117&lt;=1000),"Medium",AND(G117&gt;0,G117&lt;=150),"Easy")</f>
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="118" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B118" s="5" t="str">
         <f>""</f>
         <v/>
@@ -3975,11 +5359,15 @@
         <v/>
       </c>
       <c r="G118" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="119" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H118" t="str" cm="1">
+        <f t="array" ref="H118">_xlfn.IFS(G118="","",G118&gt;1000,"Hard",AND(G118&gt;150,G118&lt;=1000),"Medium",AND(G118&gt;0,G118&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="119" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B119" s="5" t="str">
         <f>""</f>
         <v/>
@@ -3993,11 +5381,15 @@
         <v/>
       </c>
       <c r="G119" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="120" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H119" t="str" cm="1">
+        <f t="array" ref="H119">_xlfn.IFS(G119="","",G119&gt;1000,"Hard",AND(G119&gt;150,G119&lt;=1000),"Medium",AND(G119&gt;0,G119&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="120" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B120" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4011,11 +5403,15 @@
         <v/>
       </c>
       <c r="G120" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="121" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H120" t="str" cm="1">
+        <f t="array" ref="H120">_xlfn.IFS(G120="","",G120&gt;1000,"Hard",AND(G120&gt;150,G120&lt;=1000),"Medium",AND(G120&gt;0,G120&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="121" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B121" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4029,11 +5425,15 @@
         <v/>
       </c>
       <c r="G121" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="122" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H121" t="str" cm="1">
+        <f t="array" ref="H121">_xlfn.IFS(G121="","",G121&gt;1000,"Hard",AND(G121&gt;150,G121&lt;=1000),"Medium",AND(G121&gt;0,G121&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="122" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B122" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4047,11 +5447,15 @@
         <v/>
       </c>
       <c r="G122" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="123" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H122" t="str" cm="1">
+        <f t="array" ref="H122">_xlfn.IFS(G122="","",G122&gt;1000,"Hard",AND(G122&gt;150,G122&lt;=1000),"Medium",AND(G122&gt;0,G122&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="123" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B123" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4065,11 +5469,15 @@
         <v/>
       </c>
       <c r="G123" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="124" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H123" t="str" cm="1">
+        <f t="array" ref="H123">_xlfn.IFS(G123="","",G123&gt;1000,"Hard",AND(G123&gt;150,G123&lt;=1000),"Medium",AND(G123&gt;0,G123&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="124" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B124" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4083,11 +5491,15 @@
         <v/>
       </c>
       <c r="G124" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="125" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H124" t="str" cm="1">
+        <f t="array" ref="H124">_xlfn.IFS(G124="","",G124&gt;1000,"Hard",AND(G124&gt;150,G124&lt;=1000),"Medium",AND(G124&gt;0,G124&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="125" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B125" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4101,11 +5513,15 @@
         <v/>
       </c>
       <c r="G125" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="126" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H125" t="str" cm="1">
+        <f t="array" ref="H125">_xlfn.IFS(G125="","",G125&gt;1000,"Hard",AND(G125&gt;150,G125&lt;=1000),"Medium",AND(G125&gt;0,G125&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="126" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B126" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4119,11 +5535,15 @@
         <v/>
       </c>
       <c r="G126" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="127" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H126" t="str" cm="1">
+        <f t="array" ref="H126">_xlfn.IFS(G126="","",G126&gt;1000,"Hard",AND(G126&gt;150,G126&lt;=1000),"Medium",AND(G126&gt;0,G126&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="127" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B127" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4137,11 +5557,15 @@
         <v/>
       </c>
       <c r="G127" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="128" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H127" t="str" cm="1">
+        <f t="array" ref="H127">_xlfn.IFS(G127="","",G127&gt;1000,"Hard",AND(G127&gt;150,G127&lt;=1000),"Medium",AND(G127&gt;0,G127&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="128" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B128" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4155,11 +5579,15 @@
         <v/>
       </c>
       <c r="G128" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H128" t="str" cm="1">
+        <f t="array" ref="H128">_xlfn.IFS(G128="","",G128&gt;1000,"Hard",AND(G128&gt;150,G128&lt;=1000),"Medium",AND(G128&gt;0,G128&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="129" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B129" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4173,11 +5601,15 @@
         <v/>
       </c>
       <c r="G129" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H129" t="str" cm="1">
+        <f t="array" ref="H129">_xlfn.IFS(G129="","",G129&gt;1000,"Hard",AND(G129&gt;150,G129&lt;=1000),"Medium",AND(G129&gt;0,G129&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="130" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B130" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4191,11 +5623,15 @@
         <v/>
       </c>
       <c r="G130" s="8" t="str">
-        <f t="shared" si="1"/>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="2"/>
+        <v/>
+      </c>
+      <c r="H130" t="str" cm="1">
+        <f t="array" ref="H130">_xlfn.IFS(G130="","",G130&gt;1000,"Hard",AND(G130&gt;150,G130&lt;=1000),"Medium",AND(G130&gt;0,G130&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="131" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B131" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4209,11 +5645,15 @@
         <v/>
       </c>
       <c r="G131" s="8" t="str">
-        <f t="shared" ref="G131:G194" si="2">IF(LEN(A131)=0,"",LEN(A131))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="G131:G194" si="3">IF(LEN(A131)=0,"",LEN(A131))</f>
+        <v/>
+      </c>
+      <c r="H131" t="str" cm="1">
+        <f t="array" ref="H131">_xlfn.IFS(G131="","",G131&gt;1000,"Hard",AND(G131&gt;150,G131&lt;=1000),"Medium",AND(G131&gt;0,G131&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="132" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B132" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4227,11 +5667,15 @@
         <v/>
       </c>
       <c r="G132" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H132" t="str" cm="1">
+        <f t="array" ref="H132">_xlfn.IFS(G132="","",G132&gt;1000,"Hard",AND(G132&gt;150,G132&lt;=1000),"Medium",AND(G132&gt;0,G132&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="133" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B133" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4245,11 +5689,15 @@
         <v/>
       </c>
       <c r="G133" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H133" t="str" cm="1">
+        <f t="array" ref="H133">_xlfn.IFS(G133="","",G133&gt;1000,"Hard",AND(G133&gt;150,G133&lt;=1000),"Medium",AND(G133&gt;0,G133&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="134" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B134" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4263,11 +5711,15 @@
         <v/>
       </c>
       <c r="G134" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H134" t="str" cm="1">
+        <f t="array" ref="H134">_xlfn.IFS(G134="","",G134&gt;1000,"Hard",AND(G134&gt;150,G134&lt;=1000),"Medium",AND(G134&gt;0,G134&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="135" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B135" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4281,11 +5733,15 @@
         <v/>
       </c>
       <c r="G135" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H135" t="str" cm="1">
+        <f t="array" ref="H135">_xlfn.IFS(G135="","",G135&gt;1000,"Hard",AND(G135&gt;150,G135&lt;=1000),"Medium",AND(G135&gt;0,G135&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="136" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B136" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4299,11 +5755,15 @@
         <v/>
       </c>
       <c r="G136" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H136" t="str" cm="1">
+        <f t="array" ref="H136">_xlfn.IFS(G136="","",G136&gt;1000,"Hard",AND(G136&gt;150,G136&lt;=1000),"Medium",AND(G136&gt;0,G136&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="137" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B137" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4317,11 +5777,15 @@
         <v/>
       </c>
       <c r="G137" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H137" t="str" cm="1">
+        <f t="array" ref="H137">_xlfn.IFS(G137="","",G137&gt;1000,"Hard",AND(G137&gt;150,G137&lt;=1000),"Medium",AND(G137&gt;0,G137&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="138" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B138" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4335,11 +5799,15 @@
         <v/>
       </c>
       <c r="G138" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H138" t="str" cm="1">
+        <f t="array" ref="H138">_xlfn.IFS(G138="","",G138&gt;1000,"Hard",AND(G138&gt;150,G138&lt;=1000),"Medium",AND(G138&gt;0,G138&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="139" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B139" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4353,11 +5821,15 @@
         <v/>
       </c>
       <c r="G139" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="140" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H139" t="str" cm="1">
+        <f t="array" ref="H139">_xlfn.IFS(G139="","",G139&gt;1000,"Hard",AND(G139&gt;150,G139&lt;=1000),"Medium",AND(G139&gt;0,G139&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="140" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B140" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4371,11 +5843,15 @@
         <v/>
       </c>
       <c r="G140" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="141" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H140" t="str" cm="1">
+        <f t="array" ref="H140">_xlfn.IFS(G140="","",G140&gt;1000,"Hard",AND(G140&gt;150,G140&lt;=1000),"Medium",AND(G140&gt;0,G140&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="141" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B141" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4389,11 +5865,15 @@
         <v/>
       </c>
       <c r="G141" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="142" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H141" t="str" cm="1">
+        <f t="array" ref="H141">_xlfn.IFS(G141="","",G141&gt;1000,"Hard",AND(G141&gt;150,G141&lt;=1000),"Medium",AND(G141&gt;0,G141&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="142" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B142" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4407,11 +5887,15 @@
         <v/>
       </c>
       <c r="G142" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="143" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H142" t="str" cm="1">
+        <f t="array" ref="H142">_xlfn.IFS(G142="","",G142&gt;1000,"Hard",AND(G142&gt;150,G142&lt;=1000),"Medium",AND(G142&gt;0,G142&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="143" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B143" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4425,11 +5909,15 @@
         <v/>
       </c>
       <c r="G143" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="144" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H143" t="str" cm="1">
+        <f t="array" ref="H143">_xlfn.IFS(G143="","",G143&gt;1000,"Hard",AND(G143&gt;150,G143&lt;=1000),"Medium",AND(G143&gt;0,G143&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="144" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B144" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4443,11 +5931,15 @@
         <v/>
       </c>
       <c r="G144" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="145" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H144" t="str" cm="1">
+        <f t="array" ref="H144">_xlfn.IFS(G144="","",G144&gt;1000,"Hard",AND(G144&gt;150,G144&lt;=1000),"Medium",AND(G144&gt;0,G144&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="145" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B145" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4461,11 +5953,15 @@
         <v/>
       </c>
       <c r="G145" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="146" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H145" t="str" cm="1">
+        <f t="array" ref="H145">_xlfn.IFS(G145="","",G145&gt;1000,"Hard",AND(G145&gt;150,G145&lt;=1000),"Medium",AND(G145&gt;0,G145&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="146" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B146" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4479,11 +5975,15 @@
         <v/>
       </c>
       <c r="G146" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="147" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H146" t="str" cm="1">
+        <f t="array" ref="H146">_xlfn.IFS(G146="","",G146&gt;1000,"Hard",AND(G146&gt;150,G146&lt;=1000),"Medium",AND(G146&gt;0,G146&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="147" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B147" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4497,11 +5997,15 @@
         <v/>
       </c>
       <c r="G147" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="148" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H147" t="str" cm="1">
+        <f t="array" ref="H147">_xlfn.IFS(G147="","",G147&gt;1000,"Hard",AND(G147&gt;150,G147&lt;=1000),"Medium",AND(G147&gt;0,G147&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="148" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B148" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4515,11 +6019,15 @@
         <v/>
       </c>
       <c r="G148" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="149" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H148" t="str" cm="1">
+        <f t="array" ref="H148">_xlfn.IFS(G148="","",G148&gt;1000,"Hard",AND(G148&gt;150,G148&lt;=1000),"Medium",AND(G148&gt;0,G148&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="149" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B149" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4533,11 +6041,15 @@
         <v/>
       </c>
       <c r="G149" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="150" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H149" t="str" cm="1">
+        <f t="array" ref="H149">_xlfn.IFS(G149="","",G149&gt;1000,"Hard",AND(G149&gt;150,G149&lt;=1000),"Medium",AND(G149&gt;0,G149&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="150" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B150" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4551,11 +6063,15 @@
         <v/>
       </c>
       <c r="G150" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="151" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H150" t="str" cm="1">
+        <f t="array" ref="H150">_xlfn.IFS(G150="","",G150&gt;1000,"Hard",AND(G150&gt;150,G150&lt;=1000),"Medium",AND(G150&gt;0,G150&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="151" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B151" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4569,11 +6085,15 @@
         <v/>
       </c>
       <c r="G151" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="152" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H151" t="str" cm="1">
+        <f t="array" ref="H151">_xlfn.IFS(G151="","",G151&gt;1000,"Hard",AND(G151&gt;150,G151&lt;=1000),"Medium",AND(G151&gt;0,G151&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="152" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B152" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4587,11 +6107,15 @@
         <v/>
       </c>
       <c r="G152" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="153" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H152" t="str" cm="1">
+        <f t="array" ref="H152">_xlfn.IFS(G152="","",G152&gt;1000,"Hard",AND(G152&gt;150,G152&lt;=1000),"Medium",AND(G152&gt;0,G152&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="153" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B153" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4605,11 +6129,15 @@
         <v/>
       </c>
       <c r="G153" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="154" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H153" t="str" cm="1">
+        <f t="array" ref="H153">_xlfn.IFS(G153="","",G153&gt;1000,"Hard",AND(G153&gt;150,G153&lt;=1000),"Medium",AND(G153&gt;0,G153&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="154" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B154" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4623,11 +6151,15 @@
         <v/>
       </c>
       <c r="G154" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="155" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H154" t="str" cm="1">
+        <f t="array" ref="H154">_xlfn.IFS(G154="","",G154&gt;1000,"Hard",AND(G154&gt;150,G154&lt;=1000),"Medium",AND(G154&gt;0,G154&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="155" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B155" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4641,11 +6173,15 @@
         <v/>
       </c>
       <c r="G155" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="156" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H155" t="str" cm="1">
+        <f t="array" ref="H155">_xlfn.IFS(G155="","",G155&gt;1000,"Hard",AND(G155&gt;150,G155&lt;=1000),"Medium",AND(G155&gt;0,G155&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="156" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B156" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4659,11 +6195,15 @@
         <v/>
       </c>
       <c r="G156" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="157" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H156" t="str" cm="1">
+        <f t="array" ref="H156">_xlfn.IFS(G156="","",G156&gt;1000,"Hard",AND(G156&gt;150,G156&lt;=1000),"Medium",AND(G156&gt;0,G156&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="157" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B157" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4677,11 +6217,15 @@
         <v/>
       </c>
       <c r="G157" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="158" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H157" t="str" cm="1">
+        <f t="array" ref="H157">_xlfn.IFS(G157="","",G157&gt;1000,"Hard",AND(G157&gt;150,G157&lt;=1000),"Medium",AND(G157&gt;0,G157&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="158" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B158" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4695,11 +6239,15 @@
         <v/>
       </c>
       <c r="G158" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="159" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H158" t="str" cm="1">
+        <f t="array" ref="H158">_xlfn.IFS(G158="","",G158&gt;1000,"Hard",AND(G158&gt;150,G158&lt;=1000),"Medium",AND(G158&gt;0,G158&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="159" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B159" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4713,11 +6261,15 @@
         <v/>
       </c>
       <c r="G159" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="160" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H159" t="str" cm="1">
+        <f t="array" ref="H159">_xlfn.IFS(G159="","",G159&gt;1000,"Hard",AND(G159&gt;150,G159&lt;=1000),"Medium",AND(G159&gt;0,G159&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="160" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B160" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4731,11 +6283,15 @@
         <v/>
       </c>
       <c r="G160" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="161" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H160" t="str" cm="1">
+        <f t="array" ref="H160">_xlfn.IFS(G160="","",G160&gt;1000,"Hard",AND(G160&gt;150,G160&lt;=1000),"Medium",AND(G160&gt;0,G160&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="161" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B161" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4749,11 +6305,15 @@
         <v/>
       </c>
       <c r="G161" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="162" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H161" t="str" cm="1">
+        <f t="array" ref="H161">_xlfn.IFS(G161="","",G161&gt;1000,"Hard",AND(G161&gt;150,G161&lt;=1000),"Medium",AND(G161&gt;0,G161&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="162" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B162" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4767,11 +6327,15 @@
         <v/>
       </c>
       <c r="G162" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="163" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H162" t="str" cm="1">
+        <f t="array" ref="H162">_xlfn.IFS(G162="","",G162&gt;1000,"Hard",AND(G162&gt;150,G162&lt;=1000),"Medium",AND(G162&gt;0,G162&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="163" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B163" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4785,11 +6349,15 @@
         <v/>
       </c>
       <c r="G163" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="164" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H163" t="str" cm="1">
+        <f t="array" ref="H163">_xlfn.IFS(G163="","",G163&gt;1000,"Hard",AND(G163&gt;150,G163&lt;=1000),"Medium",AND(G163&gt;0,G163&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="164" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B164" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4803,11 +6371,15 @@
         <v/>
       </c>
       <c r="G164" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="165" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H164" t="str" cm="1">
+        <f t="array" ref="H164">_xlfn.IFS(G164="","",G164&gt;1000,"Hard",AND(G164&gt;150,G164&lt;=1000),"Medium",AND(G164&gt;0,G164&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="165" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B165" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4821,11 +6393,15 @@
         <v/>
       </c>
       <c r="G165" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="166" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H165" t="str" cm="1">
+        <f t="array" ref="H165">_xlfn.IFS(G165="","",G165&gt;1000,"Hard",AND(G165&gt;150,G165&lt;=1000),"Medium",AND(G165&gt;0,G165&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="166" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B166" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4839,11 +6415,15 @@
         <v/>
       </c>
       <c r="G166" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="167" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H166" t="str" cm="1">
+        <f t="array" ref="H166">_xlfn.IFS(G166="","",G166&gt;1000,"Hard",AND(G166&gt;150,G166&lt;=1000),"Medium",AND(G166&gt;0,G166&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="167" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B167" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4857,11 +6437,15 @@
         <v/>
       </c>
       <c r="G167" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="168" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H167" t="str" cm="1">
+        <f t="array" ref="H167">_xlfn.IFS(G167="","",G167&gt;1000,"Hard",AND(G167&gt;150,G167&lt;=1000),"Medium",AND(G167&gt;0,G167&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="168" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B168" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4875,11 +6459,15 @@
         <v/>
       </c>
       <c r="G168" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="169" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H168" t="str" cm="1">
+        <f t="array" ref="H168">_xlfn.IFS(G168="","",G168&gt;1000,"Hard",AND(G168&gt;150,G168&lt;=1000),"Medium",AND(G168&gt;0,G168&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="169" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B169" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4893,11 +6481,15 @@
         <v/>
       </c>
       <c r="G169" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="170" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H169" t="str" cm="1">
+        <f t="array" ref="H169">_xlfn.IFS(G169="","",G169&gt;1000,"Hard",AND(G169&gt;150,G169&lt;=1000),"Medium",AND(G169&gt;0,G169&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="170" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B170" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4911,11 +6503,15 @@
         <v/>
       </c>
       <c r="G170" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="171" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H170" t="str" cm="1">
+        <f t="array" ref="H170">_xlfn.IFS(G170="","",G170&gt;1000,"Hard",AND(G170&gt;150,G170&lt;=1000),"Medium",AND(G170&gt;0,G170&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="171" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B171" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4929,11 +6525,15 @@
         <v/>
       </c>
       <c r="G171" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="172" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H171" t="str" cm="1">
+        <f t="array" ref="H171">_xlfn.IFS(G171="","",G171&gt;1000,"Hard",AND(G171&gt;150,G171&lt;=1000),"Medium",AND(G171&gt;0,G171&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="172" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B172" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4947,11 +6547,15 @@
         <v/>
       </c>
       <c r="G172" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="173" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H172" t="str" cm="1">
+        <f t="array" ref="H172">_xlfn.IFS(G172="","",G172&gt;1000,"Hard",AND(G172&gt;150,G172&lt;=1000),"Medium",AND(G172&gt;0,G172&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="173" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B173" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4965,11 +6569,15 @@
         <v/>
       </c>
       <c r="G173" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="174" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H173" t="str" cm="1">
+        <f t="array" ref="H173">_xlfn.IFS(G173="","",G173&gt;1000,"Hard",AND(G173&gt;150,G173&lt;=1000),"Medium",AND(G173&gt;0,G173&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="174" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B174" s="5" t="str">
         <f>""</f>
         <v/>
@@ -4983,11 +6591,15 @@
         <v/>
       </c>
       <c r="G174" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="175" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H174" t="str" cm="1">
+        <f t="array" ref="H174">_xlfn.IFS(G174="","",G174&gt;1000,"Hard",AND(G174&gt;150,G174&lt;=1000),"Medium",AND(G174&gt;0,G174&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="175" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B175" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5001,11 +6613,15 @@
         <v/>
       </c>
       <c r="G175" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="176" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H175" t="str" cm="1">
+        <f t="array" ref="H175">_xlfn.IFS(G175="","",G175&gt;1000,"Hard",AND(G175&gt;150,G175&lt;=1000),"Medium",AND(G175&gt;0,G175&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="176" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B176" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5019,11 +6635,15 @@
         <v/>
       </c>
       <c r="G176" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="177" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H176" t="str" cm="1">
+        <f t="array" ref="H176">_xlfn.IFS(G176="","",G176&gt;1000,"Hard",AND(G176&gt;150,G176&lt;=1000),"Medium",AND(G176&gt;0,G176&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="177" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B177" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5037,11 +6657,15 @@
         <v/>
       </c>
       <c r="G177" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="178" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H177" t="str" cm="1">
+        <f t="array" ref="H177">_xlfn.IFS(G177="","",G177&gt;1000,"Hard",AND(G177&gt;150,G177&lt;=1000),"Medium",AND(G177&gt;0,G177&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="178" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B178" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5055,11 +6679,15 @@
         <v/>
       </c>
       <c r="G178" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="179" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H178" t="str" cm="1">
+        <f t="array" ref="H178">_xlfn.IFS(G178="","",G178&gt;1000,"Hard",AND(G178&gt;150,G178&lt;=1000),"Medium",AND(G178&gt;0,G178&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="179" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B179" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5073,11 +6701,15 @@
         <v/>
       </c>
       <c r="G179" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="180" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H179" t="str" cm="1">
+        <f t="array" ref="H179">_xlfn.IFS(G179="","",G179&gt;1000,"Hard",AND(G179&gt;150,G179&lt;=1000),"Medium",AND(G179&gt;0,G179&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="180" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B180" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5091,11 +6723,15 @@
         <v/>
       </c>
       <c r="G180" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="181" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H180" t="str" cm="1">
+        <f t="array" ref="H180">_xlfn.IFS(G180="","",G180&gt;1000,"Hard",AND(G180&gt;150,G180&lt;=1000),"Medium",AND(G180&gt;0,G180&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="181" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B181" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5109,11 +6745,15 @@
         <v/>
       </c>
       <c r="G181" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="182" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H181" t="str" cm="1">
+        <f t="array" ref="H181">_xlfn.IFS(G181="","",G181&gt;1000,"Hard",AND(G181&gt;150,G181&lt;=1000),"Medium",AND(G181&gt;0,G181&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="182" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B182" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5127,11 +6767,15 @@
         <v/>
       </c>
       <c r="G182" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="183" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H182" t="str" cm="1">
+        <f t="array" ref="H182">_xlfn.IFS(G182="","",G182&gt;1000,"Hard",AND(G182&gt;150,G182&lt;=1000),"Medium",AND(G182&gt;0,G182&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="183" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B183" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5145,11 +6789,15 @@
         <v/>
       </c>
       <c r="G183" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="184" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H183" t="str" cm="1">
+        <f t="array" ref="H183">_xlfn.IFS(G183="","",G183&gt;1000,"Hard",AND(G183&gt;150,G183&lt;=1000),"Medium",AND(G183&gt;0,G183&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="184" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B184" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5163,11 +6811,15 @@
         <v/>
       </c>
       <c r="G184" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="185" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H184" t="str" cm="1">
+        <f t="array" ref="H184">_xlfn.IFS(G184="","",G184&gt;1000,"Hard",AND(G184&gt;150,G184&lt;=1000),"Medium",AND(G184&gt;0,G184&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="185" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B185" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5181,11 +6833,15 @@
         <v/>
       </c>
       <c r="G185" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="186" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H185" t="str" cm="1">
+        <f t="array" ref="H185">_xlfn.IFS(G185="","",G185&gt;1000,"Hard",AND(G185&gt;150,G185&lt;=1000),"Medium",AND(G185&gt;0,G185&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="186" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B186" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5199,11 +6855,15 @@
         <v/>
       </c>
       <c r="G186" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="187" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H186" t="str" cm="1">
+        <f t="array" ref="H186">_xlfn.IFS(G186="","",G186&gt;1000,"Hard",AND(G186&gt;150,G186&lt;=1000),"Medium",AND(G186&gt;0,G186&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="187" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B187" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5217,11 +6877,15 @@
         <v/>
       </c>
       <c r="G187" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="188" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H187" t="str" cm="1">
+        <f t="array" ref="H187">_xlfn.IFS(G187="","",G187&gt;1000,"Hard",AND(G187&gt;150,G187&lt;=1000),"Medium",AND(G187&gt;0,G187&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="188" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B188" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5235,11 +6899,15 @@
         <v/>
       </c>
       <c r="G188" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="189" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H188" t="str" cm="1">
+        <f t="array" ref="H188">_xlfn.IFS(G188="","",G188&gt;1000,"Hard",AND(G188&gt;150,G188&lt;=1000),"Medium",AND(G188&gt;0,G188&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="189" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B189" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5253,11 +6921,15 @@
         <v/>
       </c>
       <c r="G189" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="190" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H189" t="str" cm="1">
+        <f t="array" ref="H189">_xlfn.IFS(G189="","",G189&gt;1000,"Hard",AND(G189&gt;150,G189&lt;=1000),"Medium",AND(G189&gt;0,G189&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="190" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B190" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5271,11 +6943,15 @@
         <v/>
       </c>
       <c r="G190" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="191" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H190" t="str" cm="1">
+        <f t="array" ref="H190">_xlfn.IFS(G190="","",G190&gt;1000,"Hard",AND(G190&gt;150,G190&lt;=1000),"Medium",AND(G190&gt;0,G190&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="191" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B191" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5289,11 +6965,15 @@
         <v/>
       </c>
       <c r="G191" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="192" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H191" t="str" cm="1">
+        <f t="array" ref="H191">_xlfn.IFS(G191="","",G191&gt;1000,"Hard",AND(G191&gt;150,G191&lt;=1000),"Medium",AND(G191&gt;0,G191&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="192" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B192" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5307,11 +6987,15 @@
         <v/>
       </c>
       <c r="G192" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="193" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H192" t="str" cm="1">
+        <f t="array" ref="H192">_xlfn.IFS(G192="","",G192&gt;1000,"Hard",AND(G192&gt;150,G192&lt;=1000),"Medium",AND(G192&gt;0,G192&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="193" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B193" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5325,11 +7009,15 @@
         <v/>
       </c>
       <c r="G193" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="194" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H193" t="str" cm="1">
+        <f t="array" ref="H193">_xlfn.IFS(G193="","",G193&gt;1000,"Hard",AND(G193&gt;150,G193&lt;=1000),"Medium",AND(G193&gt;0,G193&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="194" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B194" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5343,11 +7031,15 @@
         <v/>
       </c>
       <c r="G194" s="8" t="str">
-        <f t="shared" si="2"/>
-        <v/>
-      </c>
-    </row>
-    <row r="195" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="3"/>
+        <v/>
+      </c>
+      <c r="H194" t="str" cm="1">
+        <f t="array" ref="H194">_xlfn.IFS(G194="","",G194&gt;1000,"Hard",AND(G194&gt;150,G194&lt;=1000),"Medium",AND(G194&gt;0,G194&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="195" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B195" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5361,11 +7053,15 @@
         <v/>
       </c>
       <c r="G195" s="8" t="str">
-        <f t="shared" ref="G195:G258" si="3">IF(LEN(A195)=0,"",LEN(A195))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="196" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="G195:G258" si="4">IF(LEN(A195)=0,"",LEN(A195))</f>
+        <v/>
+      </c>
+      <c r="H195" t="str" cm="1">
+        <f t="array" ref="H195">_xlfn.IFS(G195="","",G195&gt;1000,"Hard",AND(G195&gt;150,G195&lt;=1000),"Medium",AND(G195&gt;0,G195&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="196" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B196" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5379,11 +7075,15 @@
         <v/>
       </c>
       <c r="G196" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="197" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H196" t="str" cm="1">
+        <f t="array" ref="H196">_xlfn.IFS(G196="","",G196&gt;1000,"Hard",AND(G196&gt;150,G196&lt;=1000),"Medium",AND(G196&gt;0,G196&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="197" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B197" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5397,11 +7097,15 @@
         <v/>
       </c>
       <c r="G197" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="198" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H197" t="str" cm="1">
+        <f t="array" ref="H197">_xlfn.IFS(G197="","",G197&gt;1000,"Hard",AND(G197&gt;150,G197&lt;=1000),"Medium",AND(G197&gt;0,G197&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="198" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B198" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5415,11 +7119,15 @@
         <v/>
       </c>
       <c r="G198" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="199" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H198" t="str" cm="1">
+        <f t="array" ref="H198">_xlfn.IFS(G198="","",G198&gt;1000,"Hard",AND(G198&gt;150,G198&lt;=1000),"Medium",AND(G198&gt;0,G198&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="199" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B199" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5433,11 +7141,15 @@
         <v/>
       </c>
       <c r="G199" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="200" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H199" t="str" cm="1">
+        <f t="array" ref="H199">_xlfn.IFS(G199="","",G199&gt;1000,"Hard",AND(G199&gt;150,G199&lt;=1000),"Medium",AND(G199&gt;0,G199&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="200" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B200" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5451,11 +7163,15 @@
         <v/>
       </c>
       <c r="G200" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="201" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H200" t="str" cm="1">
+        <f t="array" ref="H200">_xlfn.IFS(G200="","",G200&gt;1000,"Hard",AND(G200&gt;150,G200&lt;=1000),"Medium",AND(G200&gt;0,G200&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="201" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B201" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5469,11 +7185,15 @@
         <v/>
       </c>
       <c r="G201" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="202" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H201" t="str" cm="1">
+        <f t="array" ref="H201">_xlfn.IFS(G201="","",G201&gt;1000,"Hard",AND(G201&gt;150,G201&lt;=1000),"Medium",AND(G201&gt;0,G201&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="202" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B202" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5487,11 +7207,15 @@
         <v/>
       </c>
       <c r="G202" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="203" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H202" t="str" cm="1">
+        <f t="array" ref="H202">_xlfn.IFS(G202="","",G202&gt;1000,"Hard",AND(G202&gt;150,G202&lt;=1000),"Medium",AND(G202&gt;0,G202&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="203" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B203" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5505,11 +7229,15 @@
         <v/>
       </c>
       <c r="G203" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="204" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H203" t="str" cm="1">
+        <f t="array" ref="H203">_xlfn.IFS(G203="","",G203&gt;1000,"Hard",AND(G203&gt;150,G203&lt;=1000),"Medium",AND(G203&gt;0,G203&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="204" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B204" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5523,11 +7251,15 @@
         <v/>
       </c>
       <c r="G204" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="205" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H204" t="str" cm="1">
+        <f t="array" ref="H204">_xlfn.IFS(G204="","",G204&gt;1000,"Hard",AND(G204&gt;150,G204&lt;=1000),"Medium",AND(G204&gt;0,G204&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="205" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B205" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5541,11 +7273,15 @@
         <v/>
       </c>
       <c r="G205" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="206" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H205" t="str" cm="1">
+        <f t="array" ref="H205">_xlfn.IFS(G205="","",G205&gt;1000,"Hard",AND(G205&gt;150,G205&lt;=1000),"Medium",AND(G205&gt;0,G205&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="206" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B206" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5559,11 +7295,15 @@
         <v/>
       </c>
       <c r="G206" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="207" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H206" t="str" cm="1">
+        <f t="array" ref="H206">_xlfn.IFS(G206="","",G206&gt;1000,"Hard",AND(G206&gt;150,G206&lt;=1000),"Medium",AND(G206&gt;0,G206&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="207" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B207" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5577,11 +7317,15 @@
         <v/>
       </c>
       <c r="G207" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="208" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H207" t="str" cm="1">
+        <f t="array" ref="H207">_xlfn.IFS(G207="","",G207&gt;1000,"Hard",AND(G207&gt;150,G207&lt;=1000),"Medium",AND(G207&gt;0,G207&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="208" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B208" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5595,11 +7339,15 @@
         <v/>
       </c>
       <c r="G208" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="209" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H208" t="str" cm="1">
+        <f t="array" ref="H208">_xlfn.IFS(G208="","",G208&gt;1000,"Hard",AND(G208&gt;150,G208&lt;=1000),"Medium",AND(G208&gt;0,G208&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="209" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B209" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5613,11 +7361,15 @@
         <v/>
       </c>
       <c r="G209" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="210" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H209" t="str" cm="1">
+        <f t="array" ref="H209">_xlfn.IFS(G209="","",G209&gt;1000,"Hard",AND(G209&gt;150,G209&lt;=1000),"Medium",AND(G209&gt;0,G209&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="210" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B210" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5631,11 +7383,15 @@
         <v/>
       </c>
       <c r="G210" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="211" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H210" t="str" cm="1">
+        <f t="array" ref="H210">_xlfn.IFS(G210="","",G210&gt;1000,"Hard",AND(G210&gt;150,G210&lt;=1000),"Medium",AND(G210&gt;0,G210&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="211" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B211" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5649,11 +7405,15 @@
         <v/>
       </c>
       <c r="G211" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="212" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H211" t="str" cm="1">
+        <f t="array" ref="H211">_xlfn.IFS(G211="","",G211&gt;1000,"Hard",AND(G211&gt;150,G211&lt;=1000),"Medium",AND(G211&gt;0,G211&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="212" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B212" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5667,11 +7427,15 @@
         <v/>
       </c>
       <c r="G212" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="213" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H212" t="str" cm="1">
+        <f t="array" ref="H212">_xlfn.IFS(G212="","",G212&gt;1000,"Hard",AND(G212&gt;150,G212&lt;=1000),"Medium",AND(G212&gt;0,G212&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="213" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B213" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5685,11 +7449,15 @@
         <v/>
       </c>
       <c r="G213" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="214" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H213" t="str" cm="1">
+        <f t="array" ref="H213">_xlfn.IFS(G213="","",G213&gt;1000,"Hard",AND(G213&gt;150,G213&lt;=1000),"Medium",AND(G213&gt;0,G213&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="214" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B214" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5703,11 +7471,15 @@
         <v/>
       </c>
       <c r="G214" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="215" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H214" t="str" cm="1">
+        <f t="array" ref="H214">_xlfn.IFS(G214="","",G214&gt;1000,"Hard",AND(G214&gt;150,G214&lt;=1000),"Medium",AND(G214&gt;0,G214&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="215" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B215" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5721,11 +7493,15 @@
         <v/>
       </c>
       <c r="G215" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="216" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H215" t="str" cm="1">
+        <f t="array" ref="H215">_xlfn.IFS(G215="","",G215&gt;1000,"Hard",AND(G215&gt;150,G215&lt;=1000),"Medium",AND(G215&gt;0,G215&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="216" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B216" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5739,11 +7515,15 @@
         <v/>
       </c>
       <c r="G216" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="217" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H216" t="str" cm="1">
+        <f t="array" ref="H216">_xlfn.IFS(G216="","",G216&gt;1000,"Hard",AND(G216&gt;150,G216&lt;=1000),"Medium",AND(G216&gt;0,G216&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="217" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B217" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5757,11 +7537,15 @@
         <v/>
       </c>
       <c r="G217" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="218" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H217" t="str" cm="1">
+        <f t="array" ref="H217">_xlfn.IFS(G217="","",G217&gt;1000,"Hard",AND(G217&gt;150,G217&lt;=1000),"Medium",AND(G217&gt;0,G217&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="218" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B218" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5775,11 +7559,15 @@
         <v/>
       </c>
       <c r="G218" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="219" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H218" t="str" cm="1">
+        <f t="array" ref="H218">_xlfn.IFS(G218="","",G218&gt;1000,"Hard",AND(G218&gt;150,G218&lt;=1000),"Medium",AND(G218&gt;0,G218&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="219" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B219" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5793,11 +7581,15 @@
         <v/>
       </c>
       <c r="G219" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="220" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H219" t="str" cm="1">
+        <f t="array" ref="H219">_xlfn.IFS(G219="","",G219&gt;1000,"Hard",AND(G219&gt;150,G219&lt;=1000),"Medium",AND(G219&gt;0,G219&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="220" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B220" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5811,11 +7603,15 @@
         <v/>
       </c>
       <c r="G220" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="221" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H220" t="str" cm="1">
+        <f t="array" ref="H220">_xlfn.IFS(G220="","",G220&gt;1000,"Hard",AND(G220&gt;150,G220&lt;=1000),"Medium",AND(G220&gt;0,G220&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="221" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B221" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5829,11 +7625,15 @@
         <v/>
       </c>
       <c r="G221" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="222" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H221" t="str" cm="1">
+        <f t="array" ref="H221">_xlfn.IFS(G221="","",G221&gt;1000,"Hard",AND(G221&gt;150,G221&lt;=1000),"Medium",AND(G221&gt;0,G221&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="222" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B222" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5847,11 +7647,15 @@
         <v/>
       </c>
       <c r="G222" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="223" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H222" t="str" cm="1">
+        <f t="array" ref="H222">_xlfn.IFS(G222="","",G222&gt;1000,"Hard",AND(G222&gt;150,G222&lt;=1000),"Medium",AND(G222&gt;0,G222&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="223" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B223" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5865,11 +7669,15 @@
         <v/>
       </c>
       <c r="G223" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="224" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H223" t="str" cm="1">
+        <f t="array" ref="H223">_xlfn.IFS(G223="","",G223&gt;1000,"Hard",AND(G223&gt;150,G223&lt;=1000),"Medium",AND(G223&gt;0,G223&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="224" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B224" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5883,11 +7691,15 @@
         <v/>
       </c>
       <c r="G224" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="225" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H224" t="str" cm="1">
+        <f t="array" ref="H224">_xlfn.IFS(G224="","",G224&gt;1000,"Hard",AND(G224&gt;150,G224&lt;=1000),"Medium",AND(G224&gt;0,G224&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="225" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B225" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5901,11 +7713,15 @@
         <v/>
       </c>
       <c r="G225" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="226" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H225" t="str" cm="1">
+        <f t="array" ref="H225">_xlfn.IFS(G225="","",G225&gt;1000,"Hard",AND(G225&gt;150,G225&lt;=1000),"Medium",AND(G225&gt;0,G225&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="226" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B226" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5919,11 +7735,15 @@
         <v/>
       </c>
       <c r="G226" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="227" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H226" t="str" cm="1">
+        <f t="array" ref="H226">_xlfn.IFS(G226="","",G226&gt;1000,"Hard",AND(G226&gt;150,G226&lt;=1000),"Medium",AND(G226&gt;0,G226&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="227" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B227" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5937,11 +7757,15 @@
         <v/>
       </c>
       <c r="G227" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="228" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H227" t="str" cm="1">
+        <f t="array" ref="H227">_xlfn.IFS(G227="","",G227&gt;1000,"Hard",AND(G227&gt;150,G227&lt;=1000),"Medium",AND(G227&gt;0,G227&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="228" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B228" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5955,11 +7779,15 @@
         <v/>
       </c>
       <c r="G228" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="229" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H228" t="str" cm="1">
+        <f t="array" ref="H228">_xlfn.IFS(G228="","",G228&gt;1000,"Hard",AND(G228&gt;150,G228&lt;=1000),"Medium",AND(G228&gt;0,G228&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="229" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B229" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5973,11 +7801,15 @@
         <v/>
       </c>
       <c r="G229" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="230" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H229" t="str" cm="1">
+        <f t="array" ref="H229">_xlfn.IFS(G229="","",G229&gt;1000,"Hard",AND(G229&gt;150,G229&lt;=1000),"Medium",AND(G229&gt;0,G229&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="230" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B230" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5991,11 +7823,15 @@
         <v/>
       </c>
       <c r="G230" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="231" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H230" t="str" cm="1">
+        <f t="array" ref="H230">_xlfn.IFS(G230="","",G230&gt;1000,"Hard",AND(G230&gt;150,G230&lt;=1000),"Medium",AND(G230&gt;0,G230&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="231" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B231" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6009,11 +7845,15 @@
         <v/>
       </c>
       <c r="G231" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="232" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H231" t="str" cm="1">
+        <f t="array" ref="H231">_xlfn.IFS(G231="","",G231&gt;1000,"Hard",AND(G231&gt;150,G231&lt;=1000),"Medium",AND(G231&gt;0,G231&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="232" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B232" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6027,11 +7867,15 @@
         <v/>
       </c>
       <c r="G232" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="233" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H232" t="str" cm="1">
+        <f t="array" ref="H232">_xlfn.IFS(G232="","",G232&gt;1000,"Hard",AND(G232&gt;150,G232&lt;=1000),"Medium",AND(G232&gt;0,G232&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="233" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B233" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6045,11 +7889,15 @@
         <v/>
       </c>
       <c r="G233" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="234" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H233" t="str" cm="1">
+        <f t="array" ref="H233">_xlfn.IFS(G233="","",G233&gt;1000,"Hard",AND(G233&gt;150,G233&lt;=1000),"Medium",AND(G233&gt;0,G233&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="234" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B234" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6063,11 +7911,15 @@
         <v/>
       </c>
       <c r="G234" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="235" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H234" t="str" cm="1">
+        <f t="array" ref="H234">_xlfn.IFS(G234="","",G234&gt;1000,"Hard",AND(G234&gt;150,G234&lt;=1000),"Medium",AND(G234&gt;0,G234&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="235" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B235" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6081,11 +7933,15 @@
         <v/>
       </c>
       <c r="G235" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="236" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H235" t="str" cm="1">
+        <f t="array" ref="H235">_xlfn.IFS(G235="","",G235&gt;1000,"Hard",AND(G235&gt;150,G235&lt;=1000),"Medium",AND(G235&gt;0,G235&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="236" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B236" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6099,11 +7955,15 @@
         <v/>
       </c>
       <c r="G236" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="237" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H236" t="str" cm="1">
+        <f t="array" ref="H236">_xlfn.IFS(G236="","",G236&gt;1000,"Hard",AND(G236&gt;150,G236&lt;=1000),"Medium",AND(G236&gt;0,G236&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="237" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B237" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6117,11 +7977,15 @@
         <v/>
       </c>
       <c r="G237" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="238" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H237" t="str" cm="1">
+        <f t="array" ref="H237">_xlfn.IFS(G237="","",G237&gt;1000,"Hard",AND(G237&gt;150,G237&lt;=1000),"Medium",AND(G237&gt;0,G237&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="238" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B238" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6135,11 +7999,15 @@
         <v/>
       </c>
       <c r="G238" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="239" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H238" t="str" cm="1">
+        <f t="array" ref="H238">_xlfn.IFS(G238="","",G238&gt;1000,"Hard",AND(G238&gt;150,G238&lt;=1000),"Medium",AND(G238&gt;0,G238&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="239" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B239" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6153,11 +8021,15 @@
         <v/>
       </c>
       <c r="G239" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="240" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H239" t="str" cm="1">
+        <f t="array" ref="H239">_xlfn.IFS(G239="","",G239&gt;1000,"Hard",AND(G239&gt;150,G239&lt;=1000),"Medium",AND(G239&gt;0,G239&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="240" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B240" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6171,11 +8043,15 @@
         <v/>
       </c>
       <c r="G240" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="241" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H240" t="str" cm="1">
+        <f t="array" ref="H240">_xlfn.IFS(G240="","",G240&gt;1000,"Hard",AND(G240&gt;150,G240&lt;=1000),"Medium",AND(G240&gt;0,G240&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="241" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B241" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6189,11 +8065,15 @@
         <v/>
       </c>
       <c r="G241" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="242" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H241" t="str" cm="1">
+        <f t="array" ref="H241">_xlfn.IFS(G241="","",G241&gt;1000,"Hard",AND(G241&gt;150,G241&lt;=1000),"Medium",AND(G241&gt;0,G241&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="242" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B242" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6207,11 +8087,15 @@
         <v/>
       </c>
       <c r="G242" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="243" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H242" t="str" cm="1">
+        <f t="array" ref="H242">_xlfn.IFS(G242="","",G242&gt;1000,"Hard",AND(G242&gt;150,G242&lt;=1000),"Medium",AND(G242&gt;0,G242&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="243" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B243" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6225,11 +8109,15 @@
         <v/>
       </c>
       <c r="G243" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="244" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H243" t="str" cm="1">
+        <f t="array" ref="H243">_xlfn.IFS(G243="","",G243&gt;1000,"Hard",AND(G243&gt;150,G243&lt;=1000),"Medium",AND(G243&gt;0,G243&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="244" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B244" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6243,11 +8131,15 @@
         <v/>
       </c>
       <c r="G244" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="245" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H244" t="str" cm="1">
+        <f t="array" ref="H244">_xlfn.IFS(G244="","",G244&gt;1000,"Hard",AND(G244&gt;150,G244&lt;=1000),"Medium",AND(G244&gt;0,G244&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="245" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B245" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6261,11 +8153,15 @@
         <v/>
       </c>
       <c r="G245" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="246" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H245" t="str" cm="1">
+        <f t="array" ref="H245">_xlfn.IFS(G245="","",G245&gt;1000,"Hard",AND(G245&gt;150,G245&lt;=1000),"Medium",AND(G245&gt;0,G245&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="246" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B246" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6279,11 +8175,15 @@
         <v/>
       </c>
       <c r="G246" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="247" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H246" t="str" cm="1">
+        <f t="array" ref="H246">_xlfn.IFS(G246="","",G246&gt;1000,"Hard",AND(G246&gt;150,G246&lt;=1000),"Medium",AND(G246&gt;0,G246&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="247" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B247" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6297,11 +8197,15 @@
         <v/>
       </c>
       <c r="G247" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="248" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H247" t="str" cm="1">
+        <f t="array" ref="H247">_xlfn.IFS(G247="","",G247&gt;1000,"Hard",AND(G247&gt;150,G247&lt;=1000),"Medium",AND(G247&gt;0,G247&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="248" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B248" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6315,11 +8219,15 @@
         <v/>
       </c>
       <c r="G248" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="249" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H248" t="str" cm="1">
+        <f t="array" ref="H248">_xlfn.IFS(G248="","",G248&gt;1000,"Hard",AND(G248&gt;150,G248&lt;=1000),"Medium",AND(G248&gt;0,G248&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="249" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B249" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6333,11 +8241,15 @@
         <v/>
       </c>
       <c r="G249" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="250" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H249" t="str" cm="1">
+        <f t="array" ref="H249">_xlfn.IFS(G249="","",G249&gt;1000,"Hard",AND(G249&gt;150,G249&lt;=1000),"Medium",AND(G249&gt;0,G249&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="250" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B250" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6351,11 +8263,15 @@
         <v/>
       </c>
       <c r="G250" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="251" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H250" t="str" cm="1">
+        <f t="array" ref="H250">_xlfn.IFS(G250="","",G250&gt;1000,"Hard",AND(G250&gt;150,G250&lt;=1000),"Medium",AND(G250&gt;0,G250&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="251" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B251" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6369,11 +8285,15 @@
         <v/>
       </c>
       <c r="G251" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="252" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H251" t="str" cm="1">
+        <f t="array" ref="H251">_xlfn.IFS(G251="","",G251&gt;1000,"Hard",AND(G251&gt;150,G251&lt;=1000),"Medium",AND(G251&gt;0,G251&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="252" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B252" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6387,11 +8307,15 @@
         <v/>
       </c>
       <c r="G252" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="253" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H252" t="str" cm="1">
+        <f t="array" ref="H252">_xlfn.IFS(G252="","",G252&gt;1000,"Hard",AND(G252&gt;150,G252&lt;=1000),"Medium",AND(G252&gt;0,G252&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="253" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B253" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6405,11 +8329,15 @@
         <v/>
       </c>
       <c r="G253" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="254" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H253" t="str" cm="1">
+        <f t="array" ref="H253">_xlfn.IFS(G253="","",G253&gt;1000,"Hard",AND(G253&gt;150,G253&lt;=1000),"Medium",AND(G253&gt;0,G253&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="254" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B254" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6423,11 +8351,15 @@
         <v/>
       </c>
       <c r="G254" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="255" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H254" t="str" cm="1">
+        <f t="array" ref="H254">_xlfn.IFS(G254="","",G254&gt;1000,"Hard",AND(G254&gt;150,G254&lt;=1000),"Medium",AND(G254&gt;0,G254&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="255" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B255" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6441,11 +8373,15 @@
         <v/>
       </c>
       <c r="G255" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="256" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H255" t="str" cm="1">
+        <f t="array" ref="H255">_xlfn.IFS(G255="","",G255&gt;1000,"Hard",AND(G255&gt;150,G255&lt;=1000),"Medium",AND(G255&gt;0,G255&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="256" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B256" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6459,11 +8395,15 @@
         <v/>
       </c>
       <c r="G256" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="257" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H256" t="str" cm="1">
+        <f t="array" ref="H256">_xlfn.IFS(G256="","",G256&gt;1000,"Hard",AND(G256&gt;150,G256&lt;=1000),"Medium",AND(G256&gt;0,G256&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="257" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B257" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6477,11 +8417,15 @@
         <v/>
       </c>
       <c r="G257" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="258" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H257" t="str" cm="1">
+        <f t="array" ref="H257">_xlfn.IFS(G257="","",G257&gt;1000,"Hard",AND(G257&gt;150,G257&lt;=1000),"Medium",AND(G257&gt;0,G257&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="258" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B258" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6495,11 +8439,15 @@
         <v/>
       </c>
       <c r="G258" s="8" t="str">
-        <f t="shared" si="3"/>
-        <v/>
-      </c>
-    </row>
-    <row r="259" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="4"/>
+        <v/>
+      </c>
+      <c r="H258" t="str" cm="1">
+        <f t="array" ref="H258">_xlfn.IFS(G258="","",G258&gt;1000,"Hard",AND(G258&gt;150,G258&lt;=1000),"Medium",AND(G258&gt;0,G258&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="259" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B259" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6513,11 +8461,15 @@
         <v/>
       </c>
       <c r="G259" s="8" t="str">
-        <f t="shared" ref="G259:G300" si="4">IF(LEN(A259)=0,"",LEN(A259))</f>
-        <v/>
-      </c>
-    </row>
-    <row r="260" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" ref="G259:G300" si="5">IF(LEN(A259)=0,"",LEN(A259))</f>
+        <v/>
+      </c>
+      <c r="H259" t="str" cm="1">
+        <f t="array" ref="H259">_xlfn.IFS(G259="","",G259&gt;1000,"Hard",AND(G259&gt;150,G259&lt;=1000),"Medium",AND(G259&gt;0,G259&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="260" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B260" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6531,11 +8483,15 @@
         <v/>
       </c>
       <c r="G260" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="261" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H260" t="str" cm="1">
+        <f t="array" ref="H260">_xlfn.IFS(G260="","",G260&gt;1000,"Hard",AND(G260&gt;150,G260&lt;=1000),"Medium",AND(G260&gt;0,G260&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="261" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B261" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6549,11 +8505,15 @@
         <v/>
       </c>
       <c r="G261" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="262" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H261" t="str" cm="1">
+        <f t="array" ref="H261">_xlfn.IFS(G261="","",G261&gt;1000,"Hard",AND(G261&gt;150,G261&lt;=1000),"Medium",AND(G261&gt;0,G261&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="262" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B262" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6567,11 +8527,15 @@
         <v/>
       </c>
       <c r="G262" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="263" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H262" t="str" cm="1">
+        <f t="array" ref="H262">_xlfn.IFS(G262="","",G262&gt;1000,"Hard",AND(G262&gt;150,G262&lt;=1000),"Medium",AND(G262&gt;0,G262&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="263" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B263" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6585,11 +8549,15 @@
         <v/>
       </c>
       <c r="G263" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="264" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H263" t="str" cm="1">
+        <f t="array" ref="H263">_xlfn.IFS(G263="","",G263&gt;1000,"Hard",AND(G263&gt;150,G263&lt;=1000),"Medium",AND(G263&gt;0,G263&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="264" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B264" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6603,11 +8571,15 @@
         <v/>
       </c>
       <c r="G264" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="265" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H264" t="str" cm="1">
+        <f t="array" ref="H264">_xlfn.IFS(G264="","",G264&gt;1000,"Hard",AND(G264&gt;150,G264&lt;=1000),"Medium",AND(G264&gt;0,G264&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="265" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B265" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6621,11 +8593,15 @@
         <v/>
       </c>
       <c r="G265" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="266" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H265" t="str" cm="1">
+        <f t="array" ref="H265">_xlfn.IFS(G265="","",G265&gt;1000,"Hard",AND(G265&gt;150,G265&lt;=1000),"Medium",AND(G265&gt;0,G265&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="266" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B266" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6639,11 +8615,15 @@
         <v/>
       </c>
       <c r="G266" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="267" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H266" t="str" cm="1">
+        <f t="array" ref="H266">_xlfn.IFS(G266="","",G266&gt;1000,"Hard",AND(G266&gt;150,G266&lt;=1000),"Medium",AND(G266&gt;0,G266&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="267" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B267" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6657,11 +8637,15 @@
         <v/>
       </c>
       <c r="G267" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="268" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H267" t="str" cm="1">
+        <f t="array" ref="H267">_xlfn.IFS(G267="","",G267&gt;1000,"Hard",AND(G267&gt;150,G267&lt;=1000),"Medium",AND(G267&gt;0,G267&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="268" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B268" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6675,11 +8659,15 @@
         <v/>
       </c>
       <c r="G268" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="269" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H268" t="str" cm="1">
+        <f t="array" ref="H268">_xlfn.IFS(G268="","",G268&gt;1000,"Hard",AND(G268&gt;150,G268&lt;=1000),"Medium",AND(G268&gt;0,G268&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="269" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B269" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6693,11 +8681,15 @@
         <v/>
       </c>
       <c r="G269" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="270" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H269" t="str" cm="1">
+        <f t="array" ref="H269">_xlfn.IFS(G269="","",G269&gt;1000,"Hard",AND(G269&gt;150,G269&lt;=1000),"Medium",AND(G269&gt;0,G269&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="270" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B270" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6711,11 +8703,15 @@
         <v/>
       </c>
       <c r="G270" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="271" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H270" t="str" cm="1">
+        <f t="array" ref="H270">_xlfn.IFS(G270="","",G270&gt;1000,"Hard",AND(G270&gt;150,G270&lt;=1000),"Medium",AND(G270&gt;0,G270&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="271" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B271" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6729,11 +8725,15 @@
         <v/>
       </c>
       <c r="G271" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="272" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H271" t="str" cm="1">
+        <f t="array" ref="H271">_xlfn.IFS(G271="","",G271&gt;1000,"Hard",AND(G271&gt;150,G271&lt;=1000),"Medium",AND(G271&gt;0,G271&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="272" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B272" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6747,11 +8747,15 @@
         <v/>
       </c>
       <c r="G272" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="273" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H272" t="str" cm="1">
+        <f t="array" ref="H272">_xlfn.IFS(G272="","",G272&gt;1000,"Hard",AND(G272&gt;150,G272&lt;=1000),"Medium",AND(G272&gt;0,G272&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="273" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B273" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6765,11 +8769,15 @@
         <v/>
       </c>
       <c r="G273" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="274" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H273" t="str" cm="1">
+        <f t="array" ref="H273">_xlfn.IFS(G273="","",G273&gt;1000,"Hard",AND(G273&gt;150,G273&lt;=1000),"Medium",AND(G273&gt;0,G273&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="274" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B274" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6783,11 +8791,15 @@
         <v/>
       </c>
       <c r="G274" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="275" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H274" t="str" cm="1">
+        <f t="array" ref="H274">_xlfn.IFS(G274="","",G274&gt;1000,"Hard",AND(G274&gt;150,G274&lt;=1000),"Medium",AND(G274&gt;0,G274&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="275" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B275" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6801,11 +8813,15 @@
         <v/>
       </c>
       <c r="G275" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="276" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H275" t="str" cm="1">
+        <f t="array" ref="H275">_xlfn.IFS(G275="","",G275&gt;1000,"Hard",AND(G275&gt;150,G275&lt;=1000),"Medium",AND(G275&gt;0,G275&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="276" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B276" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6819,11 +8835,15 @@
         <v/>
       </c>
       <c r="G276" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="277" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H276" t="str" cm="1">
+        <f t="array" ref="H276">_xlfn.IFS(G276="","",G276&gt;1000,"Hard",AND(G276&gt;150,G276&lt;=1000),"Medium",AND(G276&gt;0,G276&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="277" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B277" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6837,11 +8857,15 @@
         <v/>
       </c>
       <c r="G277" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="278" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H277" t="str" cm="1">
+        <f t="array" ref="H277">_xlfn.IFS(G277="","",G277&gt;1000,"Hard",AND(G277&gt;150,G277&lt;=1000),"Medium",AND(G277&gt;0,G277&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="278" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B278" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6855,11 +8879,15 @@
         <v/>
       </c>
       <c r="G278" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="279" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H278" t="str" cm="1">
+        <f t="array" ref="H278">_xlfn.IFS(G278="","",G278&gt;1000,"Hard",AND(G278&gt;150,G278&lt;=1000),"Medium",AND(G278&gt;0,G278&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="279" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B279" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6873,11 +8901,15 @@
         <v/>
       </c>
       <c r="G279" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="280" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H279" t="str" cm="1">
+        <f t="array" ref="H279">_xlfn.IFS(G279="","",G279&gt;1000,"Hard",AND(G279&gt;150,G279&lt;=1000),"Medium",AND(G279&gt;0,G279&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="280" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B280" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6891,11 +8923,15 @@
         <v/>
       </c>
       <c r="G280" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="281" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H280" t="str" cm="1">
+        <f t="array" ref="H280">_xlfn.IFS(G280="","",G280&gt;1000,"Hard",AND(G280&gt;150,G280&lt;=1000),"Medium",AND(G280&gt;0,G280&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="281" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B281" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6909,11 +8945,15 @@
         <v/>
       </c>
       <c r="G281" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="282" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H281" t="str" cm="1">
+        <f t="array" ref="H281">_xlfn.IFS(G281="","",G281&gt;1000,"Hard",AND(G281&gt;150,G281&lt;=1000),"Medium",AND(G281&gt;0,G281&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="282" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B282" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6927,11 +8967,15 @@
         <v/>
       </c>
       <c r="G282" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="283" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H282" t="str" cm="1">
+        <f t="array" ref="H282">_xlfn.IFS(G282="","",G282&gt;1000,"Hard",AND(G282&gt;150,G282&lt;=1000),"Medium",AND(G282&gt;0,G282&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="283" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B283" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6945,11 +8989,15 @@
         <v/>
       </c>
       <c r="G283" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="284" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H283" t="str" cm="1">
+        <f t="array" ref="H283">_xlfn.IFS(G283="","",G283&gt;1000,"Hard",AND(G283&gt;150,G283&lt;=1000),"Medium",AND(G283&gt;0,G283&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="284" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B284" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6963,11 +9011,15 @@
         <v/>
       </c>
       <c r="G284" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="285" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H284" t="str" cm="1">
+        <f t="array" ref="H284">_xlfn.IFS(G284="","",G284&gt;1000,"Hard",AND(G284&gt;150,G284&lt;=1000),"Medium",AND(G284&gt;0,G284&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="285" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B285" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6981,11 +9033,15 @@
         <v/>
       </c>
       <c r="G285" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="286" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H285" t="str" cm="1">
+        <f t="array" ref="H285">_xlfn.IFS(G285="","",G285&gt;1000,"Hard",AND(G285&gt;150,G285&lt;=1000),"Medium",AND(G285&gt;0,G285&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="286" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B286" s="5" t="str">
         <f>""</f>
         <v/>
@@ -6999,11 +9055,15 @@
         <v/>
       </c>
       <c r="G286" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="287" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H286" t="str" cm="1">
+        <f t="array" ref="H286">_xlfn.IFS(G286="","",G286&gt;1000,"Hard",AND(G286&gt;150,G286&lt;=1000),"Medium",AND(G286&gt;0,G286&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="287" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B287" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7017,11 +9077,15 @@
         <v/>
       </c>
       <c r="G287" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="288" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H287" t="str" cm="1">
+        <f t="array" ref="H287">_xlfn.IFS(G287="","",G287&gt;1000,"Hard",AND(G287&gt;150,G287&lt;=1000),"Medium",AND(G287&gt;0,G287&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="288" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B288" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7035,11 +9099,15 @@
         <v/>
       </c>
       <c r="G288" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="289" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H288" t="str" cm="1">
+        <f t="array" ref="H288">_xlfn.IFS(G288="","",G288&gt;1000,"Hard",AND(G288&gt;150,G288&lt;=1000),"Medium",AND(G288&gt;0,G288&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="289" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B289" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7053,11 +9121,15 @@
         <v/>
       </c>
       <c r="G289" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="290" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H289" t="str" cm="1">
+        <f t="array" ref="H289">_xlfn.IFS(G289="","",G289&gt;1000,"Hard",AND(G289&gt;150,G289&lt;=1000),"Medium",AND(G289&gt;0,G289&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="290" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B290" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7071,11 +9143,15 @@
         <v/>
       </c>
       <c r="G290" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="291" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H290" t="str" cm="1">
+        <f t="array" ref="H290">_xlfn.IFS(G290="","",G290&gt;1000,"Hard",AND(G290&gt;150,G290&lt;=1000),"Medium",AND(G290&gt;0,G290&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="291" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B291" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7089,11 +9165,15 @@
         <v/>
       </c>
       <c r="G291" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="292" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H291" t="str" cm="1">
+        <f t="array" ref="H291">_xlfn.IFS(G291="","",G291&gt;1000,"Hard",AND(G291&gt;150,G291&lt;=1000),"Medium",AND(G291&gt;0,G291&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="292" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B292" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7107,11 +9187,15 @@
         <v/>
       </c>
       <c r="G292" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="293" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H292" t="str" cm="1">
+        <f t="array" ref="H292">_xlfn.IFS(G292="","",G292&gt;1000,"Hard",AND(G292&gt;150,G292&lt;=1000),"Medium",AND(G292&gt;0,G292&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="293" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B293" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7125,11 +9209,15 @@
         <v/>
       </c>
       <c r="G293" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="294" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H293" t="str" cm="1">
+        <f t="array" ref="H293">_xlfn.IFS(G293="","",G293&gt;1000,"Hard",AND(G293&gt;150,G293&lt;=1000),"Medium",AND(G293&gt;0,G293&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="294" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B294" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7143,11 +9231,15 @@
         <v/>
       </c>
       <c r="G294" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="295" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H294" t="str" cm="1">
+        <f t="array" ref="H294">_xlfn.IFS(G294="","",G294&gt;1000,"Hard",AND(G294&gt;150,G294&lt;=1000),"Medium",AND(G294&gt;0,G294&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="295" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B295" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7161,11 +9253,15 @@
         <v/>
       </c>
       <c r="G295" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="296" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H295" t="str" cm="1">
+        <f t="array" ref="H295">_xlfn.IFS(G295="","",G295&gt;1000,"Hard",AND(G295&gt;150,G295&lt;=1000),"Medium",AND(G295&gt;0,G295&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="296" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B296" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7179,11 +9275,15 @@
         <v/>
       </c>
       <c r="G296" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="297" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H296" t="str" cm="1">
+        <f t="array" ref="H296">_xlfn.IFS(G296="","",G296&gt;1000,"Hard",AND(G296&gt;150,G296&lt;=1000),"Medium",AND(G296&gt;0,G296&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="297" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B297" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7197,11 +9297,15 @@
         <v/>
       </c>
       <c r="G297" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="298" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H297" t="str" cm="1">
+        <f t="array" ref="H297">_xlfn.IFS(G297="","",G297&gt;1000,"Hard",AND(G297&gt;150,G297&lt;=1000),"Medium",AND(G297&gt;0,G297&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="298" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B298" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7215,11 +9319,15 @@
         <v/>
       </c>
       <c r="G298" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="299" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H298" t="str" cm="1">
+        <f t="array" ref="H298">_xlfn.IFS(G298="","",G298&gt;1000,"Hard",AND(G298&gt;150,G298&lt;=1000),"Medium",AND(G298&gt;0,G298&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="299" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B299" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7233,11 +9341,15 @@
         <v/>
       </c>
       <c r="G299" s="8" t="str">
-        <f t="shared" si="4"/>
-        <v/>
-      </c>
-    </row>
-    <row r="300" spans="2:7" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.35">
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H299" t="str" cm="1">
+        <f t="array" ref="H299">_xlfn.IFS(G299="","",G299&gt;1000,"Hard",AND(G299&gt;150,G299&lt;=1000),"Medium",AND(G299&gt;0,G299&lt;=150),"Easy")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="300" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B300" s="5" t="str">
         <f>""</f>
         <v/>
@@ -7251,7 +9363,11 @@
         <v/>
       </c>
       <c r="G300" s="8" t="str">
-        <f t="shared" si="4"/>
+        <f t="shared" si="5"/>
+        <v/>
+      </c>
+      <c r="H300" t="str" cm="1">
+        <f t="array" ref="H300">_xlfn.IFS(G300="","",G300&gt;1000,"Hard",AND(G300&gt;150,G300&lt;=1000),"Medium",AND(G300&gt;0,G300&lt;=150),"Easy")</f>
         <v/>
       </c>
     </row>
@@ -7260,12 +9376,18 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{18F672AA-1B6A-4B7E-8DFD-8F8C9B817B80}">
           <x14:formula1>
             <xm:f>Reference!$A$2:$A$84</xm:f>
           </x14:formula1>
           <xm:sqref>C1:C1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A7FA73B3-11E3-47B9-89F7-B5B7D3A8C32E}">
+          <x14:formula1>
+            <xm:f>Reference!$B$2:$B$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>H2:H1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7276,84 +9398,84 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E0A8A7CF-4CD4-4711-9263-846931855D3C}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:1" ht="25.8" x14ac:dyDescent="0.5">
+    <row r="1" spans="1:1" ht="26.25" x14ac:dyDescent="0.4">
       <c r="A1" s="1" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>137</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>139</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>141</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>143</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>145</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>146</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>147</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>148</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>150</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>151</v>
       </c>
@@ -7366,41 +9488,41 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C645F4B-34D2-4DB1-A544-892297E89749}">
   <dimension ref="A1:B84"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B1" t="s">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>3</v>
       </c>
-      <c r="B2" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B2" t="s">
+        <v>226</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>4</v>
       </c>
-      <c r="B3" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B3" t="s">
+        <v>227</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>5</v>
       </c>
-      <c r="B4" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>6</v>
       </c>
@@ -7409,7 +9531,7 @@
         <v/>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>7</v>
       </c>
@@ -7418,7 +9540,7 @@
         <v/>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>8</v>
       </c>
@@ -7427,7 +9549,7 @@
         <v/>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>9</v>
       </c>
@@ -7436,7 +9558,7 @@
         <v/>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>10</v>
       </c>
@@ -7445,7 +9567,7 @@
         <v/>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>11</v>
       </c>
@@ -7454,7 +9576,7 @@
         <v/>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>12</v>
       </c>
@@ -7463,7 +9585,7 @@
         <v/>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>13</v>
       </c>
@@ -7472,7 +9594,7 @@
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>14</v>
       </c>
@@ -7481,7 +9603,7 @@
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>15</v>
       </c>
@@ -7490,7 +9612,7 @@
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>16</v>
       </c>
@@ -7499,7 +9621,7 @@
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>17</v>
       </c>
@@ -7508,7 +9630,7 @@
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -7517,7 +9639,7 @@
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>19</v>
       </c>
@@ -7526,7 +9648,7 @@
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -7535,7 +9657,7 @@
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -7544,7 +9666,7 @@
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -7553,7 +9675,7 @@
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -7562,7 +9684,7 @@
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -7571,7 +9693,7 @@
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -7580,7 +9702,7 @@
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
@@ -7589,7 +9711,7 @@
         <v/>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A26" t="s">
         <v>27</v>
       </c>
@@ -7598,7 +9720,7 @@
         <v/>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A27" t="s">
         <v>28</v>
       </c>
@@ -7607,7 +9729,7 @@
         <v/>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A28" t="s">
         <v>29</v>
       </c>
@@ -7616,7 +9738,7 @@
         <v/>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A29" t="s">
         <v>30</v>
       </c>
@@ -7625,7 +9747,7 @@
         <v/>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A30" t="s">
         <v>31</v>
       </c>
@@ -7634,7 +9756,7 @@
         <v/>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A31" t="s">
         <v>32</v>
       </c>
@@ -7643,7 +9765,7 @@
         <v/>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A32" t="s">
         <v>33</v>
       </c>
@@ -7652,7 +9774,7 @@
         <v/>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A33" t="s">
         <v>34</v>
       </c>
@@ -7661,7 +9783,7 @@
         <v/>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A34" t="s">
         <v>35</v>
       </c>
@@ -7670,7 +9792,7 @@
         <v/>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A35" t="s">
         <v>36</v>
       </c>
@@ -7679,7 +9801,7 @@
         <v/>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A36" t="s">
         <v>37</v>
       </c>
@@ -7688,7 +9810,7 @@
         <v/>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A37" t="s">
         <v>38</v>
       </c>
@@ -7697,7 +9819,7 @@
         <v/>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A38" t="s">
         <v>39</v>
       </c>
@@ -7706,7 +9828,7 @@
         <v/>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A39" t="s">
         <v>40</v>
       </c>
@@ -7715,7 +9837,7 @@
         <v/>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A40" t="s">
         <v>41</v>
       </c>
@@ -7724,7 +9846,7 @@
         <v/>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A41" t="s">
         <v>42</v>
       </c>
@@ -7733,7 +9855,7 @@
         <v/>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A42" t="s">
         <v>43</v>
       </c>
@@ -7742,7 +9864,7 @@
         <v/>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A43" t="s">
         <v>44</v>
       </c>
@@ -7751,7 +9873,7 @@
         <v/>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A44" t="s">
         <v>45</v>
       </c>
@@ -7760,7 +9882,7 @@
         <v/>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A45" t="s">
         <v>46</v>
       </c>
@@ -7769,7 +9891,7 @@
         <v/>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A46" t="s">
         <v>47</v>
       </c>
@@ -7778,7 +9900,7 @@
         <v/>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A47" t="s">
         <v>48</v>
       </c>
@@ -7787,7 +9909,7 @@
         <v/>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A48" t="s">
         <v>49</v>
       </c>
@@ -7796,7 +9918,7 @@
         <v/>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A49" t="s">
         <v>50</v>
       </c>
@@ -7805,7 +9927,7 @@
         <v/>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A50" t="s">
         <v>51</v>
       </c>
@@ -7814,7 +9936,7 @@
         <v/>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A51" t="s">
         <v>52</v>
       </c>
@@ -7823,7 +9945,7 @@
         <v/>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A52" t="s">
         <v>53</v>
       </c>
@@ -7832,7 +9954,7 @@
         <v/>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A53" t="s">
         <v>54</v>
       </c>
@@ -7841,7 +9963,7 @@
         <v/>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A54" t="s">
         <v>55</v>
       </c>
@@ -7850,7 +9972,7 @@
         <v/>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A55" t="s">
         <v>56</v>
       </c>
@@ -7859,7 +9981,7 @@
         <v/>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A56" t="s">
         <v>57</v>
       </c>
@@ -7868,7 +9990,7 @@
         <v/>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A57" t="s">
         <v>58</v>
       </c>
@@ -7877,7 +9999,7 @@
         <v/>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A58" t="s">
         <v>59</v>
       </c>
@@ -7886,7 +10008,7 @@
         <v/>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A59" t="s">
         <v>60</v>
       </c>
@@ -7895,7 +10017,7 @@
         <v/>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A60" t="s">
         <v>61</v>
       </c>
@@ -7904,7 +10026,7 @@
         <v/>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A61" t="s">
         <v>62</v>
       </c>
@@ -7913,7 +10035,7 @@
         <v/>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A62" t="s">
         <v>63</v>
       </c>
@@ -7922,7 +10044,7 @@
         <v/>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A63" t="s">
         <v>64</v>
       </c>
@@ -7931,7 +10053,7 @@
         <v/>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A64" t="s">
         <v>65</v>
       </c>
@@ -7940,7 +10062,7 @@
         <v/>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A65" t="s">
         <v>66</v>
       </c>
@@ -7949,7 +10071,7 @@
         <v/>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A66" t="s">
         <v>67</v>
       </c>
@@ -7958,7 +10080,7 @@
         <v/>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A67" t="s">
         <v>68</v>
       </c>
@@ -7967,7 +10089,7 @@
         <v/>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A68" t="s">
         <v>69</v>
       </c>
@@ -7976,7 +10098,7 @@
         <v/>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A69" t="s">
         <v>70</v>
       </c>
@@ -7985,7 +10107,7 @@
         <v/>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A70" t="s">
         <v>71</v>
       </c>
@@ -7994,7 +10116,7 @@
         <v/>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A71" t="s">
         <v>72</v>
       </c>
@@ -8003,7 +10125,7 @@
         <v/>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A72" t="s">
         <v>73</v>
       </c>
@@ -8012,7 +10134,7 @@
         <v/>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A73" t="s">
         <v>74</v>
       </c>
@@ -8021,7 +10143,7 @@
         <v/>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A74" t="s">
         <v>75</v>
       </c>
@@ -8030,7 +10152,7 @@
         <v/>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A75" t="s">
         <v>76</v>
       </c>
@@ -8039,7 +10161,7 @@
         <v/>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A76" t="s">
         <v>77</v>
       </c>
@@ -8048,7 +10170,7 @@
         <v/>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A77" t="s">
         <v>78</v>
       </c>
@@ -8057,7 +10179,7 @@
         <v/>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A78" t="s">
         <v>79</v>
       </c>
@@ -8066,7 +10188,7 @@
         <v/>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A79" t="s">
         <v>80</v>
       </c>
@@ -8075,7 +10197,7 @@
         <v/>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A80" t="s">
         <v>81</v>
       </c>
@@ -8084,7 +10206,7 @@
         <v/>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A81" t="s">
         <v>82</v>
       </c>
@@ -8093,7 +10215,7 @@
         <v/>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A82" t="s">
         <v>83</v>
       </c>
@@ -8102,7 +10224,7 @@
         <v/>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A83" t="s">
         <v>84</v>
       </c>
@@ -8111,7 +10233,7 @@
         <v/>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A84" t="s">
         <v>85</v>
       </c>

--- a/New Files/Problem Repository.xlsx
+++ b/New Files/Problem Repository.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pomf\Documents\GitHub\calculus-worksheets\New Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97D56604-0520-4270-A0B9-026927E5B254}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D7C309-45C4-4731-958F-96A35AF80F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19365" windowHeight="21285" xr2:uid="{D3F02B99-6D0D-4708-8A55-E87CA732C5E2}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21420" activeTab="1" xr2:uid="{D3F02B99-6D0D-4708-8A55-E87CA732C5E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>

--- a/New Files/Problem Repository.xlsx
+++ b/New Files/Problem Repository.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Pomf\Documents\GitHub\calculus-worksheets\New Files\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F3D7C309-45C4-4731-958F-96A35AF80F04}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D5A01B48-1FD0-4FB6-8FFE-736D58C9695F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21420" activeTab="1" xr2:uid="{D3F02B99-6D0D-4708-8A55-E87CA732C5E2}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15800" xr2:uid="{D3F02B99-6D0D-4708-8A55-E87CA732C5E2}"/>
   </bookViews>
   <sheets>
     <sheet name="Main" sheetId="1" r:id="rId1"/>
@@ -60,7 +60,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="460" uniqueCount="229">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="544" uniqueCount="273">
   <si>
     <t>Question</t>
   </si>
@@ -1208,6 +1208,386 @@
   </si>
   <si>
     <t>Hard</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convert between degrees and radians: $180^{\circ}=$ </t>
+  </si>
+  <si>
+    <t>$\pi$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convert between degrees and radians: $30^{\circ}=$ </t>
+  </si>
+  <si>
+    <t>$\displaystyle \frac{\pi}{6}$</t>
+  </si>
+  <si>
+    <t>Convert between degrees and radians: $135^{\circ}=$</t>
+  </si>
+  <si>
+    <t>$\displaystyle \frac{3\pi}{4}$</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Convert between degrees and radians: $\displaystyle \frac{\pi}{4}=$ </t>
+  </si>
+  <si>
+    <t>$45^{\circ}$</t>
+  </si>
+  <si>
+    <t>Convert between degrees and radians: $\displaystyle \frac{3\pi}{2}=$</t>
+  </si>
+  <si>
+    <t>$270^{\circ}$</t>
+  </si>
+  <si>
+    <t>Convert between degrees and radians: $\displaystyle \frac{11\pi}{6}=$</t>
+  </si>
+  <si>
+    <t>$330^{\circ}$</t>
+  </si>
+  <si>
+    <t>0.1 Precalc</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate the trigonometric value: $\displaystyle \sin{(3\pi)}=$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate the trigonometric value:  $\displaystyle \sin{\left(-\frac{\pi}{6} \right)}=$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate the trigonometric value: $\displaystyle \cos{\left( \frac{5\pi}{4} \right)}=$ </t>
+  </si>
+  <si>
+    <t xml:space="preserve">Calculate the trigonometric value: $\displaystyle \sec{\left( \frac{5\pi}{3} \right)}=$ </t>
+  </si>
+  <si>
+    <t>Calculate the trigonometric value: $\displaystyle \tan{\left(\frac{7\pi}{6} \right)}=$</t>
+  </si>
+  <si>
+    <t>Calculate the trigonometric value: $\displaystyle \tan{\left(-\frac{3\pi}{2}\right)}=$</t>
+  </si>
+  <si>
+    <t>$0$</t>
+  </si>
+  <si>
+    <t>$\displaystyle-\frac{1}{2}$</t>
+  </si>
+  <si>
+    <t>$\displaystyle -\frac{\sqrt{2}}{2}$</t>
+  </si>
+  <si>
+    <t>$2$</t>
+  </si>
+  <si>
+    <t>$\displaystyle \frac{\sqrt{3}}{3}$</t>
+  </si>
+  <si>
+    <t>undefined</t>
+  </si>
+  <si>
+    <t>Review trig identities: match each expression on the left with all expressions on the right that produce a trig identity.
+\vspace{.1in}
+\begin{tikzpicture}
+\node at (0, 7) [right] {(1) $\cos^2{x} =$};
+% \draw[blue,thick, opacity=\opsol] (2.6,7) -- (9,8);
+% \draw[blue,thick, opacity=\opsol] (2.6,7) -- (9,5);
+\node at (0, 5) [right] {(2) $\sin{(2x)=}$};
+% \draw[blue,thick, opacity=\opsol] (2.6,5) -- (9,4);
+\node at (0, 3) [ right] {(3) $\cos{(2x)}=$};
+% \draw[blue,thick, opacity=\opsol] (2.6,3) -- (9,6);
+% \draw[blue,thick, opacity=\opsol] (2.6,3) -- (9,2);
+% \draw[blue,thick, opacity=\opsol] (2.6,3) -- (9,1);
+\node at (0, 1) [ right] {(4) $\sin^2x$=};
+% \draw[blue,thick, opacity=\opsol] (2.6,1) -- (9,3);
+% \draw[blue,thick, opacity=\opsol] (2.6,1) -- (9,7);
+\node at (9, 8) [ right] {(a) $1-\sin^2{x}$};
+\node at (9, 7) [ right] {(b) $\frac{1}{2}(1-\cos{2x})$};
+\node at (9, 6) [ right] {(c)
+ $\cos^2{x}-\sin^2{x}$};
+\node at (9, 5) [ right] {(d)
+ $\frac{1}{2}(1+\cos{2x})$};
+\node at (9, 4) [ right] {(e)
+ $2\sin{x}\cos{x}$};
+\node at (9, 3) [ right] {(f) $1-\cos^2{x}$};
+\node at (9, 2) [ right] {(g) $1-2\sin^2{x}$};
+\node at (9, 1) [ right] {(h) $2\cos^2{x}-1$};
+\node at (9, 0) [ right] {(i) $\cos^2{x}+\sin^2{x}$};
+\end{tikzpicture}</t>
+  </si>
+  <si>
+    <t>\begin{tikzpicture}
+\node at (0, 7) [right] {(1) $\cos^2{x} =$};
+\draw[blue,thick, opacity=\opsol] (2.6,7) -- (9,8);
+\draw[blue,thick, opacity=\opsol] (2.6,7) -- (9,5);
+\node at (0, 5) [right] {(2) $\sin{(2x)=}$};
+\draw[blue,thick, opacity=\opsol] (2.6,5) -- (9,4);
+\node at (0, 3) [ right] {(3) $\cos{(2x)}=$};
+\draw[blue,thick, opacity=\opsol] (2.6,3) -- (9,6);
+\draw[blue,thick, opacity=\opsol] (2.6,3) -- (9,2);
+\draw[blue,thick, opacity=\opsol] (2.6,3) -- (9,1);
+\node at (0, 1) [ right] {(4) $\sin^2x$=};
+\draw[blue,thick, opacity=\opsol] (2.6,1) -- (9,3);
+\draw[blue,thick, opacity=\opsol] (2.6,1) -- (9,7);
+\node at (9, 8) [ right] {(a) $1-\sin^2{x}$};
+\node at (9, 7) [ right] {(b) $\frac{1}{2}(1-\cos{2x})$};
+\node at (9, 6) [ right] {(c)
+ $\cos^2{x}-\sin^2{x}$};
+\node at (9, 5) [ right] {(d)
+ $\frac{1}{2}(1+\cos{2x})$};
+\node at (9, 4) [ right] {(e)
+ $2\sin{x}\cos{x}$};
+\node at (9, 3) [ right] {(f) $1-\cos^2{x}$};
+\node at (9, 2) [ right] {(g) $1-2\sin^2{x}$};
+\node at (9, 1) [ right] {(h) $2\cos^2{x}-1$};
+\node at (9, 0) [ right] {(i) $\cos^2{x}+\sin^2{x}$};
+\end{tikzpicture}</t>
+  </si>
+  <si>
+    <t>A 15-foot long ladder is leaning against a wall
+with its base 2 feet from the wall.  Find the angle the ladder makes with the floor.  Use a calculator to compute the answer in radians and in degrees.</t>
+  </si>
+  <si>
+    <t>\begin{wrapfigure}{l}{4cm}
+\begin{tikzpicture}[scale =0.3]
+\pgfmathsetmacro{\Arad}{.75}%
+\pgfmathsetmacro{\Angle}{97.66}%
+\pgfmathsetmacro{\XValueArc}{\Arad*cos(\Angle)}%
+\pgfmathsetmacro{\YValueArc}{\Arad*sin(\Angle)}%
+\draw [thick] ($(2,0)+(\XValueArc,\YValueArc)$) %starting point of the arc
+    arc (\Angle:180:\Arad); %(starting angle, ending angle, radius)
+\draw [ultra thick] (0,0) -- (6,0);% Horizontal
+\draw [ultra thick] (0,0) -- (0,15);% Vert
+\draw [ultra thick] (2,0) -- (0,14.8); %Top
+\node at (2.5,7) {$15$ ft};
+\node at (1,-1) {$2$ ft};
+\node at (1,.8){$\theta$};
+\end{tikzpicture}
+\end{wrapfigure}
+Looking at a picture of the situation, we see that the ladder forms the hypotenuse of a right triangle between the wall and floor. With reference to the angle the ladder makes with the floor, the adjacent side is 2 ft, while the hypotenuse is 15 ft. So we have:
+\begin{align*}
+\cos\theta &amp;= \dfrac{2}{15}\\
+\theta &amp;= \arccos\left(\dfrac{2}{15}\right)\\
+\theta &amp;\approx1.437 \text{ radians}\\
+\text{or} \hspace{2em}\theta &amp;\approx 82.34^{\circ}
+\end{align*}</t>
+  </si>
+  <si>
+    <t>The bottom of the ladder in the previous problem starts to slide away
+from the wall at the constant rate of 1 foot per second. 
+When will the ladder make a $60^{\circ}$ angle with
+the ground?</t>
+  </si>
+  <si>
+    <t>We need to determine how far the base of the ladder is from the wall when the ladder makes a $60^{\circ}$ angle with the ground. Let $t$ be the time (in seconds) since the ladder started sliding, so at time $t$ the bottom of the ladder is $2+t$ feet from the wall. The length of the ladder is still 15 feet.\\\\
+Using right-triangle trigonometry: $$\cos60^{\circ} = \dfrac{2+t}{15}\quad\Rightarrow\quad \dfrac{1}{2} = \dfrac{2+t}{15}\quad\Rightarrow\quad t=\frac{15}{2}-2\quad\Rightarrow\quad t=5.5 \text{ sec}$$</t>
+  </si>
+  <si>
+    <t>Find all solutions to the equation $2\sin{x}+1=0$</t>
+  </si>
+  <si>
+    <t>Simplifying gives $\sin{x}=-\frac{1}{2}$.  There are two points on the unit circle that match this, at $x=-\frac{\pi}{6}$ and $x=\frac{7\pi}{6}$.  The function $\sin{x}$ is periodic with period $2\pi$, so all solutions are of the form $x=-\frac{\pi}{6}+2\pi n$ or
+$x=\frac{7\pi}{6}+2\pi n$, where $n$ is an integer.</t>
+  </si>
+  <si>
+    <t>Use technology to help you find at least two approximate solutions to the equation $\tan{2x} = 20$.</t>
+  </si>
+  <si>
+    <t>One solution occurs when $2x=\arctan{20}$.  Using a calculator (in radian mode), I get $2x \approx 1.5208$, so $x \approx 0.7604$.  Recalling that $\tan{x}$ has a period of $\pi$, a second solution would occur when $2x =\arctan{20} + \pi$, so $x \approx .7604+\frac{\pi}{2} \approx 2.3312$.</t>
+  </si>
+  <si>
+    <t>On the shore sits Sea Lion Rock. A lighthouse stands off-shore, 100 yards east of Sea Lion Rock.  Due north of  Sea Lion
+Rock is the exclusive See Sea Lion Motel.  The lighthouse light rotates twice a minute. If the beam of
+light from the lighthouse takes 5 seconds to travel along the shore from Sea Lion Rock
+to the motel, how far is the motel from the rock?</t>
+  </si>
+  <si>
+    <t>\begin{wrapfigure}{l}{4cm}
+\begin{tikzpicture}[scale =1.3]
+\pgfmathsetmacro{\Arad}{.75}%
+\pgfmathsetmacro{\Angle}{120}%
+\pgfmathsetmacro{\XValueArc}{\Arad*cos(\Angle)}%
+\pgfmathsetmacro{\YValueArc}{\Arad*sin(\Angle)}%
+\draw [thick,&lt;-] ($(2,0)+(\XValueArc,\YValueArc)$) %starting point of the arc
+    arc (\Angle:180:\Arad); %(starting angle, ending angle, radius)
+\draw [ultra thick] (0,0) -- (2,0);% Horizontal
+\draw [ultra thick] (0,0) -- (0,4);% Vert
+\draw [ultra thick, dotted] (2,0) -- (0,1.5); 
+\draw [ultra thick] (2,0) -- (0,4); 
+\draw [thick,-&gt;] (.1,1.7)--(0.1,3.4);
+\draw[thick,fill] (0,0) circle(0.1);
+\draw [decorate,decoration={brace,amplitude=12pt},xshift=-4pt,yshift=0pt]
+(0,0) -- (0,4) node [midway,xshift=-0.25in] 
+{$y$};
+\node at (1,-0.5) {$100$ yd};
+\node at (1.2,.3){$\omega$};
+\end{tikzpicture}
+\end{wrapfigure}
+The first thing we should do is convert our angular velocity into units of $\frac{\text{rad}}{\text{sec}}$: $$\omega=\dfrac{2\text{ rev}}{1\text{ min}}\left(\dfrac{2\pi \text{ rad}}{1\text{ rev}}\right)\left(\dfrac{1\text{ min}}{60\text{ sec}}\right)=\dfrac{\pi \text{ rad}}{15 \text{ sec}}$$
+If it takes 5 seconds for the light to travel between the Sea Lion Rock and the See Sea Lion Motel, then the angle in which the light passes during this time is: $$\theta = \omega \cdot t=\dfrac{\pi \text{ rad}}{15 \text{ sec}}\cdot (5 \text{ sec})=\dfrac{\pi}{3} \text{ rad}$$
+Using trig ratios to solve, we have:
+\[\tan\theta = \dfrac{y}{100}\quad\Rightarrow\quad y = 100\cdot\tan\left(\dfrac{\pi}{3}\right)=100\sqrt{3}\approx 173 \text{ yd}\]</t>
+  </si>
+  <si>
+    <t>While staring out the window, you notice 
+	\begin{enumerate}
+		\item[a)] that it is a warm and sunny day, 
+		\item[b)] that your line of sight to the top of a nearby tree makes an angle of 45 degrees above the horizontal, and
+		\item[c)] that your line of sight to the base of the tree makes an angle of 30 degrees below the horizontal. 
+	\end{enumerate}
+			Taking advantage of a), you go outside and measure that it is 40 feet from the building to the base of the tree. How tall is the tree?</t>
+  </si>
+  <si>
+    <t>\begin{tabular}{cp{\dimexpr 0.825\linewidth}}
+\begin{tikzpicture}[yshift=20]
+\draw [thick] (0,0) -- (2,0) {};
+\draw [thick] (2,0) -- (2,2) {};
+\draw [thick] (2,0) -- (2,-1.15) {};
+\draw [thick] (0,0) -- (2,2) {};
+\draw [thick] (0,0) -- (2,-1.15) {};
+\draw [decorate,decoration={brace,amplitude=12pt}] (0,2.1) -- (2,2.1) node [midway, yshift=20] {40 ft};
+\draw [thick] (0.5,0) arc (0:45:0.5) {};
+\node at (0.9,0.3) {$45^\circ$};
+\draw [thick] (1,0) arc (0:-30:1) {};
+\node at (1.4,-0.3) {$30^\circ$};
+% (*Mathematica sun...*)
+% Map[{0.5*Cos[# Pi/180], 4 + 0.5*Sin[# Pi/180]} &amp;, Range[270, 360, 10]]
+% Map[{0.6*Cos[# Pi/180], 4 + 0.6*Sin[# Pi/180]} &amp;, Range[270, 360, 10]]
+\draw (0,3.5) arc (270:360:0.5) {};
+\draw (0,3.5) -- (0,3.4) {};
+\draw (0.086, 3.507) -- (0.104, 3.409) {};
+\draw (0.171,3.53) -- (0.205,3.436) {};
+\draw (0.25,3.566) -- (0.3,3.48) {};
+\draw (0.321,3.616) -- (0.385,3.54) {};
+\draw (0.383,3.678) -- (0.459,3.614) {};
+\draw (0.433,3.75) -- (0.519,3.7) {};
+\draw (0.469,3.828) -- (0.563,3.794) {};
+\draw (0.492,3.913) -- (0.59,3.895) {};
+\draw (0.5,4) -- (0.6,4) {};
+\end{tikzpicture}&amp;\begin{minipage}[b]{\linewidth}
+Draw a triangle from your window, straight across, then vertically to the top of the tree. The angle at your window is $45^{\circ}$, and the adjacent side is $40$ feet, which means the opposite side is also $40$ feet. This is how high the tree extends above your window.\\\\
+Then, draw a another triangle from the window, straight across then down to the bottom of the tree. The angle at the window is $30^{\circ}$ and the adjacent side is $40$ feet; that means the opposite side (the height of your window) is $40\cdot \tan{30^\circ}\approx23$ feet.\\\\
+The total height of the tree is the sum of these two heights, which is about 63 feet.
+\end{minipage}\end{tabular}</t>
+  </si>
+  <si>
+    <t>The red stripe on a barber pole makes one complete revolution around the pole. If the pole is 50 inches tall and has the amazingly precise radius of ${ \frac{25}{\pi \sqrt 3}}$ inches, what angle does the stripe make with base of the pole, and how long is the stripe?  (Assume the stripe is a thin line.)</t>
+  </si>
+  <si>
+    <t>\begin{wrapfigure}{l}{4cm}
+\begin{tikzpicture}
+\draw [thick] (0,0) -- (2.8,0) {};
+\draw [thick] (2.8,0) -- (2.8,5) {};
+\draw [thick] (2.8,5) -- (0,5) {};
+\draw [thick] (0,5) -- (0,0) {};
+\draw [thick] (0,0) -- (2.8,5) {};
+\node at (1.2,2.7) {$\ell$};
+\draw [thick] (1,0) arc (0:60:1) {};
+\node at (1.1,0.75) {$\theta$};
+\draw [decorate,decoration={brace,amplitude=12pt}] (2.8,-.1) -- (0,-.1) node [midway, yshift=-25] {$\frac{50}{\sqrt{3}}$ ft};
+\draw [decorate,decoration={brace,amplitude=12pt}] (2.9,5) -- (2.9,0) node [midway, xshift=25] {50 ft};
+\end{tikzpicture}
+\end{wrapfigure}
+The trick is to imagine the barber pole as a rectangle that is rolled up into a cylinder. The stripe makes one complete revolution which means that it goes from the bottom left corner of the rectangle to the top right of the rectangle directly. Now the width of the rectangle is the circumference of the pole: $2\pi r = \frac{50}{\sqrt{3}}$ inches. The height of the rectangle is the height of the pole: $50$ inches. So the right triangle formed has opposite side $50$ and adjacent side $\frac{50}{\sqrt{3}}$, which means the tangent of the angle we're looking for satisfies 
+$$ \tan{\theta} = \frac{50}{\frac{50}{\sqrt{3}}} = \sqrt{3}.$$ $$\theta = \arctan{\sqrt{3}} = \frac{\pi}{3} = 60^{\circ}$$ The length of the stripe can be found with the Pythagorean Theorem as $\ell^2=50^2+\left(\frac{50}{\sqrt{3}}\right)^2$, so $\ell=\frac{100}{\sqrt{3}}$, making the length of the strip $\frac{100}{\sqrt{3}}$ inches.</t>
+  </si>
+  <si>
+    <t>Yours Truly</t>
+  </si>
+  <si>
+    <t>Consider the graph of a unit circle.
+\begin{center}
+    \begin{tikzpicture}
+\begin{axis}[
+    width = 3in,
+    height = 3in,
+    axis lines = center,
+    xlabel = \(x\),
+    ylabel = {\(f(x)\)},
+    xmin=-1.5, xmax=1.5,
+    ymin=-1.5, ymax=1.5,
+    ymajorgrids=true,
+    xmajorgrids=true,
+    xtick={-1.5,-1,-0.5,0.5,1,1.5},
+    ytick={-1.5,-1,-0.5,0.5,1,1.5},
+]
+\addplot [
+    domain=-1:1, 
+    samples=100, 
+    color=black,
+]
+{sqrt(1-x^2)};
+\addplot [
+    domain=-1:1, 
+    samples=100, 
+    color=black,
+]
+{-sqrt(1-x^2)};
+\end{axis}
+\end{tikzpicture}
+\end{center}
+\begin{enumerate}[label = \alph*.]
+    \item What is the equation of the tangent at $(0,1)$? \\
+    % \ifsolutions \textcolor{blue} { $y=1$ } \fi
+    \vspace{1.5in}
+    \item What is the equation of the tangent at $(1,0)$? \\
+    % \ifsolutions \textcolor{blue} { $x=1$ } \fi
+    \vspace{1.5in}
+    \newpage
+    \item What is the equation of the tangent at $(\frac{\sqrt{2}}{2}, \frac{\sqrt{2}}{2})$? You may need to make an educated guess on the slope $m$.\\
+    % \ifsolutions \textcolor{blue} { $y=-1(x-\frac{\sqrt{2}}{2}) + \frac{\sqrt{2}}{2} = \sqrt{2} - x$ } \fi
+    \vspace{1.5in}
+    \item Regarding the position and slope, what are the two rules that a tangent line must follow?\\
+    % \ifsolutions \textcolor{blue} { The line must touch the point and the slope must match the curve. } \fi
+    \vspace{1.5in}
+\end{enumerate}</t>
+  </si>
+  <si>
+    <t>Consider the graph of a unit circle.
+\begin{center}
+    \begin{tikzpicture}
+\begin{axis}[
+    width = 3in,
+    height = 3in,
+    axis lines = center,
+    xlabel = \(x\),
+    ylabel = {\(f(x)\)},
+    xmin=-1.5, xmax=1.5,
+    ymin=-1.5, ymax=1.5,
+    ymajorgrids=true,
+    xmajorgrids=true,
+    xtick={-1.5,-1,-0.5,0.5,1,1.5},
+    ytick={-1.5,-1,-0.5,0.5,1,1.5},
+]
+\addplot [
+    domain=-1:1, 
+    samples=100, 
+    color=black,
+]
+{sqrt(1-x^2)};
+\addplot [
+    domain=-1:1, 
+    samples=100, 
+    color=black,
+]
+{-sqrt(1-x^2)};
+\end{axis}
+\end{tikzpicture}
+\end{center}
+\begin{enumerate}[label = \alph*.]
+    \item What is the equation of the tangent at $(0,1)$? \\
+    \ifsolutions \textcolor{blue} { $y=1$ } \fi
+    \vspace{1.5in}
+    \item What is the equation of the tangent at $(1,0)$? \\
+    \ifsolutions \textcolor{blue} { $x=1$ } \fi
+    \vspace{1.5in}
+    \newpage
+    \item What is the equation of the tangent at $(\frac{\sqrt{2}}{2}, \frac{\sqrt{2}}{2})$? You may need to make an educated guess on the slope $m$.\\
+    \ifsolutions \textcolor{blue} { $y=-1(x-\frac{\sqrt{2}}{2}) + \frac{\sqrt{2}}{2} = \sqrt{2} - x$ } \fi
+    \vspace{1.5in}
+    \item Regarding the position and slope, what are the two rules that a tangent line must follow?\\
+    \ifsolutions \textcolor{blue} { The line must touch the point and the slope must match the curve. } \fi
+    \vspace{1.5in}
+\end{enumerate}</t>
   </si>
 </sst>
 </file>
@@ -1357,7 +1737,7 @@
     <xf numFmtId="0" fontId="6" fillId="0" borderId="4" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="1"/>
@@ -1372,6 +1752,9 @@
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="5"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="4" xfId="4" applyAlignment="1">
+      <alignment wrapText="1"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Explanatory Text" xfId="5" builtinId="53"/>
@@ -5346,468 +5729,633 @@
       </c>
     </row>
     <row r="118" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B118" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D118" s="6" t="str" cm="1">
+      <c r="A118" s="3" t="s">
+        <v>229</v>
+      </c>
+      <c r="B118" s="5" t="s">
+        <v>230</v>
+      </c>
+      <c r="C118" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D118" s="6" cm="1">
         <f t="array" aca="1" ref="D118" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C118, MATCH(FALSE, ISNUMBER(MID(C118, ROW(INDIRECT("1:"&amp;LEN(C118)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E118" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E118" s="7" cm="1">
         <f t="array" aca="1" ref="E118" ca="1">_xlfn.IFNA(_xlfn.IFS(D118&lt;6,1,D118&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G118" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F118" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G118" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>52</v>
       </c>
       <c r="H118" t="str" cm="1">
         <f t="array" ref="H118">_xlfn.IFS(G118="","",G118&gt;1000,"Hard",AND(G118&gt;150,G118&lt;=1000),"Medium",AND(G118&gt;0,G118&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="119" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B119" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D119" s="6" t="str" cm="1">
+      <c r="A119" s="3" t="s">
+        <v>231</v>
+      </c>
+      <c r="B119" s="5" t="s">
+        <v>232</v>
+      </c>
+      <c r="C119" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D119" s="6" cm="1">
         <f t="array" aca="1" ref="D119" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C119, MATCH(FALSE, ISNUMBER(MID(C119, ROW(INDIRECT("1:"&amp;LEN(C119)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E119" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E119" s="7" cm="1">
         <f t="array" aca="1" ref="E119" ca="1">_xlfn.IFNA(_xlfn.IFS(D119&lt;6,1,D119&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G119" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F119" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G119" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>51</v>
       </c>
       <c r="H119" t="str" cm="1">
         <f t="array" ref="H119">_xlfn.IFS(G119="","",G119&gt;1000,"Hard",AND(G119&gt;150,G119&lt;=1000),"Medium",AND(G119&gt;0,G119&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="120" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B120" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D120" s="6" t="str" cm="1">
+      <c r="A120" s="3" t="s">
+        <v>233</v>
+      </c>
+      <c r="B120" s="5" t="s">
+        <v>234</v>
+      </c>
+      <c r="C120" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D120" s="6" cm="1">
         <f t="array" aca="1" ref="D120" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C120, MATCH(FALSE, ISNUMBER(MID(C120, ROW(INDIRECT("1:"&amp;LEN(C120)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E120" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E120" s="7" cm="1">
         <f t="array" aca="1" ref="E120" ca="1">_xlfn.IFNA(_xlfn.IFS(D120&lt;6,1,D120&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G120" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F120" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G120" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>51</v>
       </c>
       <c r="H120" t="str" cm="1">
         <f t="array" ref="H120">_xlfn.IFS(G120="","",G120&gt;1000,"Hard",AND(G120&gt;150,G120&lt;=1000),"Medium",AND(G120&gt;0,G120&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="121" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B121" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D121" s="6" t="str" cm="1">
+      <c r="A121" s="3" t="s">
+        <v>235</v>
+      </c>
+      <c r="B121" s="5" t="s">
+        <v>236</v>
+      </c>
+      <c r="C121" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D121" s="6" cm="1">
         <f t="array" aca="1" ref="D121" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C121, MATCH(FALSE, ISNUMBER(MID(C121, ROW(INDIRECT("1:"&amp;LEN(C121)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E121" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E121" s="7" cm="1">
         <f t="array" aca="1" ref="E121" ca="1">_xlfn.IFNA(_xlfn.IFS(D121&lt;6,1,D121&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G121" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F121" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G121" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>68</v>
       </c>
       <c r="H121" t="str" cm="1">
         <f t="array" ref="H121">_xlfn.IFS(G121="","",G121&gt;1000,"Hard",AND(G121&gt;150,G121&lt;=1000),"Medium",AND(G121&gt;0,G121&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="122" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B122" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D122" s="6" t="str" cm="1">
+      <c r="A122" s="3" t="s">
+        <v>237</v>
+      </c>
+      <c r="B122" s="5" t="s">
+        <v>238</v>
+      </c>
+      <c r="C122" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D122" s="6" cm="1">
         <f t="array" aca="1" ref="D122" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C122, MATCH(FALSE, ISNUMBER(MID(C122, ROW(INDIRECT("1:"&amp;LEN(C122)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E122" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E122" s="7" cm="1">
         <f t="array" aca="1" ref="E122" ca="1">_xlfn.IFNA(_xlfn.IFS(D122&lt;6,1,D122&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G122" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F122" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G122" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>68</v>
       </c>
       <c r="H122" t="str" cm="1">
         <f t="array" ref="H122">_xlfn.IFS(G122="","",G122&gt;1000,"Hard",AND(G122&gt;150,G122&lt;=1000),"Medium",AND(G122&gt;0,G122&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="123" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B123" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D123" s="6" t="str" cm="1">
+      <c r="A123" s="3" t="s">
+        <v>239</v>
+      </c>
+      <c r="B123" s="5" t="s">
+        <v>240</v>
+      </c>
+      <c r="C123" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D123" s="6" cm="1">
         <f t="array" aca="1" ref="D123" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C123, MATCH(FALSE, ISNUMBER(MID(C123, ROW(INDIRECT("1:"&amp;LEN(C123)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E123" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E123" s="7" cm="1">
         <f t="array" aca="1" ref="E123" ca="1">_xlfn.IFNA(_xlfn.IFS(D123&lt;6,1,D123&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G123" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F123" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G123" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>69</v>
       </c>
       <c r="H123" t="str" cm="1">
         <f t="array" ref="H123">_xlfn.IFS(G123="","",G123&gt;1000,"Hard",AND(G123&gt;150,G123&lt;=1000),"Medium",AND(G123&gt;0,G123&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="124" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B124" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D124" s="6" t="str" cm="1">
+      <c r="A124" s="3" t="s">
+        <v>242</v>
+      </c>
+      <c r="B124" s="5" t="s">
+        <v>248</v>
+      </c>
+      <c r="C124" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D124" s="6" cm="1">
         <f t="array" aca="1" ref="D124" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C124, MATCH(FALSE, ISNUMBER(MID(C124, ROW(INDIRECT("1:"&amp;LEN(C124)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E124" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E124" s="7" cm="1">
         <f t="array" aca="1" ref="E124" ca="1">_xlfn.IFNA(_xlfn.IFS(D124&lt;6,1,D124&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G124" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F124" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G124" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>65</v>
       </c>
       <c r="H124" t="str" cm="1">
         <f t="array" ref="H124">_xlfn.IFS(G124="","",G124&gt;1000,"Hard",AND(G124&gt;150,G124&lt;=1000),"Medium",AND(G124&gt;0,G124&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="125" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B125" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D125" s="6" t="str" cm="1">
+      <c r="A125" s="3" t="s">
+        <v>243</v>
+      </c>
+      <c r="B125" s="5" t="s">
+        <v>249</v>
+      </c>
+      <c r="C125" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D125" s="6" cm="1">
         <f t="array" aca="1" ref="D125" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C125, MATCH(FALSE, ISNUMBER(MID(C125, ROW(INDIRECT("1:"&amp;LEN(C125)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E125" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E125" s="7" cm="1">
         <f t="array" aca="1" ref="E125" ca="1">_xlfn.IFNA(_xlfn.IFS(D125&lt;6,1,D125&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G125" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F125" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G125" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>88</v>
       </c>
       <c r="H125" t="str" cm="1">
         <f t="array" ref="H125">_xlfn.IFS(G125="","",G125&gt;1000,"Hard",AND(G125&gt;150,G125&lt;=1000),"Medium",AND(G125&gt;0,G125&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="126" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B126" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D126" s="6" t="str" cm="1">
+      <c r="A126" s="3" t="s">
+        <v>244</v>
+      </c>
+      <c r="B126" s="5" t="s">
+        <v>250</v>
+      </c>
+      <c r="C126" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D126" s="6" cm="1">
         <f t="array" aca="1" ref="D126" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C126, MATCH(FALSE, ISNUMBER(MID(C126, ROW(INDIRECT("1:"&amp;LEN(C126)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E126" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E126" s="7" cm="1">
         <f t="array" aca="1" ref="E126" ca="1">_xlfn.IFNA(_xlfn.IFS(D126&lt;6,1,D126&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G126" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F126" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G126" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>88</v>
       </c>
       <c r="H126" t="str" cm="1">
         <f t="array" ref="H126">_xlfn.IFS(G126="","",G126&gt;1000,"Hard",AND(G126&gt;150,G126&lt;=1000),"Medium",AND(G126&gt;0,G126&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="127" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B127" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D127" s="6" t="str" cm="1">
+      <c r="A127" s="3" t="s">
+        <v>245</v>
+      </c>
+      <c r="B127" s="5" t="s">
+        <v>251</v>
+      </c>
+      <c r="C127" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D127" s="6" cm="1">
         <f t="array" aca="1" ref="D127" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C127, MATCH(FALSE, ISNUMBER(MID(C127, ROW(INDIRECT("1:"&amp;LEN(C127)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E127" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E127" s="7" cm="1">
         <f t="array" aca="1" ref="E127" ca="1">_xlfn.IFNA(_xlfn.IFS(D127&lt;6,1,D127&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G127" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F127" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G127" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>88</v>
       </c>
       <c r="H127" t="str" cm="1">
         <f t="array" ref="H127">_xlfn.IFS(G127="","",G127&gt;1000,"Hard",AND(G127&gt;150,G127&lt;=1000),"Medium",AND(G127&gt;0,G127&lt;=150),"Easy")</f>
-        <v/>
+        <v>Easy</v>
       </c>
     </row>
     <row r="128" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B128" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D128" s="6" t="str" cm="1">
+      <c r="A128" s="3" t="s">
+        <v>246</v>
+      </c>
+      <c r="B128" s="5" t="s">
+        <v>252</v>
+      </c>
+      <c r="C128" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D128" s="6" cm="1">
         <f t="array" aca="1" ref="D128" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C128, MATCH(FALSE, ISNUMBER(MID(C128, ROW(INDIRECT("1:"&amp;LEN(C128)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E128" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E128" s="7" cm="1">
         <f t="array" aca="1" ref="E128" ca="1">_xlfn.IFNA(_xlfn.IFS(D128&lt;6,1,D128&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G128" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F128" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G128" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>86</v>
       </c>
       <c r="H128" t="str" cm="1">
         <f t="array" ref="H128">_xlfn.IFS(G128="","",G128&gt;1000,"Hard",AND(G128&gt;150,G128&lt;=1000),"Medium",AND(G128&gt;0,G128&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="129" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B129" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D129" s="6" t="str" cm="1">
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="129" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A129" s="3" t="s">
+        <v>247</v>
+      </c>
+      <c r="B129" s="5" t="s">
+        <v>253</v>
+      </c>
+      <c r="C129" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D129" s="6" cm="1">
         <f t="array" aca="1" ref="D129" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C129, MATCH(FALSE, ISNUMBER(MID(C129, ROW(INDIRECT("1:"&amp;LEN(C129)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E129" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E129" s="7" cm="1">
         <f t="array" aca="1" ref="E129" ca="1">_xlfn.IFNA(_xlfn.IFS(D129&lt;6,1,D129&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G129" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F129" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G129" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>86</v>
       </c>
       <c r="H129" t="str" cm="1">
         <f t="array" ref="H129">_xlfn.IFS(G129="","",G129&gt;1000,"Hard",AND(G129&gt;150,G129&lt;=1000),"Medium",AND(G129&gt;0,G129&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="130" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B130" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D130" s="6" t="str" cm="1">
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="130" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A130" s="4" t="s">
+        <v>254</v>
+      </c>
+      <c r="B130" s="10" t="s">
+        <v>255</v>
+      </c>
+      <c r="C130" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D130" s="6" cm="1">
         <f t="array" aca="1" ref="D130" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C130, MATCH(FALSE, ISNUMBER(MID(C130, ROW(INDIRECT("1:"&amp;LEN(C130)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E130" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E130" s="7" cm="1">
         <f t="array" aca="1" ref="E130" ca="1">_xlfn.IFNA(_xlfn.IFS(D130&lt;6,1,D130&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G130" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F130" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G130" s="8">
         <f t="shared" si="2"/>
-        <v/>
+        <v>1249</v>
       </c>
       <c r="H130" t="str" cm="1">
         <f t="array" ref="H130">_xlfn.IFS(G130="","",G130&gt;1000,"Hard",AND(G130&gt;150,G130&lt;=1000),"Medium",AND(G130&gt;0,G130&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="131" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B131" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D131" s="6" t="str" cm="1">
+        <v>Hard</v>
+      </c>
+    </row>
+    <row r="131" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A131" s="4" t="s">
+        <v>256</v>
+      </c>
+      <c r="B131" s="10" t="s">
+        <v>257</v>
+      </c>
+      <c r="C131" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D131" s="6" cm="1">
         <f t="array" aca="1" ref="D131" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C131, MATCH(FALSE, ISNUMBER(MID(C131, ROW(INDIRECT("1:"&amp;LEN(C131)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E131" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E131" s="7" cm="1">
         <f t="array" aca="1" ref="E131" ca="1">_xlfn.IFNA(_xlfn.IFS(D131&lt;6,1,D131&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G131" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F131" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G131" s="8">
         <f t="shared" ref="G131:G194" si="3">IF(LEN(A131)=0,"",LEN(A131))</f>
-        <v/>
+        <v>199</v>
       </c>
       <c r="H131" t="str" cm="1">
         <f t="array" ref="H131">_xlfn.IFS(G131="","",G131&gt;1000,"Hard",AND(G131&gt;150,G131&lt;=1000),"Medium",AND(G131&gt;0,G131&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="132" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B132" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D132" s="6" t="str" cm="1">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="132" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A132" s="4" t="s">
+        <v>258</v>
+      </c>
+      <c r="B132" s="10" t="s">
+        <v>259</v>
+      </c>
+      <c r="C132" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D132" s="6" cm="1">
         <f t="array" aca="1" ref="D132" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C132, MATCH(FALSE, ISNUMBER(MID(C132, ROW(INDIRECT("1:"&amp;LEN(C132)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E132" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E132" s="7" cm="1">
         <f t="array" aca="1" ref="E132" ca="1">_xlfn.IFNA(_xlfn.IFS(D132&lt;6,1,D132&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G132" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F132" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G132" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>192</v>
       </c>
       <c r="H132" t="str" cm="1">
         <f t="array" ref="H132">_xlfn.IFS(G132="","",G132&gt;1000,"Hard",AND(G132&gt;150,G132&lt;=1000),"Medium",AND(G132&gt;0,G132&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="133" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B133" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D133" s="6" t="str" cm="1">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="133" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A133" s="3" t="s">
+        <v>260</v>
+      </c>
+      <c r="B133" s="10" t="s">
+        <v>261</v>
+      </c>
+      <c r="C133" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D133" s="6" cm="1">
         <f t="array" aca="1" ref="D133" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C133, MATCH(FALSE, ISNUMBER(MID(C133, ROW(INDIRECT("1:"&amp;LEN(C133)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E133" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E133" s="7" cm="1">
         <f t="array" aca="1" ref="E133" ca="1">_xlfn.IFNA(_xlfn.IFS(D133&lt;6,1,D133&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G133" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F133" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G133" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>49</v>
       </c>
       <c r="H133" t="str" cm="1">
         <f t="array" ref="H133">_xlfn.IFS(G133="","",G133&gt;1000,"Hard",AND(G133&gt;150,G133&lt;=1000),"Medium",AND(G133&gt;0,G133&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="134" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B134" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D134" s="6" t="str" cm="1">
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="134" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A134" s="3" t="s">
+        <v>262</v>
+      </c>
+      <c r="B134" s="5" t="s">
+        <v>263</v>
+      </c>
+      <c r="C134" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D134" s="6" cm="1">
         <f t="array" aca="1" ref="D134" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C134, MATCH(FALSE, ISNUMBER(MID(C134, ROW(INDIRECT("1:"&amp;LEN(C134)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E134" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E134" s="7" cm="1">
         <f t="array" aca="1" ref="E134" ca="1">_xlfn.IFNA(_xlfn.IFS(D134&lt;6,1,D134&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G134" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F134" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G134" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>99</v>
       </c>
       <c r="H134" t="str" cm="1">
         <f t="array" ref="H134">_xlfn.IFS(G134="","",G134&gt;1000,"Hard",AND(G134&gt;150,G134&lt;=1000),"Medium",AND(G134&gt;0,G134&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="135" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B135" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D135" s="6" t="str" cm="1">
+        <v>Easy</v>
+      </c>
+    </row>
+    <row r="135" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A135" s="4" t="s">
+        <v>264</v>
+      </c>
+      <c r="B135" s="10" t="s">
+        <v>265</v>
+      </c>
+      <c r="C135" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D135" s="6" cm="1">
         <f t="array" aca="1" ref="D135" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C135, MATCH(FALSE, ISNUMBER(MID(C135, ROW(INDIRECT("1:"&amp;LEN(C135)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E135" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E135" s="7" cm="1">
         <f t="array" aca="1" ref="E135" ca="1">_xlfn.IFNA(_xlfn.IFS(D135&lt;6,1,D135&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G135" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F135" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G135" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>360</v>
       </c>
       <c r="H135" t="str" cm="1">
         <f t="array" ref="H135">_xlfn.IFS(G135="","",G135&gt;1000,"Hard",AND(G135&gt;150,G135&lt;=1000),"Medium",AND(G135&gt;0,G135&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="136" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B136" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D136" s="6" t="str" cm="1">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="136" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A136" s="4" t="s">
+        <v>266</v>
+      </c>
+      <c r="B136" s="10" t="s">
+        <v>267</v>
+      </c>
+      <c r="C136" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D136" s="6" cm="1">
         <f t="array" aca="1" ref="D136" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C136, MATCH(FALSE, ISNUMBER(MID(C136, ROW(INDIRECT("1:"&amp;LEN(C136)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E136" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E136" s="7" cm="1">
         <f t="array" aca="1" ref="E136" ca="1">_xlfn.IFNA(_xlfn.IFS(D136&lt;6,1,D136&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G136" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F136" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G136" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>492</v>
       </c>
       <c r="H136" t="str" cm="1">
         <f t="array" ref="H136">_xlfn.IFS(G136="","",G136&gt;1000,"Hard",AND(G136&gt;150,G136&lt;=1000),"Medium",AND(G136&gt;0,G136&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="137" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B137" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D137" s="6" t="str" cm="1">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="137" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A137" s="3" t="s">
+        <v>268</v>
+      </c>
+      <c r="B137" s="10" t="s">
+        <v>269</v>
+      </c>
+      <c r="C137" s="5" t="s">
+        <v>241</v>
+      </c>
+      <c r="D137" s="6" cm="1">
         <f t="array" aca="1" ref="D137" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C137, MATCH(FALSE, ISNUMBER(MID(C137, ROW(INDIRECT("1:"&amp;LEN(C137)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E137" s="7" t="str" cm="1">
+        <v>0</v>
+      </c>
+      <c r="E137" s="7" cm="1">
         <f t="array" aca="1" ref="E137" ca="1">_xlfn.IFNA(_xlfn.IFS(D137&lt;6,1,D137&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G137" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="F137" s="8" t="s">
+        <v>270</v>
+      </c>
+      <c r="G137" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>304</v>
       </c>
       <c r="H137" t="str" cm="1">
         <f t="array" ref="H137">_xlfn.IFS(G137="","",G137&gt;1000,"Hard",AND(G137&gt;150,G137&lt;=1000),"Medium",AND(G137&gt;0,G137&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="138" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="B138" s="5" t="str">
-        <f>""</f>
-        <v/>
-      </c>
-      <c r="D138" s="6" t="str" cm="1">
+        <v>Medium</v>
+      </c>
+    </row>
+    <row r="138" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A138" s="4" t="s">
+        <v>271</v>
+      </c>
+      <c r="B138" s="10" t="s">
+        <v>272</v>
+      </c>
+      <c r="C138" s="5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D138" s="6" cm="1">
         <f t="array" aca="1" ref="D138" ca="1">_xlfn.IFNA(_xlfn.FLOOR.MATH(LEFT(C138, MATCH(FALSE, ISNUMBER(MID(C138, ROW(INDIRECT("1:"&amp;LEN(C138)+1)), 1) *1), 0) -1)),"")</f>
-        <v/>
-      </c>
-      <c r="E138" s="7" t="str" cm="1">
+        <v>2</v>
+      </c>
+      <c r="E138" s="7" cm="1">
         <f t="array" aca="1" ref="E138" ca="1">_xlfn.IFNA(_xlfn.IFS(D138&lt;6,1,D138&lt;12,2),"")</f>
-        <v/>
-      </c>
-      <c r="G138" s="8" t="str">
+        <v>1</v>
+      </c>
+      <c r="G138" s="8">
         <f t="shared" si="3"/>
-        <v/>
+        <v>1402</v>
       </c>
       <c r="H138" t="str" cm="1">
         <f t="array" ref="H138">_xlfn.IFS(G138="","",G138&gt;1000,"Hard",AND(G138&gt;150,G138&lt;=1000),"Medium",AND(G138&gt;0,G138&lt;=150),"Easy")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="139" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+        <v>Hard</v>
+      </c>
+    </row>
+    <row r="139" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B139" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5829,7 +6377,7 @@
         <v/>
       </c>
     </row>
-    <row r="140" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B140" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5851,7 +6399,7 @@
         <v/>
       </c>
     </row>
-    <row r="141" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B141" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5873,7 +6421,7 @@
         <v/>
       </c>
     </row>
-    <row r="142" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B142" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5895,7 +6443,7 @@
         <v/>
       </c>
     </row>
-    <row r="143" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B143" s="5" t="str">
         <f>""</f>
         <v/>
@@ -5917,7 +6465,7 @@
         <v/>
       </c>
     </row>
-    <row r="144" spans="2:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:8" ht="15" customHeight="1" thickTop="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B144" s="5" t="str">
         <f>""</f>
         <v/>
@@ -9376,18 +9924,24 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="3">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{18F672AA-1B6A-4B7E-8DFD-8F8C9B817B80}">
           <x14:formula1>
             <xm:f>Reference!$A$2:$A$84</xm:f>
           </x14:formula1>
-          <xm:sqref>C1:C1048576</xm:sqref>
+          <xm:sqref>C1</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{A7FA73B3-11E3-47B9-89F7-B5B7D3A8C32E}">
           <x14:formula1>
             <xm:f>Reference!$B$2:$B$4</xm:f>
           </x14:formula1>
           <xm:sqref>H2:H1048576</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{B739B498-5B7F-4652-BB2D-ABF9B4F04CEA}">
+          <x14:formula1>
+            <xm:f>Reference!$A$2:$A$85</xm:f>
+          </x14:formula1>
+          <xm:sqref>C2:C1048576</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -9487,7 +10041,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C645F4B-34D2-4DB1-A544-892297E89749}">
-  <dimension ref="A1:B84"/>
+  <dimension ref="A1:B85"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:2" x14ac:dyDescent="0.25">
@@ -10242,6 +10796,11 @@
         <v/>
       </c>
     </row>
+    <row r="85" spans="1:2" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>241</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
